--- a/question/game_ques.xlsx
+++ b/question/game_ques.xlsx
@@ -2806,9 +2806,8 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="15.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
@@ -2844,10 +2843,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="0" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -2882,7 +2881,7 @@
       <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="3" t="n">
@@ -2917,7 +2916,7 @@
       <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2949,7 +2948,7 @@
       <c r="J4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2981,7 +2980,7 @@
       <c r="J5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3013,7 +3012,7 @@
       <c r="J6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3045,7 +3044,7 @@
       <c r="J7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3077,7 +3076,7 @@
       <c r="J8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3109,7 +3108,7 @@
       <c r="J9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3141,7 +3140,7 @@
       <c r="J10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="0" t="s">
+      <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3173,7 +3172,7 @@
       <c r="J11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="0" t="s">
+      <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3205,10 +3204,10 @@
       <c r="J12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="0" t="s">
+      <c r="K12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -3243,10 +3242,10 @@
       <c r="J13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="0" t="s">
+      <c r="K13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L13" s="0" t="s">
+      <c r="L13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3278,10 +3277,10 @@
       <c r="J14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="0" t="s">
+      <c r="K14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3313,10 +3312,10 @@
       <c r="J15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="0" t="s">
+      <c r="K15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3348,10 +3347,10 @@
       <c r="J16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="0" t="s">
+      <c r="K16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="0" t="s">
+      <c r="L16" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3383,10 +3382,10 @@
       <c r="J17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="0" t="s">
+      <c r="K17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3418,10 +3417,10 @@
       <c r="J18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K18" s="0" t="s">
+      <c r="K18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3453,10 +3452,10 @@
       <c r="J19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="0" t="s">
+      <c r="K19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="0" t="s">
+      <c r="L19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3488,10 +3487,10 @@
       <c r="J20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K20" s="0" t="s">
+      <c r="K20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L20" s="0" t="s">
+      <c r="L20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3523,10 +3522,10 @@
       <c r="J21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K21" s="0" t="s">
+      <c r="K21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L21" s="0" t="s">
+      <c r="L21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3558,10 +3557,10 @@
       <c r="J22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K22" s="0" t="s">
+      <c r="K22" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L22" s="0" t="s">
+      <c r="L22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -3596,10 +3595,10 @@
       <c r="J23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="K23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="0" t="s">
+      <c r="L23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3631,10 +3630,10 @@
       <c r="J24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K24" s="0" t="s">
+      <c r="K24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="0" t="s">
+      <c r="L24" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3666,10 +3665,10 @@
       <c r="J25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K25" s="0" t="s">
+      <c r="K25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L25" s="0" t="s">
+      <c r="L25" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3701,10 +3700,10 @@
       <c r="J26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K26" s="0" t="s">
+      <c r="K26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L26" s="0" t="s">
+      <c r="L26" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3736,10 +3735,10 @@
       <c r="J27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="0" t="s">
+      <c r="K27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L27" s="0" t="s">
+      <c r="L27" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3771,10 +3770,10 @@
       <c r="J28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K28" s="0" t="s">
+      <c r="K28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="0" t="s">
+      <c r="L28" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3806,10 +3805,10 @@
       <c r="J29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="0" t="s">
+      <c r="K29" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L29" s="0" t="s">
+      <c r="L29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3841,10 +3840,10 @@
       <c r="J30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K30" s="0" t="s">
+      <c r="K30" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="0" t="s">
+      <c r="L30" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3876,10 +3875,10 @@
       <c r="J31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="0" t="s">
+      <c r="K31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="0" t="s">
+      <c r="L31" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3911,10 +3910,10 @@
       <c r="J32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="0" t="s">
+      <c r="K32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L32" s="0" t="s">
+      <c r="L32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3949,10 +3948,10 @@
       <c r="J33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K33" s="0" t="s">
+      <c r="K33" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L33" s="0" t="s">
+      <c r="L33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3984,10 +3983,10 @@
       <c r="J34" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K34" s="0" t="s">
+      <c r="K34" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L34" s="0" t="s">
+      <c r="L34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4019,10 +4018,10 @@
       <c r="J35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K35" s="0" t="s">
+      <c r="K35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="0" t="s">
+      <c r="L35" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4054,10 +4053,10 @@
       <c r="J36" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K36" s="0" t="s">
+      <c r="K36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L36" s="0" t="s">
+      <c r="L36" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4089,10 +4088,10 @@
       <c r="J37" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K37" s="0" t="s">
+      <c r="K37" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L37" s="0" t="s">
+      <c r="L37" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4124,10 +4123,10 @@
       <c r="J38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K38" s="0" t="s">
+      <c r="K38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L38" s="0" t="s">
+      <c r="L38" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4159,10 +4158,10 @@
       <c r="J39" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="0" t="s">
+      <c r="K39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L39" s="0" t="s">
+      <c r="L39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4194,10 +4193,10 @@
       <c r="J40" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K40" s="0" t="s">
+      <c r="K40" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="0" t="s">
+      <c r="L40" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4229,10 +4228,10 @@
       <c r="J41" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K41" s="0" t="s">
+      <c r="K41" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L41" s="0" t="s">
+      <c r="L41" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4264,10 +4263,10 @@
       <c r="J42" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K42" s="0" t="s">
+      <c r="K42" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L42" s="0" t="s">
+      <c r="L42" s="1" t="s">
         <v>46</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -4302,10 +4301,10 @@
       <c r="J43" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K43" s="0" t="s">
+      <c r="K43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L43" s="0" t="s">
+      <c r="L43" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4337,10 +4336,10 @@
       <c r="J44" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K44" s="0" t="s">
+      <c r="K44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L44" s="0" t="s">
+      <c r="L44" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4372,10 +4371,10 @@
       <c r="J45" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K45" s="0" t="s">
+      <c r="K45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L45" s="0" t="s">
+      <c r="L45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4407,10 +4406,10 @@
       <c r="J46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K46" s="0" t="s">
+      <c r="K46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L46" s="0" t="s">
+      <c r="L46" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4442,10 +4441,10 @@
       <c r="J47" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K47" s="0" t="s">
+      <c r="K47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L47" s="0" t="s">
+      <c r="L47" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4477,10 +4476,10 @@
       <c r="J48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K48" s="0" t="s">
+      <c r="K48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L48" s="0" t="s">
+      <c r="L48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4512,10 +4511,10 @@
       <c r="J49" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K49" s="0" t="s">
+      <c r="K49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L49" s="0" t="s">
+      <c r="L49" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4547,10 +4546,10 @@
       <c r="J50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K50" s="0" t="s">
+      <c r="K50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L50" s="0" t="s">
+      <c r="L50" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4582,10 +4581,10 @@
       <c r="J51" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K51" s="0" t="s">
+      <c r="K51" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L51" s="0" t="s">
+      <c r="L51" s="1" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4617,10 +4616,10 @@
       <c r="J52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K52" s="0" t="s">
+      <c r="K52" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L52" s="0" t="s">
+      <c r="L52" s="1" t="s">
         <v>60</v>
       </c>
       <c r="M52" s="3" t="n">
@@ -4655,10 +4654,10 @@
       <c r="J53" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K53" s="0" t="s">
+      <c r="K53" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L53" s="0" t="s">
+      <c r="L53" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4690,10 +4689,10 @@
       <c r="J54" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K54" s="0" t="s">
+      <c r="K54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L54" s="0" t="s">
+      <c r="L54" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4725,10 +4724,10 @@
       <c r="J55" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K55" s="0" t="s">
+      <c r="K55" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L55" s="0" t="s">
+      <c r="L55" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4760,10 +4759,10 @@
       <c r="J56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K56" s="0" t="s">
+      <c r="K56" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L56" s="0" t="s">
+      <c r="L56" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4795,10 +4794,10 @@
       <c r="J57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K57" s="0" t="s">
+      <c r="K57" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L57" s="0" t="s">
+      <c r="L57" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4830,10 +4829,10 @@
       <c r="J58" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K58" s="0" t="s">
+      <c r="K58" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L58" s="0" t="s">
+      <c r="L58" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4865,10 +4864,10 @@
       <c r="J59" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K59" s="0" t="s">
+      <c r="K59" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L59" s="0" t="s">
+      <c r="L59" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4900,10 +4899,10 @@
       <c r="J60" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K60" s="0" t="s">
+      <c r="K60" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L60" s="0" t="s">
+      <c r="L60" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4935,10 +4934,10 @@
       <c r="J61" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K61" s="0" t="s">
+      <c r="K61" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L61" s="0" t="s">
+      <c r="L61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4970,10 +4969,10 @@
       <c r="J62" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K62" s="0" t="s">
+      <c r="K62" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L62" s="0" t="s">
+      <c r="L62" s="1" t="s">
         <v>70</v>
       </c>
       <c r="M62" s="3" t="n">
@@ -5008,10 +5007,10 @@
       <c r="J63" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K63" s="0" t="s">
+      <c r="K63" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L63" s="0" t="s">
+      <c r="L63" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5043,10 +5042,10 @@
       <c r="J64" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K64" s="0" t="s">
+      <c r="K64" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L64" s="0" t="s">
+      <c r="L64" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5078,10 +5077,10 @@
       <c r="J65" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K65" s="0" t="s">
+      <c r="K65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L65" s="0" t="s">
+      <c r="L65" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5113,10 +5112,10 @@
       <c r="J66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K66" s="0" t="s">
+      <c r="K66" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L66" s="0" t="s">
+      <c r="L66" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5148,10 +5147,10 @@
       <c r="J67" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K67" s="0" t="s">
+      <c r="K67" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L67" s="0" t="s">
+      <c r="L67" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5183,10 +5182,10 @@
       <c r="J68" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K68" s="0" t="s">
+      <c r="K68" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L68" s="0" t="s">
+      <c r="L68" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5218,10 +5217,10 @@
       <c r="J69" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K69" s="0" t="s">
+      <c r="K69" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L69" s="0" t="s">
+      <c r="L69" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5253,10 +5252,10 @@
       <c r="J70" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K70" s="0" t="s">
+      <c r="K70" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L70" s="0" t="s">
+      <c r="L70" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5288,10 +5287,10 @@
       <c r="J71" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K71" s="0" t="s">
+      <c r="K71" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L71" s="0" t="s">
+      <c r="L71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5323,10 +5322,10 @@
       <c r="J72" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K72" s="0" t="s">
+      <c r="K72" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L72" s="0" t="s">
+      <c r="L72" s="1" t="s">
         <v>81</v>
       </c>
       <c r="M72" s="3" t="n">
@@ -5361,10 +5360,10 @@
       <c r="J73" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K73" s="0" t="s">
+      <c r="K73" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L73" s="0" t="s">
+      <c r="L73" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5396,10 +5395,10 @@
       <c r="J74" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K74" s="0" t="s">
+      <c r="K74" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L74" s="0" t="s">
+      <c r="L74" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5431,10 +5430,10 @@
       <c r="J75" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K75" s="0" t="s">
+      <c r="K75" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L75" s="0" t="s">
+      <c r="L75" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5466,10 +5465,10 @@
       <c r="J76" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K76" s="0" t="s">
+      <c r="K76" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L76" s="0" t="s">
+      <c r="L76" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5501,10 +5500,10 @@
       <c r="J77" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K77" s="0" t="s">
+      <c r="K77" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L77" s="0" t="s">
+      <c r="L77" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5536,10 +5535,10 @@
       <c r="J78" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K78" s="0" t="s">
+      <c r="K78" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L78" s="0" t="s">
+      <c r="L78" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5571,10 +5570,10 @@
       <c r="J79" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K79" s="0" t="s">
+      <c r="K79" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L79" s="0" t="s">
+      <c r="L79" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5606,10 +5605,10 @@
       <c r="J80" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K80" s="0" t="s">
+      <c r="K80" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L80" s="0" t="s">
+      <c r="L80" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5641,10 +5640,10 @@
       <c r="J81" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K81" s="0" t="s">
+      <c r="K81" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L81" s="0" t="s">
+      <c r="L81" s="1" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5676,10 +5675,10 @@
       <c r="J82" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K82" s="0" t="s">
+      <c r="K82" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L82" s="0" t="s">
+      <c r="L82" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M82" s="3" t="n">
@@ -5714,10 +5713,10 @@
       <c r="J83" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K83" s="0" t="s">
+      <c r="K83" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L83" s="0" t="s">
+      <c r="L83" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5749,10 +5748,10 @@
       <c r="J84" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K84" s="0" t="s">
+      <c r="K84" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L84" s="0" t="s">
+      <c r="L84" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5784,10 +5783,10 @@
       <c r="J85" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K85" s="0" t="s">
+      <c r="K85" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L85" s="0" t="s">
+      <c r="L85" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5819,10 +5818,10 @@
       <c r="J86" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K86" s="0" t="s">
+      <c r="K86" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L86" s="0" t="s">
+      <c r="L86" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5854,10 +5853,10 @@
       <c r="J87" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K87" s="0" t="s">
+      <c r="K87" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L87" s="0" t="s">
+      <c r="L87" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5889,10 +5888,10 @@
       <c r="J88" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K88" s="0" t="s">
+      <c r="K88" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L88" s="0" t="s">
+      <c r="L88" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5924,10 +5923,10 @@
       <c r="J89" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K89" s="0" t="s">
+      <c r="K89" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L89" s="0" t="s">
+      <c r="L89" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5959,10 +5958,10 @@
       <c r="J90" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K90" s="0" t="s">
+      <c r="K90" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L90" s="0" t="s">
+      <c r="L90" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -5994,10 +5993,10 @@
       <c r="J91" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K91" s="0" t="s">
+      <c r="K91" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L91" s="0" t="s">
+      <c r="L91" s="1" t="s">
         <v>92</v>
       </c>
     </row>
@@ -6029,10 +6028,10 @@
       <c r="J92" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K92" s="0" t="s">
+      <c r="K92" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L92" s="0" t="s">
+      <c r="L92" s="1" t="s">
         <v>104</v>
       </c>
       <c r="M92" s="3" t="n">
@@ -6067,10 +6066,10 @@
       <c r="J93" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K93" s="0" t="s">
+      <c r="K93" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L93" s="0" t="s">
+      <c r="L93" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6102,10 +6101,10 @@
       <c r="J94" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K94" s="0" t="s">
+      <c r="K94" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L94" s="0" t="s">
+      <c r="L94" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6137,10 +6136,10 @@
       <c r="J95" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K95" s="0" t="s">
+      <c r="K95" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L95" s="0" t="s">
+      <c r="L95" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6172,10 +6171,10 @@
       <c r="J96" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K96" s="0" t="s">
+      <c r="K96" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L96" s="0" t="s">
+      <c r="L96" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6207,10 +6206,10 @@
       <c r="J97" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K97" s="0" t="s">
+      <c r="K97" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L97" s="0" t="s">
+      <c r="L97" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6242,10 +6241,10 @@
       <c r="J98" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K98" s="0" t="s">
+      <c r="K98" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L98" s="0" t="s">
+      <c r="L98" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6277,10 +6276,10 @@
       <c r="J99" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K99" s="0" t="s">
+      <c r="K99" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L99" s="0" t="s">
+      <c r="L99" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6312,10 +6311,10 @@
       <c r="J100" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K100" s="0" t="s">
+      <c r="K100" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L100" s="0" t="s">
+      <c r="L100" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6347,10 +6346,10 @@
       <c r="J101" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K101" s="0" t="s">
+      <c r="K101" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="L101" s="0" t="s">
+      <c r="L101" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6382,10 +6381,10 @@
       <c r="J102" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K102" s="0" t="s">
+      <c r="K102" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L102" s="0" t="s">
+      <c r="L102" s="1" t="s">
         <v>116</v>
       </c>
       <c r="M102" s="3" t="n">
@@ -6420,10 +6419,10 @@
       <c r="J103" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K103" s="0" t="s">
+      <c r="K103" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L103" s="0" t="s">
+      <c r="L103" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6455,10 +6454,10 @@
       <c r="J104" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K104" s="0" t="s">
+      <c r="K104" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L104" s="0" t="s">
+      <c r="L104" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6490,10 +6489,10 @@
       <c r="J105" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K105" s="0" t="s">
+      <c r="K105" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L105" s="0" t="s">
+      <c r="L105" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6525,10 +6524,10 @@
       <c r="J106" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K106" s="0" t="s">
+      <c r="K106" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L106" s="0" t="s">
+      <c r="L106" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6560,10 +6559,10 @@
       <c r="J107" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K107" s="0" t="s">
+      <c r="K107" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L107" s="0" t="s">
+      <c r="L107" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6595,10 +6594,10 @@
       <c r="J108" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K108" s="0" t="s">
+      <c r="K108" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L108" s="0" t="s">
+      <c r="L108" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6630,10 +6629,10 @@
       <c r="J109" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K109" s="0" t="s">
+      <c r="K109" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L109" s="0" t="s">
+      <c r="L109" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6665,10 +6664,10 @@
       <c r="J110" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K110" s="0" t="s">
+      <c r="K110" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L110" s="0" t="s">
+      <c r="L110" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6700,10 +6699,10 @@
       <c r="J111" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K111" s="0" t="s">
+      <c r="K111" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L111" s="0" t="s">
+      <c r="L111" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -6735,10 +6734,10 @@
       <c r="J112" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K112" s="0" t="s">
+      <c r="K112" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L112" s="0" t="s">
+      <c r="L112" s="1" t="s">
         <v>127</v>
       </c>
       <c r="M112" s="3" t="n">
@@ -6773,10 +6772,10 @@
       <c r="J113" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K113" s="0" t="s">
+      <c r="K113" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L113" s="0" t="s">
+      <c r="L113" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6808,10 +6807,10 @@
       <c r="J114" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K114" s="0" t="s">
+      <c r="K114" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L114" s="0" t="s">
+      <c r="L114" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6843,10 +6842,10 @@
       <c r="J115" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K115" s="0" t="s">
+      <c r="K115" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L115" s="0" t="s">
+      <c r="L115" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6878,10 +6877,10 @@
       <c r="J116" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K116" s="0" t="s">
+      <c r="K116" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L116" s="0" t="s">
+      <c r="L116" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6913,10 +6912,10 @@
       <c r="J117" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K117" s="0" t="s">
+      <c r="K117" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L117" s="0" t="s">
+      <c r="L117" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6948,10 +6947,10 @@
       <c r="J118" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K118" s="0" t="s">
+      <c r="K118" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L118" s="0" t="s">
+      <c r="L118" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6983,10 +6982,10 @@
       <c r="J119" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K119" s="0" t="s">
+      <c r="K119" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L119" s="0" t="s">
+      <c r="L119" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7018,10 +7017,10 @@
       <c r="J120" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K120" s="0" t="s">
+      <c r="K120" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L120" s="0" t="s">
+      <c r="L120" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7053,10 +7052,10 @@
       <c r="J121" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K121" s="0" t="s">
+      <c r="K121" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L121" s="0" t="s">
+      <c r="L121" s="1" t="s">
         <v>127</v>
       </c>
     </row>
@@ -7088,10 +7087,10 @@
       <c r="J122" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K122" s="0" t="s">
+      <c r="K122" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L122" s="0" t="s">
+      <c r="L122" s="1" t="s">
         <v>138</v>
       </c>
       <c r="M122" s="1" t="n">
@@ -7126,10 +7125,10 @@
       <c r="J123" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K123" s="0" t="s">
+      <c r="K123" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L123" s="0" t="s">
+      <c r="L123" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7161,10 +7160,10 @@
       <c r="J124" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K124" s="0" t="s">
+      <c r="K124" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L124" s="0" t="s">
+      <c r="L124" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7196,10 +7195,10 @@
       <c r="J125" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K125" s="0" t="s">
+      <c r="K125" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L125" s="0" t="s">
+      <c r="L125" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7231,10 +7230,10 @@
       <c r="J126" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K126" s="0" t="s">
+      <c r="K126" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L126" s="0" t="s">
+      <c r="L126" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7266,10 +7265,10 @@
       <c r="J127" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K127" s="0" t="s">
+      <c r="K127" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L127" s="0" t="s">
+      <c r="L127" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7301,10 +7300,10 @@
       <c r="J128" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K128" s="0" t="s">
+      <c r="K128" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L128" s="0" t="s">
+      <c r="L128" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7336,10 +7335,10 @@
       <c r="J129" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K129" s="0" t="s">
+      <c r="K129" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L129" s="0" t="s">
+      <c r="L129" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7371,10 +7370,10 @@
       <c r="J130" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K130" s="0" t="s">
+      <c r="K130" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L130" s="0" t="s">
+      <c r="L130" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7406,10 +7405,10 @@
       <c r="J131" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K131" s="0" t="s">
+      <c r="K131" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L131" s="0" t="s">
+      <c r="L131" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -7441,10 +7440,10 @@
       <c r="J132" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K132" s="0" t="s">
+      <c r="K132" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L132" s="0" t="s">
+      <c r="L132" s="1" t="s">
         <v>150</v>
       </c>
       <c r="M132" s="1" t="n">
@@ -7479,10 +7478,10 @@
       <c r="J133" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K133" s="0" t="s">
+      <c r="K133" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L133" s="0" t="s">
+      <c r="L133" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7514,10 +7513,10 @@
       <c r="J134" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K134" s="0" t="s">
+      <c r="K134" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L134" s="0" t="s">
+      <c r="L134" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7549,10 +7548,10 @@
       <c r="J135" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K135" s="0" t="s">
+      <c r="K135" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L135" s="0" t="s">
+      <c r="L135" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7584,10 +7583,10 @@
       <c r="J136" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K136" s="0" t="s">
+      <c r="K136" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L136" s="0" t="s">
+      <c r="L136" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7619,10 +7618,10 @@
       <c r="J137" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K137" s="0" t="s">
+      <c r="K137" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L137" s="0" t="s">
+      <c r="L137" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7654,10 +7653,10 @@
       <c r="J138" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K138" s="0" t="s">
+      <c r="K138" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L138" s="0" t="s">
+      <c r="L138" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7689,10 +7688,10 @@
       <c r="J139" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K139" s="0" t="s">
+      <c r="K139" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L139" s="0" t="s">
+      <c r="L139" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7724,10 +7723,10 @@
       <c r="J140" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K140" s="0" t="s">
+      <c r="K140" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L140" s="0" t="s">
+      <c r="L140" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7759,10 +7758,10 @@
       <c r="J141" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K141" s="0" t="s">
+      <c r="K141" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L141" s="0" t="s">
+      <c r="L141" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -7794,10 +7793,10 @@
       <c r="J142" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K142" s="0" t="s">
+      <c r="K142" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L142" s="0" t="s">
+      <c r="L142" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7829,10 +7828,10 @@
       <c r="J143" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K143" s="0" t="s">
+      <c r="K143" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L143" s="0" t="s">
+      <c r="L143" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7864,10 +7863,10 @@
       <c r="J144" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K144" s="0" t="s">
+      <c r="K144" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L144" s="0" t="s">
+      <c r="L144" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7899,10 +7898,10 @@
       <c r="J145" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K145" s="0" t="s">
+      <c r="K145" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L145" s="0" t="s">
+      <c r="L145" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7934,10 +7933,10 @@
       <c r="J146" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K146" s="0" t="s">
+      <c r="K146" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L146" s="0" t="s">
+      <c r="L146" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -7969,10 +7968,10 @@
       <c r="J147" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K147" s="0" t="s">
+      <c r="K147" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L147" s="0" t="s">
+      <c r="L147" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8004,10 +8003,10 @@
       <c r="J148" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K148" s="0" t="s">
+      <c r="K148" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L148" s="0" t="s">
+      <c r="L148" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8039,10 +8038,10 @@
       <c r="J149" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K149" s="0" t="s">
+      <c r="K149" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L149" s="0" t="s">
+      <c r="L149" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8074,10 +8073,10 @@
       <c r="J150" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K150" s="0" t="s">
+      <c r="K150" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L150" s="0" t="s">
+      <c r="L150" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8109,10 +8108,10 @@
       <c r="J151" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="K151" s="0" t="s">
+      <c r="K151" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L151" s="0" t="s">
+      <c r="L151" s="1" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8144,10 +8143,10 @@
       <c r="J152" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K152" s="0" t="s">
+      <c r="K152" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L152" s="0" t="s">
+      <c r="L152" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8179,10 +8178,10 @@
       <c r="J153" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K153" s="0" t="s">
+      <c r="K153" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L153" s="0" t="s">
+      <c r="L153" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8214,10 +8213,10 @@
       <c r="J154" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K154" s="0" t="s">
+      <c r="K154" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L154" s="0" t="s">
+      <c r="L154" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8249,10 +8248,10 @@
       <c r="J155" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K155" s="0" t="s">
+      <c r="K155" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L155" s="0" t="s">
+      <c r="L155" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8284,10 +8283,10 @@
       <c r="J156" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K156" s="0" t="s">
+      <c r="K156" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L156" s="0" t="s">
+      <c r="L156" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8319,10 +8318,10 @@
       <c r="J157" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K157" s="0" t="s">
+      <c r="K157" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L157" s="0" t="s">
+      <c r="L157" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8354,10 +8353,10 @@
       <c r="J158" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K158" s="0" t="s">
+      <c r="K158" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L158" s="0" t="s">
+      <c r="L158" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8389,10 +8388,10 @@
       <c r="J159" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K159" s="0" t="s">
+      <c r="K159" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L159" s="0" t="s">
+      <c r="L159" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8424,10 +8423,10 @@
       <c r="J160" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K160" s="0" t="s">
+      <c r="K160" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L160" s="0" t="s">
+      <c r="L160" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8459,10 +8458,10 @@
       <c r="J161" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="K161" s="0" t="s">
+      <c r="K161" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="L161" s="0" t="s">
+      <c r="L161" s="1" t="s">
         <v>138</v>
       </c>
     </row>
@@ -8494,10 +8493,10 @@
       <c r="J162" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K162" s="0" t="s">
+      <c r="K162" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L162" s="0" t="s">
+      <c r="L162" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8529,10 +8528,10 @@
       <c r="J163" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K163" s="0" t="s">
+      <c r="K163" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L163" s="0" t="s">
+      <c r="L163" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8564,10 +8563,10 @@
       <c r="J164" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K164" s="0" t="s">
+      <c r="K164" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L164" s="0" t="s">
+      <c r="L164" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8599,10 +8598,10 @@
       <c r="J165" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K165" s="0" t="s">
+      <c r="K165" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L165" s="0" t="s">
+      <c r="L165" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8634,10 +8633,10 @@
       <c r="J166" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K166" s="0" t="s">
+      <c r="K166" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L166" s="0" t="s">
+      <c r="L166" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8669,10 +8668,10 @@
       <c r="J167" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K167" s="0" t="s">
+      <c r="K167" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L167" s="0" t="s">
+      <c r="L167" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8704,10 +8703,10 @@
       <c r="J168" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K168" s="0" t="s">
+      <c r="K168" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L168" s="0" t="s">
+      <c r="L168" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8739,10 +8738,10 @@
       <c r="J169" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K169" s="0" t="s">
+      <c r="K169" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L169" s="0" t="s">
+      <c r="L169" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8774,10 +8773,10 @@
       <c r="J170" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K170" s="0" t="s">
+      <c r="K170" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L170" s="0" t="s">
+      <c r="L170" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8809,10 +8808,10 @@
       <c r="J171" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="K171" s="0" t="s">
+      <c r="K171" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L171" s="0" t="s">
+      <c r="L171" s="1" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8844,10 +8843,10 @@
       <c r="J172" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K172" s="0" t="s">
+      <c r="K172" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L172" s="0" t="s">
+      <c r="L172" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -8879,10 +8878,10 @@
       <c r="J173" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K173" s="0" t="s">
+      <c r="K173" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L173" s="0" t="s">
+      <c r="L173" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -8914,10 +8913,10 @@
       <c r="J174" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K174" s="0" t="s">
+      <c r="K174" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L174" s="0" t="s">
+      <c r="L174" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -8949,10 +8948,10 @@
       <c r="J175" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K175" s="0" t="s">
+      <c r="K175" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L175" s="0" t="s">
+      <c r="L175" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -8984,7 +8983,7 @@
       <c r="J176" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K176" s="0" t="s">
+      <c r="K176" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -9016,10 +9015,10 @@
       <c r="J177" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K177" s="0" t="s">
+      <c r="K177" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L177" s="0" t="s">
+      <c r="L177" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9051,10 +9050,10 @@
       <c r="J178" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K178" s="0" t="s">
+      <c r="K178" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L178" s="0" t="s">
+      <c r="L178" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9086,10 +9085,10 @@
       <c r="J179" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K179" s="0" t="s">
+      <c r="K179" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L179" s="0" t="s">
+      <c r="L179" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9121,10 +9120,10 @@
       <c r="J180" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K180" s="0" t="s">
+      <c r="K180" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L180" s="0" t="s">
+      <c r="L180" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9156,10 +9155,10 @@
       <c r="J181" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K181" s="0" t="s">
+      <c r="K181" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L181" s="0" t="s">
+      <c r="L181" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9191,7 +9190,7 @@
       <c r="J182" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K182" s="0" t="s">
+      <c r="K182" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -9223,10 +9222,10 @@
       <c r="J183" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K183" s="0" t="s">
+      <c r="K183" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L183" s="0" t="s">
+      <c r="L183" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9258,10 +9257,10 @@
       <c r="J184" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K184" s="0" t="s">
+      <c r="K184" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L184" s="0" t="s">
+      <c r="L184" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9293,7 +9292,7 @@
       <c r="J185" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K185" s="0" t="s">
+      <c r="K185" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -9325,10 +9324,10 @@
       <c r="J186" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K186" s="0" t="s">
+      <c r="K186" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L186" s="0" t="s">
+      <c r="L186" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9360,7 +9359,7 @@
       <c r="J187" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K187" s="0" t="s">
+      <c r="K187" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9392,10 +9391,10 @@
       <c r="J188" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K188" s="0" t="s">
+      <c r="K188" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L188" s="0" t="s">
+      <c r="L188" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9427,10 +9426,10 @@
       <c r="J189" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K189" s="0" t="s">
+      <c r="K189" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L189" s="0" t="s">
+      <c r="L189" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9462,10 +9461,10 @@
       <c r="J190" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K190" s="0" t="s">
+      <c r="K190" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L190" s="0" t="s">
+      <c r="L190" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9497,7 +9496,7 @@
       <c r="J191" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K191" s="0" t="s">
+      <c r="K191" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9529,10 +9528,10 @@
       <c r="J192" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K192" s="0" t="s">
+      <c r="K192" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L192" s="0" t="s">
+      <c r="L192" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9564,10 +9563,10 @@
       <c r="J193" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K193" s="0" t="s">
+      <c r="K193" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L193" s="0" t="s">
+      <c r="L193" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9599,10 +9598,10 @@
       <c r="J194" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K194" s="0" t="s">
+      <c r="K194" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L194" s="0" t="s">
+      <c r="L194" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9634,7 +9633,7 @@
       <c r="J195" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K195" s="0" t="s">
+      <c r="K195" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9666,7 +9665,7 @@
       <c r="J196" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K196" s="0" t="s">
+      <c r="K196" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -9698,10 +9697,10 @@
       <c r="J197" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K197" s="0" t="s">
+      <c r="K197" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L197" s="0" t="s">
+      <c r="L197" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9733,10 +9732,10 @@
       <c r="J198" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K198" s="0" t="s">
+      <c r="K198" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L198" s="0" t="s">
+      <c r="L198" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9768,10 +9767,10 @@
       <c r="J199" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K199" s="0" t="s">
+      <c r="K199" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L199" s="0" t="s">
+      <c r="L199" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9803,10 +9802,10 @@
       <c r="J200" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K200" s="0" t="s">
+      <c r="K200" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L200" s="0" t="s">
+      <c r="L200" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -9838,10 +9837,10 @@
       <c r="J201" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K201" s="0" t="s">
+      <c r="K201" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L201" s="0" t="s">
+      <c r="L201" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -9873,10 +9872,10 @@
       <c r="J202" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K202" s="0" t="s">
+      <c r="K202" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L202" s="0" t="s">
+      <c r="L202" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -9908,7 +9907,7 @@
       <c r="J203" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K203" s="0" t="s">
+      <c r="K203" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -9940,10 +9939,10 @@
       <c r="J204" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K204" s="0" t="s">
+      <c r="K204" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L204" s="0" t="s">
+      <c r="L204" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -9975,10 +9974,10 @@
       <c r="J205" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K205" s="0" t="s">
+      <c r="K205" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L205" s="0" t="s">
+      <c r="L205" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10010,7 +10009,7 @@
       <c r="J206" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K206" s="0" t="s">
+      <c r="K206" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -10042,7 +10041,7 @@
       <c r="J207" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K207" s="0" t="s">
+      <c r="K207" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -10074,10 +10073,10 @@
       <c r="J208" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K208" s="0" t="s">
+      <c r="K208" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L208" s="0" t="s">
+      <c r="L208" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10109,10 +10108,10 @@
       <c r="J209" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K209" s="0" t="s">
+      <c r="K209" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L209" s="0" t="s">
+      <c r="L209" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10144,10 +10143,10 @@
       <c r="J210" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K210" s="0" t="s">
+      <c r="K210" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L210" s="0" t="s">
+      <c r="L210" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10179,10 +10178,10 @@
       <c r="J211" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K211" s="0" t="s">
+      <c r="K211" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L211" s="0" t="s">
+      <c r="L211" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10214,10 +10213,10 @@
       <c r="J212" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K212" s="0" t="s">
+      <c r="K212" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L212" s="0" t="s">
+      <c r="L212" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10249,10 +10248,10 @@
       <c r="J213" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K213" s="0" t="s">
+      <c r="K213" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L213" s="0" t="s">
+      <c r="L213" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10284,10 +10283,10 @@
       <c r="J214" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K214" s="0" t="s">
+      <c r="K214" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L214" s="0" t="s">
+      <c r="L214" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -10319,7 +10318,7 @@
       <c r="J215" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K215" s="0" t="s">
+      <c r="K215" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -10351,10 +10350,10 @@
       <c r="J216" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K216" s="0" t="s">
+      <c r="K216" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L216" s="0" t="s">
+      <c r="L216" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -10386,10 +10385,10 @@
       <c r="J217" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K217" s="0" t="s">
+      <c r="K217" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L217" s="0" t="s">
+      <c r="L217" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -10421,10 +10420,10 @@
       <c r="J218" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K218" s="0" t="s">
+      <c r="K218" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L218" s="0" t="s">
+      <c r="L218" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -10456,10 +10455,10 @@
       <c r="J219" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K219" s="0" t="s">
+      <c r="K219" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L219" s="0" t="s">
+      <c r="L219" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10491,10 +10490,10 @@
       <c r="J220" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K220" s="0" t="s">
+      <c r="K220" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L220" s="0" t="s">
+      <c r="L220" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10526,10 +10525,10 @@
       <c r="J221" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K221" s="0" t="s">
+      <c r="K221" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L221" s="0" t="s">
+      <c r="L221" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10561,10 +10560,10 @@
       <c r="J222" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K222" s="0" t="s">
+      <c r="K222" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L222" s="0" t="s">
+      <c r="L222" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10596,10 +10595,10 @@
       <c r="J223" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K223" s="0" t="s">
+      <c r="K223" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L223" s="0" t="s">
+      <c r="L223" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10631,10 +10630,10 @@
       <c r="J224" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K224" s="0" t="s">
+      <c r="K224" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L224" s="0" t="s">
+      <c r="L224" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10666,10 +10665,10 @@
       <c r="J225" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K225" s="0" t="s">
+      <c r="K225" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L225" s="0" t="s">
+      <c r="L225" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10701,10 +10700,10 @@
       <c r="J226" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K226" s="0" t="s">
+      <c r="K226" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L226" s="0" t="s">
+      <c r="L226" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10736,10 +10735,10 @@
       <c r="J227" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="K227" s="0" t="s">
+      <c r="K227" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L227" s="0" t="s">
+      <c r="L227" s="1" t="s">
         <v>231</v>
       </c>
     </row>
@@ -10771,10 +10770,10 @@
       <c r="J228" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K228" s="0" t="s">
+      <c r="K228" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L228" s="0" t="s">
+      <c r="L228" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10806,10 +10805,10 @@
       <c r="J229" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K229" s="0" t="s">
+      <c r="K229" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L229" s="0" t="s">
+      <c r="L229" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10841,10 +10840,10 @@
       <c r="J230" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K230" s="0" t="s">
+      <c r="K230" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L230" s="0" t="s">
+      <c r="L230" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -10876,10 +10875,10 @@
       <c r="J231" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K231" s="0" t="s">
+      <c r="K231" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L231" s="0" t="s">
+      <c r="L231" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -10911,10 +10910,10 @@
       <c r="J232" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K232" s="0" t="s">
+      <c r="K232" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L232" s="0" t="s">
+      <c r="L232" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -10946,10 +10945,10 @@
       <c r="J233" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K233" s="0" t="s">
+      <c r="K233" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L233" s="0" t="s">
+      <c r="L233" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -10981,10 +10980,10 @@
       <c r="J234" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K234" s="0" t="s">
+      <c r="K234" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L234" s="0" t="s">
+      <c r="L234" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -11016,10 +11015,10 @@
       <c r="J235" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K235" s="0" t="s">
+      <c r="K235" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L235" s="0" t="s">
+      <c r="L235" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11051,10 +11050,10 @@
       <c r="J236" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K236" s="0" t="s">
+      <c r="K236" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L236" s="0" t="s">
+      <c r="L236" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11086,10 +11085,10 @@
       <c r="J237" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K237" s="0" t="s">
+      <c r="K237" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L237" s="0" t="s">
+      <c r="L237" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11121,10 +11120,10 @@
       <c r="J238" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K238" s="0" t="s">
+      <c r="K238" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L238" s="0" t="s">
+      <c r="L238" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -11156,7 +11155,7 @@
       <c r="J239" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K239" s="0" t="s">
+      <c r="K239" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -11188,10 +11187,10 @@
       <c r="J240" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K240" s="0" t="s">
+      <c r="K240" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L240" s="0" t="s">
+      <c r="L240" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11223,10 +11222,10 @@
       <c r="J241" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K241" s="0" t="s">
+      <c r="K241" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L241" s="0" t="s">
+      <c r="L241" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11258,10 +11257,10 @@
       <c r="J242" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K242" s="0" t="s">
+      <c r="K242" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L242" s="0" t="s">
+      <c r="L242" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11293,10 +11292,10 @@
       <c r="J243" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K243" s="0" t="s">
+      <c r="K243" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L243" s="0" t="s">
+      <c r="L243" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11328,10 +11327,10 @@
       <c r="J244" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K244" s="0" t="s">
+      <c r="K244" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L244" s="0" t="s">
+      <c r="L244" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11363,10 +11362,10 @@
       <c r="J245" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K245" s="0" t="s">
+      <c r="K245" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L245" s="0" t="s">
+      <c r="L245" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -11398,10 +11397,10 @@
       <c r="J246" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K246" s="0" t="s">
+      <c r="K246" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L246" s="0" t="s">
+      <c r="L246" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11433,10 +11432,10 @@
       <c r="J247" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K247" s="0" t="s">
+      <c r="K247" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L247" s="0" t="s">
+      <c r="L247" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11468,10 +11467,10 @@
       <c r="J248" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K248" s="0" t="s">
+      <c r="K248" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L248" s="0" t="s">
+      <c r="L248" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11503,10 +11502,10 @@
       <c r="J249" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K249" s="0" t="s">
+      <c r="K249" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L249" s="0" t="s">
+      <c r="L249" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11538,10 +11537,10 @@
       <c r="J250" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K250" s="0" t="s">
+      <c r="K250" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L250" s="0" t="s">
+      <c r="L250" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11573,10 +11572,10 @@
       <c r="J251" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K251" s="0" t="s">
+      <c r="K251" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L251" s="0" t="s">
+      <c r="L251" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11608,10 +11607,10 @@
       <c r="J252" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K252" s="0" t="s">
+      <c r="K252" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L252" s="0" t="s">
+      <c r="L252" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11643,10 +11642,10 @@
       <c r="J253" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K253" s="0" t="s">
+      <c r="K253" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L253" s="0" t="s">
+      <c r="L253" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11678,7 +11677,7 @@
       <c r="J254" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K254" s="0" t="s">
+      <c r="K254" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11710,10 +11709,10 @@
       <c r="J255" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K255" s="0" t="s">
+      <c r="K255" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L255" s="0" t="s">
+      <c r="L255" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11745,10 +11744,10 @@
       <c r="J256" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K256" s="0" t="s">
+      <c r="K256" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L256" s="0" t="s">
+      <c r="L256" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11780,7 +11779,7 @@
       <c r="J257" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K257" s="0" t="s">
+      <c r="K257" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -11812,10 +11811,10 @@
       <c r="J258" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K258" s="0" t="s">
+      <c r="K258" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L258" s="0" t="s">
+      <c r="L258" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11847,10 +11846,10 @@
       <c r="J259" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K259" s="0" t="s">
+      <c r="K259" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L259" s="0" t="s">
+      <c r="L259" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11882,10 +11881,10 @@
       <c r="J260" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K260" s="0" t="s">
+      <c r="K260" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L260" s="0" t="s">
+      <c r="L260" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -11917,10 +11916,10 @@
       <c r="J261" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K261" s="0" t="s">
+      <c r="K261" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L261" s="0" t="s">
+      <c r="L261" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -11952,10 +11951,10 @@
       <c r="J262" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K262" s="0" t="s">
+      <c r="K262" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L262" s="0" t="s">
+      <c r="L262" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -11987,10 +11986,10 @@
       <c r="J263" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K263" s="0" t="s">
+      <c r="K263" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L263" s="0" t="s">
+      <c r="L263" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12022,10 +12021,10 @@
       <c r="J264" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K264" s="0" t="s">
+      <c r="K264" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L264" s="0" t="s">
+      <c r="L264" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -12057,10 +12056,10 @@
       <c r="J265" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K265" s="0" t="s">
+      <c r="K265" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L265" s="0" t="s">
+      <c r="L265" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12092,10 +12091,10 @@
       <c r="J266" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K266" s="0" t="s">
+      <c r="K266" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L266" s="0" t="s">
+      <c r="L266" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12127,10 +12126,10 @@
       <c r="J267" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K267" s="0" t="s">
+      <c r="K267" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L267" s="0" t="s">
+      <c r="L267" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -12162,10 +12161,10 @@
       <c r="J268" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K268" s="0" t="s">
+      <c r="K268" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L268" s="0" t="s">
+      <c r="L268" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12197,10 +12196,10 @@
       <c r="J269" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K269" s="0" t="s">
+      <c r="K269" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L269" s="0" t="s">
+      <c r="L269" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -12232,10 +12231,10 @@
       <c r="J270" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K270" s="0" t="s">
+      <c r="K270" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L270" s="0" t="s">
+      <c r="L270" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12267,10 +12266,10 @@
       <c r="J271" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K271" s="0" t="s">
+      <c r="K271" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L271" s="0" t="s">
+      <c r="L271" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -12302,10 +12301,10 @@
       <c r="J272" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K272" s="0" t="s">
+      <c r="K272" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L272" s="0" t="s">
+      <c r="L272" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12337,10 +12336,10 @@
       <c r="J273" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K273" s="0" t="s">
+      <c r="K273" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L273" s="0" t="s">
+      <c r="L273" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12372,10 +12371,10 @@
       <c r="J274" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K274" s="0" t="s">
+      <c r="K274" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L274" s="0" t="s">
+      <c r="L274" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -12407,10 +12406,10 @@
       <c r="J275" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="K275" s="0" t="s">
+      <c r="K275" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="L275" s="0" t="s">
+      <c r="L275" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -12442,10 +12441,10 @@
       <c r="J276" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K276" s="0" t="s">
+      <c r="K276" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L276" s="0" t="s">
+      <c r="L276" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12477,10 +12476,10 @@
       <c r="J277" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K277" s="0" t="s">
+      <c r="K277" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L277" s="0" t="s">
+      <c r="L277" s="1" t="s">
         <v>285</v>
       </c>
     </row>
@@ -12512,10 +12511,10 @@
       <c r="J278" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K278" s="0" t="s">
+      <c r="K278" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L278" s="0" t="s">
+      <c r="L278" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -12547,10 +12546,10 @@
       <c r="J279" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K279" s="0" t="s">
+      <c r="K279" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L279" s="0" t="s">
+      <c r="L279" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12582,10 +12581,10 @@
       <c r="J280" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K280" s="0" t="s">
+      <c r="K280" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L280" s="0" t="s">
+      <c r="L280" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12617,10 +12616,10 @@
       <c r="J281" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K281" s="0" t="s">
+      <c r="K281" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L281" s="0" t="s">
+      <c r="L281" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12652,10 +12651,10 @@
       <c r="J282" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K282" s="0" t="s">
+      <c r="K282" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L282" s="0" t="s">
+      <c r="L282" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12687,10 +12686,10 @@
       <c r="J283" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K283" s="0" t="s">
+      <c r="K283" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L283" s="0" t="s">
+      <c r="L283" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12722,10 +12721,10 @@
       <c r="J284" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K284" s="0" t="s">
+      <c r="K284" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L284" s="0" t="s">
+      <c r="L284" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12757,10 +12756,10 @@
       <c r="J285" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K285" s="0" t="s">
+      <c r="K285" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L285" s="0" t="s">
+      <c r="L285" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12792,10 +12791,10 @@
       <c r="J286" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K286" s="0" t="s">
+      <c r="K286" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L286" s="0" t="s">
+      <c r="L286" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -12827,10 +12826,10 @@
       <c r="J287" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K287" s="0" t="s">
+      <c r="K287" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L287" s="0" t="s">
+      <c r="L287" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -12862,10 +12861,10 @@
       <c r="J288" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K288" s="0" t="s">
+      <c r="K288" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L288" s="0" t="s">
+      <c r="L288" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12897,10 +12896,10 @@
       <c r="J289" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K289" s="0" t="s">
+      <c r="K289" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L289" s="0" t="s">
+      <c r="L289" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12932,10 +12931,10 @@
       <c r="J290" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K290" s="0" t="s">
+      <c r="K290" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L290" s="0" t="s">
+      <c r="L290" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -12967,10 +12966,10 @@
       <c r="J291" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K291" s="0" t="s">
+      <c r="K291" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L291" s="0" t="s">
+      <c r="L291" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -13002,10 +13001,10 @@
       <c r="J292" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K292" s="0" t="s">
+      <c r="K292" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L292" s="0" t="s">
+      <c r="L292" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13037,10 +13036,10 @@
       <c r="J293" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K293" s="0" t="s">
+      <c r="K293" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L293" s="0" t="s">
+      <c r="L293" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13072,10 +13071,10 @@
       <c r="J294" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K294" s="0" t="s">
+      <c r="K294" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L294" s="0" t="s">
+      <c r="L294" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13107,10 +13106,10 @@
       <c r="J295" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K295" s="0" t="s">
+      <c r="K295" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L295" s="0" t="s">
+      <c r="L295" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13142,10 +13141,10 @@
       <c r="J296" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K296" s="0" t="s">
+      <c r="K296" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L296" s="0" t="s">
+      <c r="L296" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13177,10 +13176,10 @@
       <c r="J297" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K297" s="0" t="s">
+      <c r="K297" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L297" s="0" t="s">
+      <c r="L297" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13212,10 +13211,10 @@
       <c r="J298" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K298" s="0" t="s">
+      <c r="K298" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L298" s="0" t="s">
+      <c r="L298" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13247,10 +13246,10 @@
       <c r="J299" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K299" s="0" t="s">
+      <c r="K299" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L299" s="0" t="s">
+      <c r="L299" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13282,10 +13281,10 @@
       <c r="J300" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K300" s="0" t="s">
+      <c r="K300" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L300" s="0" t="s">
+      <c r="L300" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13317,10 +13316,10 @@
       <c r="J301" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K301" s="0" t="s">
+      <c r="K301" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L301" s="0" t="s">
+      <c r="L301" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13352,10 +13351,10 @@
       <c r="J302" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K302" s="0" t="s">
+      <c r="K302" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L302" s="0" t="s">
+      <c r="L302" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13387,10 +13386,10 @@
       <c r="J303" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K303" s="0" t="s">
+      <c r="K303" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L303" s="0" t="s">
+      <c r="L303" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13422,10 +13421,10 @@
       <c r="J304" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K304" s="0" t="s">
+      <c r="K304" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L304" s="0" t="s">
+      <c r="L304" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -13457,10 +13456,10 @@
       <c r="J305" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K305" s="0" t="s">
+      <c r="K305" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L305" s="0" t="s">
+      <c r="L305" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -13492,10 +13491,10 @@
       <c r="J306" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="K306" s="0" t="s">
+      <c r="K306" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L306" s="0" t="s">
+      <c r="L306" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -13527,10 +13526,10 @@
       <c r="J307" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K307" s="0" t="s">
+      <c r="K307" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L307" s="0" t="s">
+      <c r="L307" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13562,10 +13561,10 @@
       <c r="J308" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K308" s="0" t="s">
+      <c r="K308" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L308" s="0" t="s">
+      <c r="L308" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13597,10 +13596,10 @@
       <c r="J309" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K309" s="0" t="s">
+      <c r="K309" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L309" s="0" t="s">
+      <c r="L309" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13632,10 +13631,10 @@
       <c r="J310" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K310" s="0" t="s">
+      <c r="K310" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L310" s="0" t="s">
+      <c r="L310" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13667,10 +13666,10 @@
       <c r="J311" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K311" s="0" t="s">
+      <c r="K311" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L311" s="0" t="s">
+      <c r="L311" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13702,10 +13701,10 @@
       <c r="J312" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K312" s="0" t="s">
+      <c r="K312" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L312" s="0" t="s">
+      <c r="L312" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13737,10 +13736,10 @@
       <c r="J313" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K313" s="0" t="s">
+      <c r="K313" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L313" s="0" t="s">
+      <c r="L313" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13772,10 +13771,10 @@
       <c r="J314" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K314" s="0" t="s">
+      <c r="K314" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L314" s="0" t="s">
+      <c r="L314" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13807,10 +13806,10 @@
       <c r="J315" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K315" s="0" t="s">
+      <c r="K315" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L315" s="0" t="s">
+      <c r="L315" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13842,10 +13841,10 @@
       <c r="J316" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K316" s="0" t="s">
+      <c r="K316" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L316" s="0" t="s">
+      <c r="L316" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13877,10 +13876,10 @@
       <c r="J317" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K317" s="0" t="s">
+      <c r="K317" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L317" s="0" t="s">
+      <c r="L317" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13912,10 +13911,10 @@
       <c r="J318" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K318" s="0" t="s">
+      <c r="K318" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L318" s="0" t="s">
+      <c r="L318" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13947,10 +13946,10 @@
       <c r="J319" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K319" s="0" t="s">
+      <c r="K319" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L319" s="0" t="s">
+      <c r="L319" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -13982,10 +13981,10 @@
       <c r="J320" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K320" s="0" t="s">
+      <c r="K320" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L320" s="0" t="s">
+      <c r="L320" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -14017,10 +14016,10 @@
       <c r="J321" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="K321" s="0" t="s">
+      <c r="K321" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L321" s="0" t="s">
+      <c r="L321" s="1" t="s">
         <v>230</v>
       </c>
     </row>
@@ -14052,10 +14051,10 @@
       <c r="J322" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K322" s="0" t="s">
+      <c r="K322" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L322" s="0" t="s">
+      <c r="L322" s="1" t="s">
         <v>285</v>
       </c>
     </row>
@@ -14087,10 +14086,10 @@
       <c r="J323" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K323" s="0" t="s">
+      <c r="K323" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L323" s="0" t="s">
+      <c r="L323" s="1" t="s">
         <v>285</v>
       </c>
     </row>
@@ -14122,10 +14121,10 @@
       <c r="J324" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K324" s="0" t="s">
+      <c r="K324" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L324" s="0" t="s">
+      <c r="L324" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14157,10 +14156,10 @@
       <c r="J325" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K325" s="0" t="s">
+      <c r="K325" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L325" s="0" t="s">
+      <c r="L325" s="1" t="s">
         <v>285</v>
       </c>
     </row>
@@ -14192,10 +14191,10 @@
       <c r="J326" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K326" s="0" t="s">
+      <c r="K326" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L326" s="0" t="s">
+      <c r="L326" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14227,10 +14226,10 @@
       <c r="J327" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K327" s="0" t="s">
+      <c r="K327" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L327" s="0" t="s">
+      <c r="L327" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14262,10 +14261,10 @@
       <c r="J328" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K328" s="0" t="s">
+      <c r="K328" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L328" s="0" t="s">
+      <c r="L328" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14297,10 +14296,10 @@
       <c r="J329" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K329" s="0" t="s">
+      <c r="K329" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L329" s="0" t="s">
+      <c r="L329" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14332,10 +14331,10 @@
       <c r="J330" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K330" s="0" t="s">
+      <c r="K330" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L330" s="0" t="s">
+      <c r="L330" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -14367,10 +14366,10 @@
       <c r="J331" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K331" s="0" t="s">
+      <c r="K331" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="L331" s="0" t="s">
+      <c r="L331" s="1" t="s">
         <v>280</v>
       </c>
     </row>
@@ -14402,10 +14401,10 @@
       <c r="J332" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="K332" s="0" t="s">
+      <c r="K332" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L332" s="0" t="s">
+      <c r="L332" s="1" t="s">
         <v>285</v>
       </c>
     </row>
@@ -14437,10 +14436,10 @@
       <c r="J333" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K333" s="0" t="s">
+      <c r="K333" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L333" s="0" t="s">
+      <c r="L333" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14472,10 +14471,10 @@
       <c r="J334" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K334" s="0" t="s">
+      <c r="K334" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L334" s="0" t="s">
+      <c r="L334" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14507,10 +14506,10 @@
       <c r="J335" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K335" s="0" t="s">
+      <c r="K335" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="L335" s="0" t="s">
+      <c r="L335" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -14542,10 +14541,10 @@
       <c r="J336" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="K336" s="0" t="s">
+      <c r="K336" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L336" s="0" t="s">
+      <c r="L336" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -14577,10 +14576,10 @@
       <c r="J337" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K337" s="0" t="s">
+      <c r="K337" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L337" s="0" t="s">
+      <c r="L337" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -14612,10 +14611,10 @@
       <c r="J338" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K338" s="0" t="s">
+      <c r="K338" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L338" s="0" t="s">
+      <c r="L338" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -14647,10 +14646,10 @@
       <c r="J339" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K339" s="0" t="s">
+      <c r="K339" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L339" s="0" t="s">
+      <c r="L339" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -14682,10 +14681,10 @@
       <c r="J340" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="K340" s="0" t="s">
+      <c r="K340" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L340" s="0" t="s">
+      <c r="L340" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -14717,10 +14716,10 @@
       <c r="J341" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="K341" s="0" t="s">
+      <c r="K341" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L341" s="0" t="s">
+      <c r="L341" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -14752,10 +14751,10 @@
       <c r="J342" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K342" s="0" t="s">
+      <c r="K342" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L342" s="0" t="s">
+      <c r="L342" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -14787,10 +14786,10 @@
       <c r="J343" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K343" s="0" t="s">
+      <c r="K343" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L343" s="0" t="s">
+      <c r="L343" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -14822,10 +14821,10 @@
       <c r="J344" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="K344" s="0" t="s">
+      <c r="K344" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="L344" s="0" t="s">
+      <c r="L344" s="1" t="s">
         <v>327</v>
       </c>
     </row>
@@ -14857,10 +14856,10 @@
       <c r="J345" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K345" s="0" t="s">
+      <c r="K345" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L345" s="0" t="s">
+      <c r="L345" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -14892,10 +14891,10 @@
       <c r="J346" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K346" s="0" t="s">
+      <c r="K346" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L346" s="0" t="s">
+      <c r="L346" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -14927,10 +14926,10 @@
       <c r="J347" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K347" s="0" t="s">
+      <c r="K347" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L347" s="0" t="s">
+      <c r="L347" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -14962,10 +14961,10 @@
       <c r="J348" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="K348" s="0" t="s">
+      <c r="K348" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L348" s="0" t="s">
+      <c r="L348" s="1" t="s">
         <v>328</v>
       </c>
     </row>
@@ -14997,10 +14996,10 @@
       <c r="J349" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K349" s="0" t="s">
+      <c r="K349" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L349" s="0" t="s">
+      <c r="L349" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15032,10 +15031,10 @@
       <c r="J350" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="K350" s="0" t="s">
+      <c r="K350" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="L350" s="0" t="s">
+      <c r="L350" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15067,7 +15066,7 @@
       <c r="J351" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K351" s="0" t="s">
+      <c r="K351" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -15099,7 +15098,7 @@
       <c r="J352" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K352" s="0" t="s">
+      <c r="K352" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -15131,7 +15130,7 @@
       <c r="J353" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K353" s="0" t="s">
+      <c r="K353" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -15163,7 +15162,7 @@
       <c r="J354" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K354" s="0" t="s">
+      <c r="K354" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -15195,7 +15194,7 @@
       <c r="J355" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K355" s="0" t="s">
+      <c r="K355" s="1" t="s">
         <v>281</v>
       </c>
     </row>
@@ -15227,7 +15226,7 @@
       <c r="J356" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K356" s="0" t="s">
+      <c r="K356" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15259,7 +15258,7 @@
       <c r="J357" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K357" s="0" t="s">
+      <c r="K357" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15291,7 +15290,7 @@
       <c r="J358" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K358" s="0" t="s">
+      <c r="K358" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15323,7 +15322,7 @@
       <c r="J359" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K359" s="0" t="s">
+      <c r="K359" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15355,7 +15354,7 @@
       <c r="J360" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K360" s="0" t="s">
+      <c r="K360" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15387,7 +15386,7 @@
       <c r="J361" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K361" s="0" t="s">
+      <c r="K361" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15419,7 +15418,7 @@
       <c r="J362" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="K362" s="0" t="s">
+      <c r="K362" s="1" t="s">
         <v>229</v>
       </c>
     </row>
@@ -15451,7 +15450,7 @@
       <c r="J363" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K363" s="0" t="s">
+      <c r="K363" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15483,7 +15482,7 @@
       <c r="J364" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K364" s="0" t="s">
+      <c r="K364" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15515,7 +15514,7 @@
       <c r="J365" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K365" s="0" t="s">
+      <c r="K365" s="1" t="s">
         <v>326</v>
       </c>
     </row>
@@ -15547,7 +15546,7 @@
       <c r="J366" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K366" s="0" t="s">
+      <c r="K366" s="1" t="s">
         <v>326</v>
       </c>
     </row>

--- a/question/game_ques.xlsx
+++ b/question/game_ques.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIDDHANT\Desktop\Zendalona\forkedFolder\Maths-Tutor-QT-V2\question\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BECC0CE-1213-4710-A3A0-2DA66B073A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FBD4AF-92F2-4C25-BFA5-BCB242127EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2567" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3298" uniqueCount="1197">
   <si>
     <t>question</t>
   </si>
@@ -2437,13 +2437,1192 @@
   </si>
   <si>
     <t>warmup_order</t>
+  </si>
+  <si>
+    <t>question_mr</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तुला आणखी Rs {y} सापडले. एकूण किती पैसे झाले?</t>
+  </si>
+  <si>
+    <t>एका पेनची किंमत Rs {x} आहे आणि एका खोडरबराची किंमत Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} होते. तू Rs {y} ची गोळी विकत घेतली. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>रियाला Rs {x} चे खेळणे हवे आहे. तिच्याकडे Rs {y} आहेत. तिला अजून किती पैशांची गरज आहे?</t>
+  </si>
+  <si>
+    <t>एका फुग्याची किंमत Rs {x} आहे. {y} फुग्यांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>सफरचंदाची किंमत Rs {x} आहे आणि केळ्याची किंमत Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} होते, त्यापैकी Rs {y} खर्च केले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका पुस्तकाची किंमत Rs {x} आहे. {y} पुस्तके खरेदी केल्यास एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तू Rs {x} वाचवले आणि आणखी Rs {y} मिळाले. एकूण किती झाले?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} होते, त्यापैकी Rs {y} हरवले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका गोळीची किंमत Rs {x} आहे. {y} गोळ्यांची एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>शर्टची किंमत Rs {x} आहे आणि टोपीची किंमत Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तू Rs {y} चा पेन विकत घेतलास. किती पैसे परत मिळतील?</t>
+  </si>
+  <si>
+    <t>Rs {y} प्रति पेन दराने {x} पेनांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>आईकडून Rs {x} आणि बाबांकडून Rs {y} मिळाले. एकूण किती पैसे मिळाले?</t>
+  </si>
+  <si>
+    <t>एका मांजरीने {x} उंदीर पकडले. दुसऱ्या मांजरीने {y} उंदीर पकडले. एकूण किती उंदीर पकडले गेले?</t>
+  </si>
+  <si>
+    <t>एका झाडावर {x} सफरचंदे आहेत. त्यापैकी {y} खाली पडली. किती सफरचंदे उरली?</t>
+  </si>
+  <si>
+    <t>सॅमकडे {x} खोकी आहेत. प्रत्येक खोक्यात {y} पेन आहेत. एकूण किती पेन आहेत?</t>
+  </si>
+  <si>
+    <t>{x} मुलांना {y} समान संघांमध्ये विभागले. प्रत्येक संघात किती मुले असतील?</t>
+  </si>
+  <si>
+    <t>एका मांजरीकडे {x} खेळणी आहेत. तिला आणखी {y} मिळाली. आता तिच्याकडे एकूण किती खेळणी आहेत?</t>
+  </si>
+  <si>
+    <t>सॅमने {x} पाने वाचली आणि नंतर आणखी {y} पाने वाचली. एकूण किती पाने वाचली?</t>
+  </si>
+  <si>
+    <t>झाडावर {x} पक्षी आहेत. त्यापैकी {y} उडून गेले. किती पक्षी उरले?</t>
+  </si>
+  <si>
+    <t>एका मुलाकडे {x} फुगे होते. त्यापैकी {y} फुटले. किती फुगे उरले?</t>
+  </si>
+  <si>
+    <t>{x} मांजरींचे {y} पाय प्रत्येकी आहेत. एकूण किती पाय आहेत?</t>
+  </si>
+  <si>
+    <t>{x} खोकी आहेत. प्रत्येकात {y} पेन आहेत. एकूण किती पेन आहेत?</t>
+  </si>
+  <si>
+    <t>{x} गोळ्या {y} मुलांमध्ये वाटल्या. प्रत्येक मुलाला किती गोळ्या मिळतील?</t>
+  </si>
+  <si>
+    <t>{x} पिझ्झाचे तुकडे {y} लोकांसाठी आहेत. प्रत्येकाला किती तुकडे मिळतील?</t>
+  </si>
+  <si>
+    <t>{x} पेन {y} च्या खोक्यांमध्ये भरले. किती पेन शिल्लक राहतील?</t>
+  </si>
+  <si>
+    <t>{x} विद्यार्थ्यांना {y} च्या गटांमध्ये विभागले. किती विद्यार्थी गटाबाहेर राहतील?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे खेळतोस आणि {y} मिनिटे विश्रांती घेतोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>खेळ {x} मिनिटांचा आहे. त्यापैकी {y} मिनिटे झाली. किती मिनिटे शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>तू {x} तास झोपलास आणि {y} तास डुलकी घेतलीस. एकूण किती तास झोप झाली?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे अभ्यास करतोस आणि {y} मिनिटे विश्रांती घेतोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>चित्रपट {x} मिनिटांचा आहे. त्यापैकी {y} मिनिटे पाहिली. किती मिनिटे उरली?</t>
+  </si>
+  <si>
+    <t>तू {x} तास काम करतोस आणि {y} तास खेळतोस. एकूण किती तास?</t>
+  </si>
+  <si>
+    <t>तू {x} तास वाहन चालवतोस आणि {y} तास चालतोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>वर्ग {x} मिनिटांचा आहे. त्यापैकी {y} मिनिटे झाली. किती वेळ शिल्लक आहे?</t>
+  </si>
+  <si>
+    <t>गाणे {x} सेकंदांचे आहे. त्यापैकी {y} सेकंद वाजले. किती सेकंद उरले?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे बेक करतोस आणि {y} मिनिटे थंड होऊ देतोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>उड्डाण {x} तासांचे आहे. त्यापैकी {y} तास झाले. किती तास उरले?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे वाचतोस आणि {y} मिनिटे लिहितोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे थांबलास आणि नंतर आणखी {y} मिनिटे थांबलास. एकूण प्रतीक्षा वेळ किती?</t>
+  </si>
+  <si>
+    <t>शर्यत {x} मिनिटांची आहे. त्यापैकी {y} मिनिटे झाली. किती मिनिटे शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>आज {x} तास आणि उद्या {y} तास. एकूण किती तास?</t>
+  </si>
+  <si>
+    <t>एका वहीची किंमत Rs {x} आहे. तू {y} वह्या खरेदी केल्या. एकूण बिल किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तू खाऊसाठी Rs {y} खर्च केले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>गेल्या आठवड्यात Rs {x} वाचवले आणि या आठवड्यात Rs {y} वाचवले. एकूण बचत किती?</t>
+  </si>
+  <si>
+    <t>एका चॉकलेट बॉक्सची किंमत Rs {x} आहे. {y} बॉक्सची किंमत किती?</t>
+  </si>
+  <si>
+    <t>Rs {x} ची वस्तू घेतली आणि Rs {y} ची नोट दिली. किती पैसे परत मिळतील?</t>
+  </si>
+  <si>
+    <t>शर्टची किंमत Rs {x} आहे. पँटची किंमत Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} होते. तू तुझ्या भावाला Rs {y} दिले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका चित्रपटाच्या तिकिटाची किंमत Rs {x} आहे. {y} तिकिटांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>एकूण बिल Rs {x} आहे. तुला Rs {y} ची सूट मिळाली. किती पैसे द्यावे लागतील?</t>
+  </si>
+  <si>
+    <t>तू Rs {x} ची फळे आणि Rs {y} च्या भाज्या विकत घेतल्या. एकूण खर्च किती?</t>
+  </si>
+  <si>
+    <t>तू आज Rs {x} आणि काल Rs {y} कमावले. एकूण कमाई किती?</t>
+  </si>
+  <si>
+    <t>एका खेळण्याच्या गाडीची किंमत Rs {x} आहे. तू {y} गाड्या खरेदी केल्या. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तुला खेळासाठी Rs {x} लागतात. तुझ्याकडे Rs {y} आहेत. अजून किती कमी आहेत?</t>
+  </si>
+  <si>
+    <t>जेवणाची किंमत Rs {x} आहे. तू Rs {y} टिप दिलीस. एकूण किती खर्च झाला?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तू पुस्तकांवर Rs {y} खर्च केले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका बेकरने {x} केक बनवले आणि {y} विकले. किती केक उरले?</t>
+  </si>
+  <si>
+    <t>एक रेल्वे {x} किमी प्रवास करते, नंतर आणखी {y} किमी प्रवास करते. एकूण अंतर किती?</t>
+  </si>
+  <si>
+    <t>एका पुस्तकाची किंमत ${x} आहे. {y} पुस्तकांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>एका दुकानात {x} सफरचंदे आणि {y} संत्री विकली जातात. एकूण फळे किती?</t>
+  </si>
+  <si>
+    <t>एका संघाने {x} गुण मिळवले, नंतर {y} गुण मिळवले. एकूण गुण किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे ${x} आहेत. तू ${y} खर्च केले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका आठवड्यात {x} दिवस असतात. {y} आठवड्यांत किती दिवस असतात?</t>
+  </si>
+  <si>
+    <t>{x} गाड्यांना प्रत्येकी {y} चाके आहेत. एकूण किती चाके?</t>
+  </si>
+  <si>
+    <t>{x} विद्यार्थ्यांना {y} संघांमध्ये विभागले. प्रत्येक संघात किती विद्यार्थी?</t>
+  </si>
+  <si>
+    <t>{x} दिवसांचा प्रवास {y} शहरांमध्ये विभागला. प्रत्येक शहरासाठी किती दिवस?</t>
+  </si>
+  <si>
+    <t>{x} नाणी {y} चाच्यांमध्ये वाटली. किती नाणी शिल्लक राहतील?</t>
+  </si>
+  <si>
+    <t>{x} चॉकलेट्स {y} मित्रांना दिली. किती चॉकलेट्स उरली?</t>
+  </si>
+  <si>
+    <t>{x} पत्ते {y} खेळाडूंना वाटले. पत्त्यांच्या संचात किती पत्ते उरले?</t>
+  </si>
+  <si>
+    <t>{x} तासांत किती मिनिटे असतात?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे चाललास आणि {y} मिनिटे धावलास. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>{x} दिवसांत किती तास असतात?</t>
+  </si>
+  <si>
+    <t>तू दररोज {x} मिनिटे अभ्यास करतोस. {y} दिवसांत एकूण किती मिनिटे अभ्यास होईल?</t>
+  </si>
+  <si>
+    <t>उड्डाण {x} मिनिटांचे आहे. त्यापैकी {y} मिनिटे झाली. किती मिनिटे उरली?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे {x} मिनिटे आहेत. कामाला {y} मिनिटे लागतात. किती मोकळा वेळ उरेल?</t>
+  </si>
+  <si>
+    <t>{x} आठवड्यांत किती दिवस असतात?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे खेळलास आणि {y} मिनिटे विश्रांती घेतलीस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>रेल्वेचा प्रवास {x} मिनिटांचा आहे. ती {y} मिनिटे उशिरा आहे. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>तू दररोज {x} तास झोपतोस. {y} रात्रींमध्ये एकूण किती तास झोप होईल?</t>
+  </si>
+  <si>
+    <t>व्यायाम {x} मिनिटांचा आहे. त्यापैकी {y} मिनिटे पूर्ण झाली. किती मिनिटे उरली?</t>
+  </si>
+  <si>
+    <t>{x} तास काम आणि {y} तास विश्रांती. एकूण किती तास?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे स्वयंपाक करतोस आणि {y} मिनिटे जेवतोस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>एका तांदळाच्या पिशवीची किंमत Rs {x} आहे. {y} पिशव्यांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>Rs {x} हे {y} मित्रांमध्ये समान वाटा. प्रत्येकाला किती रक्कम मिळेल?</t>
+  </si>
+  <si>
+    <t>एका जॅकेटची किंमत Rs {x} आहे. सूट Rs {y} आहे. अंतिम किंमत किती?</t>
+  </si>
+  <si>
+    <t>बिल Rs {x} आहे. तू Rs {y} भरले. अजून किती रक्कम द्यायची आहे?</t>
+  </si>
+  <si>
+    <t>तू Rs {x} आणि Rs {y} किमतीच्या वस्तू खरेदी केल्या. एकूण खर्च किती?</t>
+  </si>
+  <si>
+    <t>एका तिकिटाची किंमत Rs {x} आहे. {y} तिकिटांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>Rs {y} च्या वस्तूसाठी Rs {x} ची नोट दिली. किती पैसे परत मिळतील?</t>
+  </si>
+  <si>
+    <t>जानेवारीत Rs {x} आणि फेब्रुवारीत Rs {y} वाचवले. एकूण बचत किती?</t>
+  </si>
+  <si>
+    <t>Rs {x} हे {y} समान महिन्यांसाठी द्यायचे आहेत. दर महिन्याला किती रक्कम?</t>
+  </si>
+  <si>
+    <t>दररोज Rs {x} कमावतो. {y} दिवसांत एकूण कमाई किती?</t>
+  </si>
+  <si>
+    <t>बँक शिल्लक Rs {x} आहे. Rs {y} काढले. किती शिल्लक राहिले?</t>
+  </si>
+  <si>
+    <t>वीज बिल Rs {x} आणि पाणी बिल Rs {y} आहे. एकूण बिल किती?</t>
+  </si>
+  <si>
+    <t>एका पिझ्झाची किंमत Rs {x} आहे. {y} पिझ्झांची एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>सायकलसाठी Rs {x} लागतात. तुझ्याकडे Rs {y} आहेत. अजून किती पैसे हवेत?</t>
+  </si>
+  <si>
+    <t>Rs {x} देऊन {y} पेन खरेदी केले. एका पेनची किंमत किती?</t>
+  </si>
+  <si>
+    <t>एका शहरात {x} घरे आहेत. आणखी {y} नवीन घरे बांधली गेली. एकूण घरे किती?</t>
+  </si>
+  <si>
+    <t>एका कारखान्याने {x} खेळणी बनवली, पण {y} तुटली. चांगली खेळणी किती उरली?</t>
+  </si>
+  <si>
+    <t>एका ग्रंथालयात {x} कपाटे आहेत. प्रत्येक कपाटात {y} पुस्तके आहेत. एकूण पुस्तके किती?</t>
+  </si>
+  <si>
+    <t>{x} सफरचंदे {y} खोकेमध्ये समान वाटली. प्रत्येक खोक्यात किती सफरचंदे?</t>
+  </si>
+  <si>
+    <t>खेळ {x} मिनिटांचा आहे. त्यापैकी {y} मिनिटे झाली. किती मिनिटे उरली?</t>
+  </si>
+  <si>
+    <t>तू Rs ${x} चा शर्ट आणि Rs ${y} ची पँट विकत घेतली. एकूण खर्च किती?</t>
+  </si>
+  <si>
+    <t>तू ${x} वाचवले आणि ${y} सापडले. एकूण किती पैसे झाले?</t>
+  </si>
+  <si>
+    <t>एका शेतात {x} गायी आणि {y} घोडे आहेत. एकूण प्राणी किती?</t>
+  </si>
+  <si>
+    <t>एका पुस्तकात {x} पाने आहेत. तू {y} पाने वाचली. किती पाने उरली?</t>
+  </si>
+  <si>
+    <t>एका बरणीत {x} कुकीज आहेत. त्यापैकी {y} खाल्ल्या गेल्या. किती कुकीज उरल्या?</t>
+  </si>
+  <si>
+    <t>एका पुस्तकात {x} प्रकरणे आहेत. प्रत्येक प्रकरणात {y} पाने आहेत. एकूण किती पाने?</t>
+  </si>
+  <si>
+    <t>तू प्रत्येकी ${y} किंमतीची {x} तिकिटे खरेदी केली. एकूण खर्च किती?</t>
+  </si>
+  <si>
+    <t>{x} पुस्तके {y} कपाटांमध्ये ठेवली. प्रत्येक कपाटात किती पुस्तके?</t>
+  </si>
+  <si>
+    <t>{x} अंडी {y} च्या ट्रेमध्ये भरली. किती अंडी शिल्लक राहतील?</t>
+  </si>
+  <si>
+    <t>{x} पाहुणे {y} आसनांच्या टेबलांवर बसले. किती पाहुणे उभे राहतील?</t>
+  </si>
+  <si>
+    <t>{x} मिनिटांत किती सेकंद असतात?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे थांबलास, नंतर आणखी {y} मिनिटे थांबलास. एकूण प्रतीक्षा वेळ किती?</t>
+  </si>
+  <si>
+    <t>तू दर आठवड्याला {x} तास झोपतोस. {y} आठवड्यांत एकूण किती तास झोप होईल?</t>
+  </si>
+  <si>
+    <t>चित्रपट {x} मिनिटांचा आहे. {y} मिनिटे थांबवला होता. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>तू {x} तास प्रवास केलास आणि {y} तास थांबलास. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे काम केले. त्यापैकी {y} मिनिटे पूर्ण झाली. किती मिनिटे शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>{x} महिन्यांत किती दिवस असतात? (प्रत्येक महिना 30 दिवसांचा धरून)</t>
+  </si>
+  <si>
+    <t>{x} तास {y} कामांमध्ये विभागले. प्रत्येक कामासाठी किती तास?</t>
+  </si>
+  <si>
+    <t>प्रवास {x} दिवसांचा आहे. त्यापैकी {y} दिवस झाले. किती दिवस शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>{x} मिनिटे {y} सत्रांमध्ये विभागली. प्रत्येक सत्र किती मिनिटांचे?</t>
+  </si>
+  <si>
+    <t>प्रकल्पासाठी {x} तास आहेत. त्यापैकी {y} तास पूर्ण झाले. किती तास शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>तू दररोज {x} मिनिटे खेळतोस. {y} दिवसांत एकूण किती मिनिटे खेळशील?</t>
+  </si>
+  <si>
+    <t>अभ्यासक्रम {x} आठवड्यांचा आहे. त्यापैकी {y} आठवडे पूर्ण झाले. किती आठवडे शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>व्हिडिओ {x} सेकंदांचा आहे. त्यापैकी {y} सेकंद पाहिले. किती सेकंद उरले?</t>
+  </si>
+  <si>
+    <t>पगार Rs {x} आहे. त्यातील {y}% वाचवले. किती रक्कम वाचवली?</t>
+  </si>
+  <si>
+    <t>टीव्हीची किंमत Rs {x} आहे. ती {y} समान हप्त्यांमध्ये भरायची आहे. दर हप्ता किती?</t>
+  </si>
+  <si>
+    <t>Rs {x} गुंतवले आणि Rs {y} नफा झाला. एकूण रक्कम किती?</t>
+  </si>
+  <si>
+    <t>बजेट Rs {x} आहे. भाड्यावर Rs {y} खर्च केले. किती निधी उरला?</t>
+  </si>
+  <si>
+    <t>Rs {x} चे कर्ज {y} भागीदारांमध्ये विभागले. प्रत्येकाचा वाटा किती?</t>
+  </si>
+  <si>
+    <t>लॅपटॉपची किंमत Rs {x} आहे. कर Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>एका फोनची किंमत Rs {x} आहे. {y} फोनांची किंमत किती?</t>
+  </si>
+  <si>
+    <t>जेवणाचे बिल Rs {x} आहे. ते {y} लोकांमध्ये समान विभागले. प्रत्येकाने किती पैसे द्यायचे?</t>
+  </si>
+  <si>
+    <t>भाडे Rs {x} प्रति महिना आहे. {y} महिन्यांचे एकूण भाडे किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तू Rs {y} चे विमान तिकीट विकत घेतले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>तू दर महिन्याला Rs {x} कमावतोस. {y} महिन्यांत एकूण कमाई किती?</t>
+  </si>
+  <si>
+    <t>गाडीची किंमत Rs {x} आहे. विक्रेत्याने Rs {y} ची सूट दिली. अंतिम किंमत किती?</t>
+  </si>
+  <si>
+    <t>Rs {x} चे बक्षीस {y} विजेत्यांमध्ये समान वाटले. प्रत्येकाला किती मिळेल?</t>
+  </si>
+  <si>
+    <t>1 किलो सोन्याची किंमत Rs {x} आहे. {y} किलो सोन्याची किंमत किती?</t>
+  </si>
+  <si>
+    <t>कंपनी A चे उत्पन्न Rs {x} आहे. कंपनी B चे उत्पन्न Rs {y} आहे. एकूण उत्पन्न किती?</t>
+  </si>
+  <si>
+    <t>विमानाने {x} मैल प्रवास केला, नंतर आणखी {y} मैल प्रवास केला. एकूण किती मैल?</t>
+  </si>
+  <si>
+    <t>एका टाकीत {x} लिटर पाणी आहे. त्यापैकी {y} लिटर वापरले. किती लिटर उरले?</t>
+  </si>
+  <si>
+    <t>एका स्टेडियममध्ये {x} रांगा आहेत. प्रत्येक रांगेत {y} आसने आहेत. एकूण किती आसने?</t>
+  </si>
+  <si>
+    <t>{x} डॉलर {y} विजेत्यांमध्ये समान वाटले. प्रत्येक विजेत्याला किती डॉलर मिळतील?</t>
+  </si>
+  <si>
+    <t>एका रेल्वेत {x} पुरुष आणि {y} महिला आहेत. एकूण किती लोक आहेत?</t>
+  </si>
+  <si>
+    <t>तू {x} मीटर चाललास आणि {y} मीटर धावलास. एकूण अंतर किती?</t>
+  </si>
+  <si>
+    <t>एका ग्रंथालयात {x} पुस्तके आहेत. त्यापैकी {y} पुस्तके उधार दिली गेली. किती पुस्तके उरली?</t>
+  </si>
+  <si>
+    <t>एका दुकानात {x} शर्ट होते. त्यापैकी {y} विकले गेले. किती शर्ट उरले?</t>
+  </si>
+  <si>
+    <t>एका इमारतीत {x} मजले आहेत. प्रत्येक मजल्यावर {y} खोल्या आहेत. एकूण किती खोल्या?</t>
+  </si>
+  <si>
+    <t>एका शेतात {x} रांगा आहेत. प्रत्येक रांगेत {y} झाडे आहेत. एकूण किती झाडे?</t>
+  </si>
+  <si>
+    <t>${x} हे {y} मित्रांमध्ये समान वाटले. प्रत्येक मित्राला किती डॉलर मिळतील?</t>
+  </si>
+  <si>
+    <t>{x} मीटर लांबीची दोरी {y} समान तुकड्यांमध्ये कापली. प्रत्येक तुकड्याची लांबी किती?</t>
+  </si>
+  <si>
+    <t>{x} पत्रके {y} च्या गटांमध्ये बांधली. किती पत्रके शिल्लक राहतील?</t>
+  </si>
+  <si>
+    <t>{x} लिटर रस {y} लिटरच्या बाटल्यांमध्ये भरला. किती रस शिल्लक राहील?</t>
+  </si>
+  <si>
+    <t>{x} दिवसांत किती मिनिटे असतात? ({y} ने गुणा करा)</t>
+  </si>
+  <si>
+    <t>उड्डाणाला {x} तास लागतात. ते किती मिनिटे होतात?</t>
+  </si>
+  <si>
+    <t>तू दररोज {x} मिनिटे काम केले. {y} दिवसांत एकूण किती मिनिटे काम केले?</t>
+  </si>
+  <si>
+    <t>वर्षात {x} दिवस आहेत. ते किती तास होतात? ({y} ने गुणा करा)</t>
+  </si>
+  <si>
+    <t>बॅटरी {x} तास चालते. त्यापैकी {y} तास वापरले. किती तास शिल्लक आहेत?</t>
+  </si>
+  <si>
+    <t>एकूण {x} मिनिटे {y} कामांमध्ये समान वाटली. प्रत्येक कामासाठी किती मिनिटे?</t>
+  </si>
+  <si>
+    <t>तू {x} मिनिटे अभ्यास केलास आणि {y} मिनिटे विश्रांती घेतलीस. एकूण वेळ किती?</t>
+  </si>
+  <si>
+    <t>प्रकल्पाला {x} आठवडे लागतात. ते किती दिवस होतात?</t>
+  </si>
+  <si>
+    <t>{x} सेकंद म्हणजे किती मिनिटे?</t>
+  </si>
+  <si>
+    <t>तू {x} महिने जगला आहेस. ते किती वर्षे होतात?</t>
+  </si>
+  <si>
+    <t>कार्यक्रम {x} तासांचा आहे. त्यापैकी {y} तास झाले. किती तास उरले?</t>
+  </si>
+  <si>
+    <t>सुट्टी {x} दिवसांची आहे. त्यापैकी {y} दिवस प्रवासात गेले. किती दिवस उरले?</t>
+  </si>
+  <si>
+    <t>तू दररोज {x} मिनिटे वाचवतोस. {y} दिवसांत एकूण किती मिनिटे वाचवशील?</t>
+  </si>
+  <si>
+    <t>तू प्रत्येक प्रवासात {x} मिनिटे वाहन चालवतोस. {y} प्रवासांत एकूण किती मिनिटे?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे {x} तास संगीत आहे. त्यापैकी {y} तास ऐकले. किती तास उरले?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे {x} सफरचंदे आहेत. तू {y} खाल्लीस. किती सफरचंदे उरली?</t>
+  </si>
+  <si>
+    <t>एका कुत्र्याकडे {x} हाडे आहेत. त्याला आणखी {y} हाडे सापडली. एकूण किती हाडे?</t>
+  </si>
+  <si>
+    <t>{x} पक्षी कुंपणावर बसले आहेत. आणखी {y} पक्षी आले. एकूण किती पक्षी?</t>
+  </si>
+  <si>
+    <t>तू {x} गोल केले. तुझ्या मित्राने {y} गोल केले. एकूण किती गोल?</t>
+  </si>
+  <si>
+    <t>{x} बेडूक आहेत. त्यापैकी {y} उड्या मारून निघून गेले. किती बेडूक उरले?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} आहेत. तू Rs {y} खर्च केले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>एका पेनची किंमत Rs {x} आहे. एका पेन्सिलची किंमत Rs {y} आहे. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>तू आज Rs {x} कमावले आणि उद्या Rs {y} कमावशील. एकूण किती कमाई?</t>
+  </si>
+  <si>
+    <t>एका टॉफीची किंमत Rs {x} आहे. तू {y} टॉफ्या विकत घेतल्या. एकूण किंमत किती?</t>
+  </si>
+  <si>
+    <t>एका बिस्किटाची किंमत Rs {x} आहे. तू {y} बिस्किटे विकत घेतली. एकूण किती पैसे दिले?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे Rs {x} होते. तू मित्राला Rs {y} दिले. किती पैसे उरले?</t>
+  </si>
+  <si>
+    <t>तू {x} तास झोपलास. नंतर आणखी {y} तास झोपलास. एकूण किती तास झोप झाली?</t>
+  </si>
+  <si>
+    <t>वर्ग {x} तासांचा आहे. त्यापैकी {y} तास झाले. किती तास उरले?</t>
+  </si>
+  <si>
+    <t>तू शाळेत जाण्यासाठी {x} मिनिटे चाललास आणि परत येण्यासाठी {y} मिनिटे चाललास. एकूण चालण्याचा वेळ किती?</t>
+  </si>
+  <si>
+    <t>तुझ्याकडे {x} तास मोकळा वेळ आहे. त्यापैकी {y} तास खेळांसाठी वापरले. किती तास उरले?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. നിങ്ങൾക്ക് കൂടി Rs {y} കിട്ടി. ആകെ എത്ര പണം?</t>
+  </si>
+  <si>
+    <t>ഒരു പേനയുടെ വില Rs {x}, ഒരു ഇറേസറിന്റെ വില Rs {y}. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ടായിരുന്നു. Rs {y} വിലയുള്ള മിഠായി വാങ്ങി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>റിയയ്ക്ക് Rs {x} വിലയുള്ള ഒരു കളിപ്പാട്ടം വേണം. അവൾക്ക് Rs {y} ഉണ്ട്. ഇനി എത്ര രൂപ വേണം?</t>
+  </si>
+  <si>
+    <t>ഒരു ബലൂണിന്റെ വില Rs {x} ആണ്. {y} ബലൂണുകളുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ആപ്പിളിന്റെ വില Rs {x}, ഒരു വാഴപ്പഴത്തിന്റെ വില Rs {y}. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ടായിരുന്നു, അതിൽ Rs {y} ചെലവാക്കി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു പുസ്തകത്തിന്റെ വില Rs {x} ആണ്. {y} പുസ്തകങ്ങളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ Rs {x} സേവ് ചെയ്തു, പിന്നെ കൂടി Rs {y} ലഭിച്ചു. ആകെ എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ടായിരുന്നു. അതിൽ Rs {y} നഷ്ടപ്പെട്ടു. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു മിഠായിയുടെ വില Rs {x} ആണ്. {y} മിഠായികളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ഷർട്ടിന്റെ വില Rs {x}, ഒരു തൊപ്പിയുടെ വില Rs {y}. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. Rs {y} വിലയുള്ള ഒരു പേന വാങ്ങി. എത്ര രൂപ തിരികെ കിട്ടും?</t>
+  </si>
+  <si>
+    <t>ഒന്നിന് Rs {y} വിലയുള്ള {x} പേനകളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>അമ്മയിൽ നിന്ന് Rs {x}, അച്ഛനിൽ നിന്ന് Rs {y} ലഭിച്ചു. ആകെ എത്ര രൂപ ലഭിച്ചു?</t>
+  </si>
+  <si>
+    <t>ഒരു പൂച്ച {x} എലികളെ പിടിച്ചു. മറ്റൊരു പൂച്ച {y} എലികളെ കൂടി പിടിച്ചു. ആകെ എത്ര എലികൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു മരത്തിൽ {x} ആപ്പിളുകൾ ഉണ്ട്. അതിൽ {y} എണ്ണം വീണുപോയി. എത്ര ആപ്പിളുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>സാമിന് {x} പെട്ടികളുണ്ട്. ഓരോന്നിലും {y} പേനകളുണ്ട്. ആകെ എത്ര പേനകൾ?</t>
+  </si>
+  <si>
+    <t>{x} കുട്ടികളെ {y} തുല്യ ടീമുകളായി വിഭജിച്ചു. ഓരോ ടീമിലും എത്ര കുട്ടികൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു പൂച്ചയ്ക്ക് {x} കളിപ്പാട്ടങ്ങൾ ഉണ്ട്. അതിന് കൂടി {y} ലഭിച്ചു. ഇപ്പോൾ ആകെ എത്ര കളിപ്പാട്ടങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>സാം {x} പേജുകൾ വായിച്ചു, തുടർന്ന് {y} പേജുകൾ കൂടി വായിച്ചു. ആകെ എത്ര പേജുകൾ വായിച്ചു?</t>
+  </si>
+  <si>
+    <t>ഒരു മരത്തിൽ {x} പക്ഷികളുണ്ട്. അതിൽ {y} എണ്ണം പറന്നുപോയി. എത്ര പക്ഷികൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ബാലന് {x} ബലൂണുകൾ ഉണ്ടായിരുന്നു. അതിൽ {y} എണ്ണം പൊട്ടി. എത്ര ബലൂണുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} പൂച്ചകൾക്ക് ഓരോന്നിനും {y} കാലുകൾ വീതം ഉണ്ട്. ആകെ എത്ര കാലുകൾ?</t>
+  </si>
+  <si>
+    <t>{x} പെട്ടികളിൽ ഓരോന്നിലും {y} പേനകളുണ്ട്. ആകെ എത്ര പേനകൾ?</t>
+  </si>
+  <si>
+    <t>{x} മിഠായികൾ {y} കുട്ടികൾക്ക് പങ്കിട്ടു. ഓരോ കുട്ടിക്കും എത്ര മിഠായികൾ?</t>
+  </si>
+  <si>
+    <t>{x} പിസ്സ കഷണങ്ങൾ {y} ആളുകൾക്കായി ഉണ്ട്. ഓരോരുത്തർക്കും എത്ര കഷണങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>{x} പേനകൾ {y} വീതമുള്ള പെട്ടികളിൽ പായ്ക്ക് ചെയ്തു. എത്ര പേനകൾ ശേഷിക്കും?</t>
+  </si>
+  <si>
+    <t>{x} വിദ്യാർത്ഥികളെ {y} പേരടങ്ങുന്ന ഗ്രൂപ്പുകളാക്കി. എത്ര വിദ്യാർത്ഥികൾ ശേഷിക്കും?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് കളിക്കുകയും {y} മിനിറ്റ് വിശ്രമിക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു കളി {x} മിനിറ്റ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മിനിറ്റ് കഴിഞ്ഞു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മണിക്കൂർ ഉറങ്ങി, തുടർന്ന് {y} മണിക്കൂർ കൂടി ഉറങ്ങി. ആകെ എത്ര മണിക്കൂർ ഉറക്കം?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് പഠിക്കുകയും {y} മിനിറ്റ് വിശ്രമിക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു സിനിമ {x} മിനിറ്റ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മിനിറ്റ് കണ്ടു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മണിക്കൂർ ജോലി ചെയ്യുകയും {y} മണിക്കൂർ കളിക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മണിക്കൂർ വാഹനം ഓടിക്കുകയും {y} മണിക്കൂർ നടക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ക്ലാസ് {x} മിനിറ്റ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മിനിറ്റ് കഴിഞ്ഞു. എത്ര സമയം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു പാട്ട് {x} സെക്കൻഡ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} സെക്കൻഡ് കഴിഞ്ഞു. എത്ര സെക്കൻഡ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് ബേക്ക് ചെയ്യുകയും {y} മിനിറ്റ് തണുപ്പിക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു വിമാനയാത്ര {x} മണിക്കൂർ ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മണിക്കൂർ കഴിഞ്ഞു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് വായിക്കുകയും {y} മിനിറ്റ് എഴുതുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് കാത്തിരുന്നു, തുടർന്ന് {y} മിനിറ്റ് കൂടി കാത്തിരുന്നു. ആകെ കാത്തിരിപ്പ് സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു മത്സരം {x} മിനിറ്റ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മിനിറ്റ് കഴിഞ്ഞു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഇന്ന് {x} മണിക്കൂറും നാളെ {y} മണിക്കൂറും. ആകെ എത്ര മണിക്കൂർ?</t>
+  </si>
+  <si>
+    <t>ഒരു നോട്ട്‌ബുക്കിന്റെ വില Rs {x} ആണ്. നിങ്ങൾ {y} നോട്ട്‌ബുക്കുകൾ വാങ്ങി. ആകെ ബിൽ എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. നിങ്ങൾ Rs {y} സ്നാക്സിന് ചെലവാക്കി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>കഴിഞ്ഞ ആഴ്ച Rs {x} സേവ് ചെയ്തു, ഈ ആഴ്ച Rs {y} സേവ് ചെയ്തു. ആകെ സേവിംഗ്സ് എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ചോക്ലേറ്റ് ബോക്സിന്റെ വില Rs {x} ആണ്. {y} ബോക്സുകളുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {x} നൽകി Rs {y} വിലയുള്ള സാധനം വാങ്ങി. എത്ര രൂപ തിരികെ കിട്ടും?</t>
+  </si>
+  <si>
+    <t>ഒരു ഷർട്ടിന്റെ വില Rs {x}, ഒരു പാന്റ്സിന്റെ വില Rs {y}. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ടായിരുന്നു. അതിൽ Rs {y} സഹോദരന് നൽകി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു സിനിമാ ടിക്കറ്റിന്റെ വില Rs {x} ആണ്. {y} ടിക്കറ്റുകളുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ആകെ ബിൽ Rs {x} ആണ്. നിങ്ങൾക്ക് Rs {y} ഡിസ്കൗണ്ട് ലഭിച്ചു. എത്ര രൂപ അടയ്ക്കണം?</t>
+  </si>
+  <si>
+    <t>Rs {x} വിലയുള്ള പഴങ്ങളും Rs {y} വിലയുള്ള പച്ചക്കറികളും വാങ്ങി. ആകെ ചെലവ് എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ഇന്ന് Rs {x}യും ഇന്നലെ Rs {y}യും സമ്പാദിച്ചു. ആകെ എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു കളിക്കാർയുടെ വില Rs {x} ആണ്. നിങ്ങൾ {y} കളിക്കാറുകൾ വാങ്ങി. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു കളിക്കായി Rs {x} വേണം. നിങ്ങൾക്ക് Rs {y} ഉണ്ട്. ഇനി എത്ര രൂപ കുറവാണ്?</t>
+  </si>
+  <si>
+    <t>ഒരു ഭക്ഷണത്തിന്റെ വില Rs {x} ആണ്. നിങ്ങൾ Rs {y} ടിപ്പ് നൽകി. ആകെ ചെലവ് എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. പുസ്തകങ്ങൾക്ക് Rs {y} ചെലവാക്കി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ബേക്കർ {x} കേക്കുകൾ ഉണ്ടാക്കി, {y} എണ്ണം വിറ്റു. എത്ര കേക്കുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ട്രെയിൻ {x} കിലോമീറ്റർ സഞ്ചരിച്ചു, തുടർന്ന് {y} കിലോമീറ്റർ കൂടി സഞ്ചരിച്ചു. ആകെ ദൂരം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു പുസ്തകത്തിന്റെ വില ${x} ആണ്. {y} പുസ്തകങ്ങളുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു കടയിൽ {x} ആപ്പിളുകളും {y} ഓറഞ്ചുകളും ഉണ്ട്. ആകെ എത്ര പഴങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു ടീം {x} പോയിന്റുകളും തുടർന്ന് {y} പോയിന്റുകളും നേടി. ആകെ സ്കോർ എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് ${x} ഉണ്ട്. നിങ്ങൾ ${y} ചെലവാക്കി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ആഴ്ചയിൽ {x} ദിവസങ്ങളുണ്ട്. {y} ആഴ്ചകളിൽ എത്ര ദിവസങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>{x} കാറുകൾക്ക് ഓരോന്നിലും {y} ചക്രങ്ങളുണ്ട്. ആകെ എത്ര ചക്രങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>{x} വിദ്യാർത്ഥികളെ {y} ടീമുകളാക്കി. ഓരോ ടീമിലും എത്ര വിദ്യാർത്ഥികൾ?</t>
+  </si>
+  <si>
+    <t>{x} ദിവസങ്ങളുള്ള യാത്ര {y} നഗരങ്ങളിലായി വിഭജിച്ചു. ഓരോ നഗരത്തിനും എത്ര ദിവസം?</t>
+  </si>
+  <si>
+    <t>{x} നാണയങ്ങൾ {y} കടൽക്കൊള്ളക്കാരിൽ പങ്കിട്ടു. എത്ര നാണയങ്ങൾ ശേഷിക്കും?</t>
+  </si>
+  <si>
+    <t>{x} ചോക്ലേറ്റുകൾ {y} സുഹൃത്തുകൾക്ക് നൽകി. എത്ര ചോക്ലേറ്റുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} കാർഡുകൾ {y} കളിക്കാർക്ക് വിതരണം ചെയ്തു. കെട്ടിൽ എത്ര കാർഡുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} മണിക്കൂറിൽ എത്ര മിനിറ്റുകൾ ഉണ്ട്?</t>
+  </si>
+  <si>
+    <t>സിനിമ {x} മിനിറ്റ് ദൈർഘ്യമുള്ളതാണ്. {y} മിനിറ്റ് കണ്ടു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് നടന്നു, {y} മിനിറ്റ് ഓടി. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>{x} ദിവസങ്ങളിൽ എത്ര മണിക്കൂറുകൾ ഉണ്ട്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ദിവസവും {x} മിനിറ്റ് പഠിക്കുന്നു. {y} ദിവസങ്ങളിൽ ആകെ എത്ര മിനിറ്റ് പഠിക്കും?</t>
+  </si>
+  <si>
+    <t>വിമാനയാത്ര {x} മിനിറ്റാണ്. {y} മിനിറ്റ് കഴിഞ്ഞു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് {x} മിനിറ്റ് ഉണ്ട്. ജോലി ചെയ്യാൻ {y} മിനിറ്റ് വേണം. എത്ര സമയം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} ആഴ്ചകളിൽ എത്ര ദിവസങ്ങൾ ഉണ്ട്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് കളിച്ചു, {y} മിനിറ്റ് വിശ്രമിച്ചു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ട്രെയിൻ യാത്ര {x} മിനിറ്റാണ്. അത് {y} മിനിറ്റ് വൈകിയിരിക്കുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ഒരു രാത്രിയിൽ {x} മണിക്കൂർ ഉറങ്ങുന്നു. {y} രാത്രികളിൽ ആകെ എത്ര മണിക്കൂർ ഉറങ്ങും?</t>
+  </si>
+  <si>
+    <t>വ്യായാമം {x} മിനിറ്റാണ്. അതിൽ {y} മിനിറ്റ് ചെയ്തു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} മണിക്കൂർ ജോലി, {y} മണിക്കൂർ വിശ്രമം. ആകെ എത്ര മണിക്കൂർ?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് പാചകം ചെയ്യുകയും {y} മിനിറ്റ് ഭക്ഷണം കഴിക്കുകയും ചെയ്യുന്നു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു അരി ചാക്കിന്റെ വില Rs {x} ആണ്. {y} ചാക്കുകളുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {x} തുക {y} സുഹൃത്തുക്കൾക്കിടയിൽ തുല്യമായി പങ്കിട്ടു. ഓരോരുത്തർക്കും എത്ര ലഭിക്കും?</t>
+  </si>
+  <si>
+    <t>ഒരു ജാക്കറ്റിന്റെ വില Rs {x} ആണ്. ഡിസ്കൗണ്ട് Rs {y} ആണ്. അന്തിമ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ബിൽ Rs {x} ആണ്. നിങ്ങൾ Rs {y} അടച്ചു. ഇനി എത്ര തുക അടയ്ക്കാനുണ്ട്?</t>
+  </si>
+  <si>
+    <t>Rs {x} വിലയുള്ളതും Rs {y} വിലയുള്ളതുമായ സാധനങ്ങൾ വാങ്ങി. ആകെ ചെലവ് എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ടിക്കറ്റിന്റെ വില Rs {x} ആണ്. {y} ടിക്കറ്റുകളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {y} വിലയുള്ള സാധനത്തിന് Rs {x} നോട്ടു നൽകി. എത്ര രൂപ തിരികെ കിട്ടും?</t>
+  </si>
+  <si>
+    <t>ജനുവരിയിൽ Rs {x}യും ഫെബ്രുവരിയിൽ Rs {y}യും സേവ് ചെയ്തു. ആകെ സേവിംഗ്സ് എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {x} തുക {y} തുല്യ മാസതവണകളായി അടയ്ക്കണം. ഓരോ മാസവും എത്ര അടയ്ക്കണം?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ദിവസവും Rs {x} സമ്പാദിക്കുന്നു. {y} ദിവസങ്ങളിൽ ആകെ എത്ര സമ്പാദിക്കും?</t>
+  </si>
+  <si>
+    <t>ബാങ്ക് ബാലൻസ് Rs {x} ആണ്. Rs {y} പിൻവലിച്ചു. എത്ര ബാക്കി?</t>
+  </si>
+  <si>
+    <t>വൈദ്യുതി ബിൽ Rs {x}, ജലബിൽ Rs {y}. ആകെ ബിൽ എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു പിസയുടെ വില Rs {x} ആണ്. {y} പിസകളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു സൈക്കിളിന് Rs {x} വേണം. നിങ്ങൾക്ക് Rs {y} ഉണ്ട്. ഇനി എത്ര രൂപ വേണം?</t>
+  </si>
+  <si>
+    <t>Rs {x} നൽകി {y} പേനകൾ വാങ്ങി. ഒരു പേനയുടെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു പട്ടണത്തിൽ {x} വീടുകൾ ഉണ്ട്. കൂടി {y} വീടുകൾ പണിതു. ആകെ എത്ര വീടുകൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു ഫാക്ടറി {x} കളിപ്പാട്ടങ്ങൾ നിർമ്മിച്ചു. അതിൽ {y} എണ്ണം തകർന്നു. എത്ര നല്ല കളിപ്പാട്ടങ്ങൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ലൈബ്രറിയിൽ {x} ഷെൽഫുകൾ ഉണ്ട്. ഓരോ ഷെൽഫിലും {y} പുസ്തകങ്ങൾ. ആകെ എത്ര പുസ്തകങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>{x} ആപ്പിളുകൾ {y} പെട്ടികളിൽ തുല്യമായി പായ്ക്ക് ചെയ്തു. ഓരോ പെട്ടിയിലും എത്ര ആപ്പിളുകൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു കളി {x} മിനിറ്റാണ്. അതിൽ {y} മിനിറ്റ് കഴിഞ്ഞു. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ Rs ${x} വിലയുള്ള ഒരു ഷർട്ടും Rs ${y} വിലയുള്ള ഒരു പാന്റും വാങ്ങി. ആകെ ചെലവ് എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ${x} സേവ് ചെയ്തു, ${y} കണ്ടെത്തി. ആകെ എത്ര പണം?</t>
+  </si>
+  <si>
+    <t>ഒരു ഫാമിൽ {x} പശുക്കളും {y} കുതിരകളും ഉണ്ട്. ആകെ എത്ര മൃഗങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>ഒരു പുസ്തകത്തിൽ {x} പേജുകളുണ്ട്. നിങ്ങൾ {y} പേജുകൾ വായിച്ചു. എത്ര പേജുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു ജാറിൽ {x} ബിസ്കറ്റുകൾ ഉണ്ട്. അതിൽ {y} എണ്ണം തിന്നു. എത്ര ബിസ്കറ്റുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു പുസ്തകത്തിൽ {x} അധ്യായങ്ങളുണ്ട്. ഓരോ അധ്യായത്തിലും {y} പേജുകൾ. ആകെ എത്ര പേജുകൾ?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ഓരോന്നും ${y} വിലയുള്ള {x} ടിക്കറ്റുകൾ വാങ്ങി. ആകെ ചെലവ് എത്ര?</t>
+  </si>
+  <si>
+    <t>{x} പുസ്തകങ്ങൾ {y} ഷെൽഫുകളിൽ വെച്ചു. ഓരോ ഷെൽഫിലും എത്ര പുസ്തകങ്ങൾ?</t>
+  </si>
+  <si>
+    <t>{x} മുട്ടകൾ {y} മുട്ട ട്രേകളിൽ വെച്ചു. എത്ര മുട്ടകൾ ശേഷിക്കും?</t>
+  </si>
+  <si>
+    <t>{x} അതിഥികൾ {y} സീറ്റുകളുള്ള മേശകളിൽ ഇരിക്കുന്നു. എത്ര അതിഥികൾ നിൽക്കേണ്ടിവരും?</t>
+  </si>
+  <si>
+    <t>{x} മിനിറ്റിൽ എത്ര സെക്കൻഡുകൾ ഉണ്ട്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ആഴ്ചയിൽ {x} മണിക്കൂർ ഉറങ്ങുന്നു. {y} ആഴ്ചകളിൽ ആകെ എത്ര മണിക്കൂർ ഉറങ്ങും?</t>
+  </si>
+  <si>
+    <t>സിനിമ {x} മിനിറ്റാണ്. {y} മിനിറ്റ് നിർത്തിവെച്ചു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മണിക്കൂർ യാത്ര ചെയ്തു, {y} മണിക്കൂർ താമസിച്ചു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് ജോലി ചെയ്തു. അതിൽ {y} മിനിറ്റ് പൂർത്തിയായി. എത്ര മിനിറ്റ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} മാസങ്ങളിൽ എത്ര ദിവസങ്ങൾ ഉണ്ട്? (30 ദിവസം വീതം)</t>
+  </si>
+  <si>
+    <t>{x} മണിക്കൂറുകൾ {y} ജോലികളായി വിഭജിച്ചു. ഓരോ ജോലിക്കും എത്ര മണിക്കൂർ?</t>
+  </si>
+  <si>
+    <t>യാത്ര {x} ദിവസങ്ങളുടേതാണ്. {y} ദിവസം കഴിഞ്ഞു. എത്ര ദിവസം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} മിനിറ്റുകൾ {y} സെഷനുകളായി വിഭജിച്ചു. ഓരോ സെഷനും എത്ര മിനിറ്റ്?</t>
+  </si>
+  <si>
+    <t>പ്രോജക്റ്റിന് {x} മണിക്കൂർ വേണം. അതിൽ {y} മണിക്കൂർ ചെയ്തു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ദിവസവും {x} മിനിറ്റ് കളിക്കുന്നു. {y} ദിവസങ്ങളിൽ ആകെ എത്ര മിനിറ്റ് കളിക്കും?</t>
+  </si>
+  <si>
+    <t>കോഴ്സ് {x} ആഴ്ചകളുടേതാണ്. {y} ആഴ്ചകൾ പൂർത്തിയായി. എത്ര ആഴ്ചകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>വീഡിയോ {x} സെക്കൻഡ് ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} സെക്കൻഡ് കണ്ടു. എത്ര സെക്കൻഡ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ശമ്പളം Rs {x} ആണ്. അതിൽ {y}% സേവ് ചെയ്തു. എത്ര തുക സേവ് ചെയ്തു?</t>
+  </si>
+  <si>
+    <t>ടിവിയുടെ വില Rs {x} ആണ്. {y} തുല്യ മാസതവണകളായി അടയ്ക്കണം. ഓരോ മാസവും എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {x} നിക്ഷേപിച്ചു, Rs {y} ലാഭം ലഭിച്ചു. ആകെ മൂല്യം എത്ര?</t>
+  </si>
+  <si>
+    <t>ബജറ്റ് Rs {x} ആണ്. വാടകയ്ക്ക് Rs {y} ചെലവാക്കി. എത്ര തുക ബാക്കി?</t>
+  </si>
+  <si>
+    <t>Rs {x} വായ്പ {y} പങ്കാളികൾക്കിടയിൽ വിഭജിച്ചു. ഓരോരുത്തർക്കും എത്ര?</t>
+  </si>
+  <si>
+    <t>ലാപ്‌ടോപ്പിന്റെ വില Rs {x} ആണ്. നികുതി Rs {y} ആണ്. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ഫോണിന്റെ വില Rs {x} ആണ്. {y} ഫോണുകളുടെ ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഭക്ഷണ ബിൽ Rs {x} ആണ്. അത് {y} ആളുകൾക്കിടയിൽ തുല്യമായി പങ്കിട്ടു. ഓരോരുത്തരും എത്ര അടയ്ക്കും?</t>
+  </si>
+  <si>
+    <t>വാടക Rs {x} പ്രതിമാസമാണ്. {y} മാസങ്ങളിലെ ആകെ വാടക എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. Rs {y} വിലയുള്ള വിമാന ടിക്കറ്റ് വാങ്ങി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ മാസംതോറും Rs {x} സമ്പാദിക്കുന്നു. {y} മാസങ്ങളിൽ ആകെ വരുമാനം എത്ര?</t>
+  </si>
+  <si>
+    <t>കാറിന്റെ വില Rs {x} ആണ്. ഡീലർ Rs {y} ഡിസ്കൗണ്ട് നൽകുന്നു. അന്തിമ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>Rs {x} സമ്മാനത്തുക {y} വിജയികൾക്കിടയിൽ തുല്യമായി പങ്കിട്ടു. ഓരോരുത്തർക്കും എത്ര ലഭിക്കും?</t>
+  </si>
+  <si>
+    <t>1 കിലോ സ്വർണത്തിന്റെ വില Rs {x} ആണ്. {y} കിലോ സ്വർണത്തിന്റെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>കമ്പനി A Rs {x} സമ്പാദിക്കുന്നു. കമ്പനി B Rs {y} സമ്പാദിക്കുന്നു. ആകെ വരുമാനം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു വിമാനം {x} മൈൽ പറന്നു, തുടർന്ന് {y} മൈൽ കൂടി പറന്നു. ആകെ ദൂരം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ടാങ്കിൽ {x} ലിറ്റർ വെള്ളമുണ്ട്. അതിൽ {y} ലിറ്റർ ഉപയോഗിച്ചു. എത്ര ലിറ്റർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു സ്റ്റേഡിയത്തിൽ {x} വരികളുണ്ട്. ഓരോ വരിയിലും {y} സീറ്റുകൾ ഉണ്ട്. ആകെ സീറ്റുകൾ എത്ര?</t>
+  </si>
+  <si>
+    <t>{x} ഡോളർ {y} വിജയികൾക്കിടയിൽ പങ്കിട്ടു. ഓരോ വിജയിക്കും എത്ര ഡോളർ?</t>
+  </si>
+  <si>
+    <t>ഒരു ട്രെയിനിൽ {x} പുരുഷന്മാരും {y} സ്ത്രീകളും ഉണ്ട്. ആകെ എത്ര ആളുകൾ?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മീറ്റർ നടന്നു, {y} മീറ്റർ ഓടി. ആകെ ദൂരം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ലൈബ്രറിയിൽ {x} പുസ്തകങ്ങൾ ഉണ്ട്. അതിൽ {y} എണ്ണം വായനക്കാർ എടുത്തു. എത്ര പുസ്തകങ്ങൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു കടയിൽ {x} ഷർട്ടുകൾ ഉണ്ടായിരുന്നു. അതിൽ {y} എണ്ണം വിറ്റു. എത്ര ഷർട്ടുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു കെട്ടിടത്തിൽ {x} നിലകളുണ്ട്. ഓരോ നിലയിലും {y} മുറികളുണ്ട്. ആകെ മുറികൾ എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ഫാമിൽ {x} വരി മരങ്ങളുണ്ട്. ഓരോ വരിയിലും {y} മരങ്ങളുണ്ട്. ആകെ മരങ്ങൾ എത്ര?</t>
+  </si>
+  <si>
+    <t>${x} തുക {y} സുഹൃത്തുക്കൾക്കിടയിൽ പങ്കിട്ടു. ഓരോ സുഹൃത്തിനും എത്ര ഡോളർ?</t>
+  </si>
+  <si>
+    <t>{x} മീറ്റർ നീളമുള്ള കയർ {y} തുല്യ ഭാഗങ്ങളായി മുറിച്ചു. ഓരോ ഭാഗത്തിന്റെ നീളം എത്ര?</t>
+  </si>
+  <si>
+    <t>{x} ലഘുലേഖകൾ {y} വീതം കെട്ടുകളാക്കി. എത്ര ലഘുലേഖകൾ ശേഷിക്കും?</t>
+  </si>
+  <si>
+    <t>{x} ലിറ്റർ ജ്യൂസ് {y} ലിറ്റർ കുപ്പികളിൽ നിറച്ചു. എത്ര ജ്യൂസ് ബാക്കി?</t>
+  </si>
+  <si>
+    <t>{x} ദിവസങ്ങളിൽ എത്ര മിനിറ്റുകൾ ഉണ്ട്? ({y} കൊണ്ട് ഗുണിക്കുക)</t>
+  </si>
+  <si>
+    <t>വിമാനയാത്രയ്ക്ക് {x} മണിക്കൂർ എടുക്കും. അത് എത്ര മിനിറ്റാണ്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ദിവസവും {x} മിനിറ്റ് ജോലി ചെയ്തു. {y} ദിവസങ്ങളിൽ ആകെ എത്ര മിനിറ്റ് ജോലി ചെയ്തു?</t>
+  </si>
+  <si>
+    <t>ഒരു വർഷത്തിൽ {x} ദിവസങ്ങളുണ്ട്. അത് എത്ര മണിക്കൂർ? ({y} കൊണ്ട് ഗുണിക്കുക)</t>
+  </si>
+  <si>
+    <t>ബാറ്ററി {x} മണിക്കൂർ നീണ്ടുനിൽക്കും. അതിൽ {y} മണിക്കൂർ ഉപയോഗിച്ചു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ആകെ {x} മിനിറ്റുകൾ {y} ജോലികൾക്കിടയിൽ തുല്യമായി പങ്കിട്ടു. ഓരോ ജോലിക്കും എത്ര മിനിറ്റ്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മിനിറ്റ് പഠിച്ചു, {y} മിനിറ്റ് വിശ്രമിച്ചു. ആകെ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു പ്രോജക്ടിന് {x} ആഴ്ചകൾ വേണം. അത് എത്ര ദിവസങ്ങളാണ്?</t>
+  </si>
+  <si>
+    <t>{x} സെക്കൻഡുകൾ എത്ര മിനിറ്റാണ്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മാസം ജീവിച്ചു. അത് എത്ര വർഷമാണ്?</t>
+  </si>
+  <si>
+    <t>ഒരു പരിപാടി {x} മണിക്കൂർ ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മണിക്കൂർ കഴിഞ്ഞു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>അവധി {x} ദിവസമാണ്. അതിൽ {y} ദിവസം യാത്ര ചെയ്തു. എത്ര ദിവസം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ദിവസവും {x} മിനിറ്റ് സേവ് ചെയ്യുന്നു. {y} ദിവസങ്ങളിൽ ആകെ എത്ര മിനിറ്റ് സേവ് ചെയ്യും?</t>
+  </si>
+  <si>
+    <t>ഓരോ യാത്രക്കും {x} മിനിറ്റ് ഡ്രൈവ് ചെയ്യുന്നു. {y} യാത്രകളിൽ ആകെ എത്ര മിനിറ്റ്?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് {x} മണിക്കൂർ സംഗീതമുണ്ട്. അതിൽ {y} മണിക്കൂർ കേട്ടു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് {x} ആപ്പിളുകൾ ഉണ്ട്. അതിൽ {y} എണ്ണം കഴിച്ചു. എത്ര ആപ്പിളുകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു നായയ്ക്ക് {x} എല്ലുകളുണ്ട്. അതിന് കൂടി {y} എല്ലുകൾ കിട്ടി. ആകെ എത്ര എല്ലുകൾ?</t>
+  </si>
+  <si>
+    <t>{x} പക്ഷികൾ വേലിയിൽ ഇരിക്കുന്നു. കൂടി {y} പക്ഷികൾ എത്തി. ആകെ എത്ര പക്ഷികൾ?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} ഗോൾ നേടി. നിങ്ങളുടെ സുഹൃത്ത് {y} ഗോൾ നേടി. ആകെ എത്ര ഗോൾ?</t>
+  </si>
+  <si>
+    <t>{x} തവളകൾ ഒരു മരത്തടിയിൽ ഉണ്ട്. അതിൽ {y} എണ്ണം ചാടി പോയി. എത്ര തവളകൾ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ട്. Rs {y} ചെലവാക്കി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>ഒരു പേനയുടെ വില Rs {x} ആണ്. ഒരു പെൻസിലിന്റെ വില Rs {y} ആണ്. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ ഇന്ന് Rs {x}യും നാളെ Rs {y}യും സമ്പാദിക്കും. ആകെ വരുമാനം എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ടോഫിയുടെ വില Rs {x} ആണ്. നിങ്ങൾ {y} ടോഫികൾ വാങ്ങി. ആകെ വില എത്ര?</t>
+  </si>
+  <si>
+    <t>ഒരു ബിസ്‌കറ്റിന്റെ വില Rs {x} ആണ്. നിങ്ങൾ {y} ബിസ്‌കറ്റുകൾ വാങ്ങി. ആകെ എത്ര രൂപ നൽകി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് Rs {x} ഉണ്ടായിരുന്നു. അതിൽ Rs {y} സുഹൃത്തിന് നൽകി. എത്ര പണം ബാക്കി?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾ {x} മണിക്കൂർ ഉറങ്ങി. തുടർന്ന് {y} മണിക്കൂർ കൂടി ഉറങ്ങി. ആകെ എത്ര മണിക്കൂർ ഉറക്കം?</t>
+  </si>
+  <si>
+    <t>ക്ലാസ് {x} മണിക്കൂർ ദൈർഘ്യമുള്ളതാണ്. അതിൽ {y} മണിക്കൂർ കഴിഞ്ഞു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>സ്കൂളിലേക്ക് പോകാൻ {x} മിനിറ്റ് നടന്നു, തിരികെ വരാൻ {y} മിനിറ്റ് നടന്നു. ആകെ നടക്കൽ സമയം എത്ര?</t>
+  </si>
+  <si>
+    <t>നിങ്ങൾക്ക് {x} മണിക്കൂർ ഒഴിവുസമയം ഉണ്ട്. അതിൽ {y} മണിക്കൂർ കളികൾക്കായി ഉപയോഗിച്ചു. എത്ര മണിക്കൂർ ബാക്കി?</t>
+  </si>
+  <si>
+    <t>आपके पास {x} सेब हैं। आप {y} खा लेते हैं। कितने बचे?</t>
+  </si>
+  <si>
+    <t>एक कुत्ते के पास {x} हड्डियाँ हैं। उसे और {y} हड्डियाँ मिलती हैं। कुल हड्डियाँ कितनी?</t>
+  </si>
+  <si>
+    <t>एक बाड़ पर {x} पक्षी बैठे हैं। {y} और पक्षी आ जाते हैं। कुल पक्षी कितने?</t>
+  </si>
+  <si>
+    <t>आप {x} गोल करते हैं। आपका मित्र {y} गोल करता है। कुल गोल कितने?</t>
+  </si>
+  <si>
+    <t>एक लकड़ी के तने पर {x} मेंढक हैं। {y} कूदकर चले जाते हैं। कितने मेंढक बचे?</t>
+  </si>
+  <si>
+    <t>आपके पास Rs {x} हैं। आप Rs {y} खर्च करते हैं। कितने पैसे बचे?</t>
+  </si>
+  <si>
+    <t>एक पेन की कीमत Rs {x} है। एक पेंसिल की कीमत Rs {y} है। कुल कीमत कितनी?</t>
+  </si>
+  <si>
+    <t>आप आज Rs {x} कमाते हैं और कल Rs {y} कमाएँगे। कुल कमाई कितनी?</t>
+  </si>
+  <si>
+    <t>एक टॉफ़ी की कीमत Rs {x} है। आप {y} टॉफ़ियाँ खरीदते हैं। कुल कीमत कितनी?</t>
+  </si>
+  <si>
+    <t>आपके पास Rs {x} हैं। आपको और Rs {y} मिलते हैं। कुल पैसे कितने?</t>
+  </si>
+  <si>
+    <t>एक बिस्कुट की कीमत Rs {x} है। आप {y} बिस्कुट खरीदते हैं। कुल कितना भुगतान किया?</t>
+  </si>
+  <si>
+    <t>आपके पास Rs {x} थे। आपने अपने मित्र को Rs {y} दिए। आपके पास कितने बचे?</t>
+  </si>
+  <si>
+    <t>आप {x} घंटे सोते हैं। फिर {y} घंटे और सोते हैं। कुल नींद कितनी हुई?</t>
+  </si>
+  <si>
+    <t>कक्षा {x} घंटे की है। {y} घंटे बीत चुके हैं। कितने घंटे बचे?</t>
+  </si>
+  <si>
+    <t>स्कूल जाने में {x} मिनट लगते हैं और वापस आने में {y} मिनट लगते हैं। कुल चलने का समय कितना?</t>
+  </si>
+  <si>
+    <t>आपके पास {x} घंटे खाली समय है। आप {y} घंटे खेलों में बिताते हैं। कितने घंटे बचे?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2451,32 +3630,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3C3489"/>
-      <name val="Cambria"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCECBF6"/>
-        <bgColor rgb="FFC0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEEDFE"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2491,14 +3651,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2766,11 +3920,13 @@
   <dimension ref="A1:M366"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="16384" max="16384" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="72.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="84" customWidth="1"/>
+    <col min="11" max="11" width="58.5546875" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2805,12 +3961,14 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>804</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>803</v>
       </c>
-      <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -2840,13 +3998,18 @@
       <c r="I2" t="s">
         <v>10</v>
       </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
       <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
         <v>15</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -2876,7 +4039,13 @@
       <c r="I3" t="s">
         <v>10</v>
       </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
       <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2908,7 +4077,13 @@
       <c r="I4" t="s">
         <v>10</v>
       </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
       <c r="K4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2940,7 +4115,13 @@
       <c r="I5" t="s">
         <v>10</v>
       </c>
+      <c r="J5" t="s">
+        <v>10</v>
+      </c>
       <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2972,7 +4153,13 @@
       <c r="I6" t="s">
         <v>10</v>
       </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
       <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3004,7 +4191,13 @@
       <c r="I7" t="s">
         <v>10</v>
       </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
       <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3036,7 +4229,13 @@
       <c r="I8" t="s">
         <v>10</v>
       </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
       <c r="K8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3068,7 +4267,13 @@
       <c r="I9" t="s">
         <v>10</v>
       </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
       <c r="K9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3100,7 +4305,13 @@
       <c r="I10" t="s">
         <v>10</v>
       </c>
+      <c r="J10" t="s">
+        <v>10</v>
+      </c>
       <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3132,7 +4343,13 @@
       <c r="I11" t="s">
         <v>10</v>
       </c>
+      <c r="J11" t="s">
+        <v>10</v>
+      </c>
       <c r="K11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3164,13 +4381,18 @@
       <c r="I12" t="s">
         <v>26</v>
       </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
       <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
         <v>16</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>2</v>
       </c>
-      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -3200,7 +4422,13 @@
       <c r="I13" t="s">
         <v>26</v>
       </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
       <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3232,7 +4460,13 @@
       <c r="I14" t="s">
         <v>26</v>
       </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
       <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3264,7 +4498,13 @@
       <c r="I15" t="s">
         <v>26</v>
       </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
       <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3296,7 +4536,13 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
       <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3328,7 +4574,13 @@
       <c r="I17" t="s">
         <v>26</v>
       </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
       <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3360,7 +4612,13 @@
       <c r="I18" t="s">
         <v>26</v>
       </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
       <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3392,7 +4650,13 @@
       <c r="I19" t="s">
         <v>26</v>
       </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
       <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3424,7 +4688,13 @@
       <c r="I20" t="s">
         <v>26</v>
       </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
       <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3456,7 +4726,13 @@
       <c r="I21" t="s">
         <v>26</v>
       </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
       <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3488,13 +4764,18 @@
       <c r="I22" t="s">
         <v>39</v>
       </c>
+      <c r="J22" t="s">
+        <v>39</v>
+      </c>
       <c r="K22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22" t="s">
         <v>29</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>3</v>
       </c>
-      <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -3524,7 +4805,13 @@
       <c r="I23" t="s">
         <v>39</v>
       </c>
+      <c r="J23" t="s">
+        <v>39</v>
+      </c>
       <c r="K23" t="s">
+        <v>39</v>
+      </c>
+      <c r="L23" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3556,7 +4843,13 @@
       <c r="I24" t="s">
         <v>39</v>
       </c>
+      <c r="J24" t="s">
+        <v>39</v>
+      </c>
       <c r="K24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3588,7 +4881,13 @@
       <c r="I25" t="s">
         <v>39</v>
       </c>
+      <c r="J25" t="s">
+        <v>39</v>
+      </c>
       <c r="K25" t="s">
+        <v>39</v>
+      </c>
+      <c r="L25" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3620,7 +4919,13 @@
       <c r="I26" t="s">
         <v>39</v>
       </c>
+      <c r="J26" t="s">
+        <v>39</v>
+      </c>
       <c r="K26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L26" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3652,7 +4957,13 @@
       <c r="I27" t="s">
         <v>39</v>
       </c>
+      <c r="J27" t="s">
+        <v>39</v>
+      </c>
       <c r="K27" t="s">
+        <v>39</v>
+      </c>
+      <c r="L27" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3684,7 +4995,13 @@
       <c r="I28" t="s">
         <v>39</v>
       </c>
+      <c r="J28" t="s">
+        <v>39</v>
+      </c>
       <c r="K28" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3716,7 +5033,13 @@
       <c r="I29" t="s">
         <v>39</v>
       </c>
+      <c r="J29" t="s">
+        <v>39</v>
+      </c>
       <c r="K29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L29" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3748,7 +5071,13 @@
       <c r="I30" t="s">
         <v>39</v>
       </c>
+      <c r="J30" t="s">
+        <v>39</v>
+      </c>
       <c r="K30" t="s">
+        <v>39</v>
+      </c>
+      <c r="L30" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3780,7 +5109,13 @@
       <c r="I31" t="s">
         <v>39</v>
       </c>
+      <c r="J31" t="s">
+        <v>39</v>
+      </c>
       <c r="K31" t="s">
+        <v>39</v>
+      </c>
+      <c r="L31" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3812,13 +5147,18 @@
       <c r="I32" t="s">
         <v>53</v>
       </c>
+      <c r="J32" t="s">
+        <v>53</v>
+      </c>
       <c r="K32" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" t="s">
         <v>43</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>4</v>
       </c>
-      <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -3848,7 +5188,13 @@
       <c r="I33" t="s">
         <v>53</v>
       </c>
+      <c r="J33" t="s">
+        <v>53</v>
+      </c>
       <c r="K33" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3880,7 +5226,13 @@
       <c r="I34" t="s">
         <v>53</v>
       </c>
+      <c r="J34" t="s">
+        <v>53</v>
+      </c>
       <c r="K34" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3912,7 +5264,13 @@
       <c r="I35" t="s">
         <v>53</v>
       </c>
+      <c r="J35" t="s">
+        <v>53</v>
+      </c>
       <c r="K35" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3944,7 +5302,13 @@
       <c r="I36" t="s">
         <v>53</v>
       </c>
+      <c r="J36" t="s">
+        <v>53</v>
+      </c>
       <c r="K36" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3976,7 +5340,13 @@
       <c r="I37" t="s">
         <v>53</v>
       </c>
+      <c r="J37" t="s">
+        <v>53</v>
+      </c>
       <c r="K37" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4008,7 +5378,13 @@
       <c r="I38" t="s">
         <v>53</v>
       </c>
+      <c r="J38" t="s">
+        <v>53</v>
+      </c>
       <c r="K38" t="s">
+        <v>53</v>
+      </c>
+      <c r="L38" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4040,7 +5416,13 @@
       <c r="I39" t="s">
         <v>53</v>
       </c>
+      <c r="J39" t="s">
+        <v>53</v>
+      </c>
       <c r="K39" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4072,7 +5454,13 @@
       <c r="I40" t="s">
         <v>53</v>
       </c>
+      <c r="J40" t="s">
+        <v>53</v>
+      </c>
       <c r="K40" t="s">
+        <v>53</v>
+      </c>
+      <c r="L40" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4104,7 +5492,13 @@
       <c r="I41" t="s">
         <v>53</v>
       </c>
+      <c r="J41" t="s">
+        <v>53</v>
+      </c>
       <c r="K41" t="s">
+        <v>53</v>
+      </c>
+      <c r="L41" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4136,13 +5530,18 @@
       <c r="I42" t="s">
         <v>10</v>
       </c>
+      <c r="J42" t="s">
+        <v>10</v>
+      </c>
       <c r="K42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" t="s">
         <v>57</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>5</v>
       </c>
-      <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -4172,7 +5571,13 @@
       <c r="I43" t="s">
         <v>10</v>
       </c>
+      <c r="J43" t="s">
+        <v>10</v>
+      </c>
       <c r="K43" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4204,7 +5609,13 @@
       <c r="I44" t="s">
         <v>10</v>
       </c>
+      <c r="J44" t="s">
+        <v>10</v>
+      </c>
       <c r="K44" t="s">
+        <v>10</v>
+      </c>
+      <c r="L44" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4236,7 +5647,13 @@
       <c r="I45" t="s">
         <v>10</v>
       </c>
+      <c r="J45" t="s">
+        <v>10</v>
+      </c>
       <c r="K45" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4268,7 +5685,13 @@
       <c r="I46" t="s">
         <v>10</v>
       </c>
+      <c r="J46" t="s">
+        <v>10</v>
+      </c>
       <c r="K46" t="s">
+        <v>10</v>
+      </c>
+      <c r="L46" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4300,7 +5723,13 @@
       <c r="I47" t="s">
         <v>10</v>
       </c>
+      <c r="J47" t="s">
+        <v>10</v>
+      </c>
       <c r="K47" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4332,7 +5761,13 @@
       <c r="I48" t="s">
         <v>10</v>
       </c>
+      <c r="J48" t="s">
+        <v>10</v>
+      </c>
       <c r="K48" t="s">
+        <v>10</v>
+      </c>
+      <c r="L48" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4364,7 +5799,13 @@
       <c r="I49" t="s">
         <v>10</v>
       </c>
+      <c r="J49" t="s">
+        <v>10</v>
+      </c>
       <c r="K49" t="s">
+        <v>10</v>
+      </c>
+      <c r="L49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4396,7 +5837,13 @@
       <c r="I50" t="s">
         <v>10</v>
       </c>
+      <c r="J50" t="s">
+        <v>10</v>
+      </c>
       <c r="K50" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4428,7 +5875,13 @@
       <c r="I51" t="s">
         <v>10</v>
       </c>
+      <c r="J51" t="s">
+        <v>10</v>
+      </c>
       <c r="K51" t="s">
+        <v>10</v>
+      </c>
+      <c r="L51" t="s">
         <v>57</v>
       </c>
     </row>
@@ -4460,13 +5913,18 @@
       <c r="I52" t="s">
         <v>26</v>
       </c>
+      <c r="J52" t="s">
+        <v>26</v>
+      </c>
       <c r="K52" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" t="s">
         <v>67</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>6</v>
       </c>
-      <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -4496,7 +5954,13 @@
       <c r="I53" t="s">
         <v>26</v>
       </c>
+      <c r="J53" t="s">
+        <v>26</v>
+      </c>
       <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4528,7 +5992,13 @@
       <c r="I54" t="s">
         <v>26</v>
       </c>
+      <c r="J54" t="s">
+        <v>26</v>
+      </c>
       <c r="K54" t="s">
+        <v>26</v>
+      </c>
+      <c r="L54" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4560,7 +6030,13 @@
       <c r="I55" t="s">
         <v>26</v>
       </c>
+      <c r="J55" t="s">
+        <v>26</v>
+      </c>
       <c r="K55" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4592,7 +6068,13 @@
       <c r="I56" t="s">
         <v>26</v>
       </c>
+      <c r="J56" t="s">
+        <v>26</v>
+      </c>
       <c r="K56" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4624,7 +6106,13 @@
       <c r="I57" t="s">
         <v>26</v>
       </c>
+      <c r="J57" t="s">
+        <v>26</v>
+      </c>
       <c r="K57" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4656,7 +6144,13 @@
       <c r="I58" t="s">
         <v>26</v>
       </c>
+      <c r="J58" t="s">
+        <v>26</v>
+      </c>
       <c r="K58" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4688,7 +6182,13 @@
       <c r="I59" t="s">
         <v>26</v>
       </c>
+      <c r="J59" t="s">
+        <v>26</v>
+      </c>
       <c r="K59" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4720,7 +6220,13 @@
       <c r="I60" t="s">
         <v>26</v>
       </c>
+      <c r="J60" t="s">
+        <v>26</v>
+      </c>
       <c r="K60" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4752,7 +6258,13 @@
       <c r="I61" t="s">
         <v>26</v>
       </c>
+      <c r="J61" t="s">
+        <v>26</v>
+      </c>
       <c r="K61" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4784,13 +6296,18 @@
       <c r="I62" t="s">
         <v>39</v>
       </c>
+      <c r="J62" t="s">
+        <v>39</v>
+      </c>
       <c r="K62" t="s">
+        <v>39</v>
+      </c>
+      <c r="L62" t="s">
         <v>78</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>7</v>
       </c>
-      <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -4820,7 +6337,13 @@
       <c r="I63" t="s">
         <v>39</v>
       </c>
+      <c r="J63" t="s">
+        <v>39</v>
+      </c>
       <c r="K63" t="s">
+        <v>39</v>
+      </c>
+      <c r="L63" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4852,7 +6375,13 @@
       <c r="I64" t="s">
         <v>39</v>
       </c>
+      <c r="J64" t="s">
+        <v>39</v>
+      </c>
       <c r="K64" t="s">
+        <v>39</v>
+      </c>
+      <c r="L64" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4884,7 +6413,13 @@
       <c r="I65" t="s">
         <v>39</v>
       </c>
+      <c r="J65" t="s">
+        <v>39</v>
+      </c>
       <c r="K65" t="s">
+        <v>39</v>
+      </c>
+      <c r="L65" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4916,7 +6451,13 @@
       <c r="I66" t="s">
         <v>39</v>
       </c>
+      <c r="J66" t="s">
+        <v>39</v>
+      </c>
       <c r="K66" t="s">
+        <v>39</v>
+      </c>
+      <c r="L66" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4948,7 +6489,13 @@
       <c r="I67" t="s">
         <v>39</v>
       </c>
+      <c r="J67" t="s">
+        <v>39</v>
+      </c>
       <c r="K67" t="s">
+        <v>39</v>
+      </c>
+      <c r="L67" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4980,7 +6527,13 @@
       <c r="I68" t="s">
         <v>39</v>
       </c>
+      <c r="J68" t="s">
+        <v>39</v>
+      </c>
       <c r="K68" t="s">
+        <v>39</v>
+      </c>
+      <c r="L68" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5012,7 +6565,13 @@
       <c r="I69" t="s">
         <v>39</v>
       </c>
+      <c r="J69" t="s">
+        <v>39</v>
+      </c>
       <c r="K69" t="s">
+        <v>39</v>
+      </c>
+      <c r="L69" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5044,7 +6603,13 @@
       <c r="I70" t="s">
         <v>39</v>
       </c>
+      <c r="J70" t="s">
+        <v>39</v>
+      </c>
       <c r="K70" t="s">
+        <v>39</v>
+      </c>
+      <c r="L70" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5076,7 +6641,13 @@
       <c r="I71" t="s">
         <v>39</v>
       </c>
+      <c r="J71" t="s">
+        <v>39</v>
+      </c>
       <c r="K71" t="s">
+        <v>39</v>
+      </c>
+      <c r="L71" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5108,13 +6679,18 @@
       <c r="I72" t="s">
         <v>53</v>
       </c>
+      <c r="J72" t="s">
+        <v>53</v>
+      </c>
       <c r="K72" t="s">
+        <v>53</v>
+      </c>
+      <c r="L72" t="s">
         <v>89</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>8</v>
       </c>
-      <c r="M72" s="2"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -5144,7 +6720,13 @@
       <c r="I73" t="s">
         <v>53</v>
       </c>
+      <c r="J73" t="s">
+        <v>53</v>
+      </c>
       <c r="K73" t="s">
+        <v>53</v>
+      </c>
+      <c r="L73" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5176,7 +6758,13 @@
       <c r="I74" t="s">
         <v>53</v>
       </c>
+      <c r="J74" t="s">
+        <v>53</v>
+      </c>
       <c r="K74" t="s">
+        <v>53</v>
+      </c>
+      <c r="L74" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5208,7 +6796,13 @@
       <c r="I75" t="s">
         <v>53</v>
       </c>
+      <c r="J75" t="s">
+        <v>53</v>
+      </c>
       <c r="K75" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5240,7 +6834,13 @@
       <c r="I76" t="s">
         <v>53</v>
       </c>
+      <c r="J76" t="s">
+        <v>53</v>
+      </c>
       <c r="K76" t="s">
+        <v>53</v>
+      </c>
+      <c r="L76" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5272,7 +6872,13 @@
       <c r="I77" t="s">
         <v>53</v>
       </c>
+      <c r="J77" t="s">
+        <v>53</v>
+      </c>
       <c r="K77" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5304,7 +6910,13 @@
       <c r="I78" t="s">
         <v>53</v>
       </c>
+      <c r="J78" t="s">
+        <v>53</v>
+      </c>
       <c r="K78" t="s">
+        <v>53</v>
+      </c>
+      <c r="L78" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5336,7 +6948,13 @@
       <c r="I79" t="s">
         <v>53</v>
       </c>
+      <c r="J79" t="s">
+        <v>53</v>
+      </c>
       <c r="K79" t="s">
+        <v>53</v>
+      </c>
+      <c r="L79" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5368,7 +6986,13 @@
       <c r="I80" t="s">
         <v>53</v>
       </c>
+      <c r="J80" t="s">
+        <v>53</v>
+      </c>
       <c r="K80" t="s">
+        <v>53</v>
+      </c>
+      <c r="L80" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5400,7 +7024,13 @@
       <c r="I81" t="s">
         <v>53</v>
       </c>
+      <c r="J81" t="s">
+        <v>53</v>
+      </c>
       <c r="K81" t="s">
+        <v>53</v>
+      </c>
+      <c r="L81" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5432,13 +7062,18 @@
       <c r="I82" t="s">
         <v>10</v>
       </c>
+      <c r="J82" t="s">
+        <v>10</v>
+      </c>
       <c r="K82" t="s">
+        <v>10</v>
+      </c>
+      <c r="L82" t="s">
         <v>101</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>9</v>
       </c>
-      <c r="M82" s="2"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -5468,7 +7103,13 @@
       <c r="I83" t="s">
         <v>10</v>
       </c>
+      <c r="J83" t="s">
+        <v>10</v>
+      </c>
       <c r="K83" t="s">
+        <v>10</v>
+      </c>
+      <c r="L83" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5500,7 +7141,13 @@
       <c r="I84" t="s">
         <v>10</v>
       </c>
+      <c r="J84" t="s">
+        <v>10</v>
+      </c>
       <c r="K84" t="s">
+        <v>10</v>
+      </c>
+      <c r="L84" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5532,7 +7179,13 @@
       <c r="I85" t="s">
         <v>10</v>
       </c>
+      <c r="J85" t="s">
+        <v>10</v>
+      </c>
       <c r="K85" t="s">
+        <v>10</v>
+      </c>
+      <c r="L85" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5564,7 +7217,13 @@
       <c r="I86" t="s">
         <v>10</v>
       </c>
+      <c r="J86" t="s">
+        <v>10</v>
+      </c>
       <c r="K86" t="s">
+        <v>10</v>
+      </c>
+      <c r="L86" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5596,7 +7255,13 @@
       <c r="I87" t="s">
         <v>10</v>
       </c>
+      <c r="J87" t="s">
+        <v>10</v>
+      </c>
       <c r="K87" t="s">
+        <v>10</v>
+      </c>
+      <c r="L87" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5628,7 +7293,13 @@
       <c r="I88" t="s">
         <v>10</v>
       </c>
+      <c r="J88" t="s">
+        <v>10</v>
+      </c>
       <c r="K88" t="s">
+        <v>10</v>
+      </c>
+      <c r="L88" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5660,7 +7331,13 @@
       <c r="I89" t="s">
         <v>10</v>
       </c>
+      <c r="J89" t="s">
+        <v>10</v>
+      </c>
       <c r="K89" t="s">
+        <v>10</v>
+      </c>
+      <c r="L89" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5692,7 +7369,13 @@
       <c r="I90" t="s">
         <v>10</v>
       </c>
+      <c r="J90" t="s">
+        <v>10</v>
+      </c>
       <c r="K90" t="s">
+        <v>10</v>
+      </c>
+      <c r="L90" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5724,7 +7407,13 @@
       <c r="I91" t="s">
         <v>10</v>
       </c>
+      <c r="J91" t="s">
+        <v>10</v>
+      </c>
       <c r="K91" t="s">
+        <v>10</v>
+      </c>
+      <c r="L91" t="s">
         <v>101</v>
       </c>
     </row>
@@ -5756,13 +7445,18 @@
       <c r="I92" t="s">
         <v>26</v>
       </c>
+      <c r="J92" t="s">
+        <v>26</v>
+      </c>
       <c r="K92" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" t="s">
         <v>113</v>
       </c>
-      <c r="L92">
-        <v>10</v>
-      </c>
-      <c r="M92" s="2"/>
+      <c r="M92">
+        <v>10</v>
+      </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
@@ -5792,7 +7486,13 @@
       <c r="I93" t="s">
         <v>26</v>
       </c>
+      <c r="J93" t="s">
+        <v>26</v>
+      </c>
       <c r="K93" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5824,7 +7524,13 @@
       <c r="I94" t="s">
         <v>26</v>
       </c>
+      <c r="J94" t="s">
+        <v>26</v>
+      </c>
       <c r="K94" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5856,7 +7562,13 @@
       <c r="I95" t="s">
         <v>26</v>
       </c>
+      <c r="J95" t="s">
+        <v>26</v>
+      </c>
       <c r="K95" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5888,7 +7600,13 @@
       <c r="I96" t="s">
         <v>26</v>
       </c>
+      <c r="J96" t="s">
+        <v>26</v>
+      </c>
       <c r="K96" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5920,7 +7638,13 @@
       <c r="I97" t="s">
         <v>26</v>
       </c>
+      <c r="J97" t="s">
+        <v>26</v>
+      </c>
       <c r="K97" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5952,7 +7676,13 @@
       <c r="I98" t="s">
         <v>26</v>
       </c>
+      <c r="J98" t="s">
+        <v>26</v>
+      </c>
       <c r="K98" t="s">
+        <v>26</v>
+      </c>
+      <c r="L98" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5984,7 +7714,13 @@
       <c r="I99" t="s">
         <v>26</v>
       </c>
+      <c r="J99" t="s">
+        <v>26</v>
+      </c>
       <c r="K99" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6016,7 +7752,13 @@
       <c r="I100" t="s">
         <v>26</v>
       </c>
+      <c r="J100" t="s">
+        <v>26</v>
+      </c>
       <c r="K100" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6048,7 +7790,13 @@
       <c r="I101" t="s">
         <v>26</v>
       </c>
+      <c r="J101" t="s">
+        <v>26</v>
+      </c>
       <c r="K101" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6080,13 +7828,18 @@
       <c r="I102" t="s">
         <v>39</v>
       </c>
+      <c r="J102" t="s">
+        <v>39</v>
+      </c>
       <c r="K102" t="s">
+        <v>39</v>
+      </c>
+      <c r="L102" t="s">
         <v>124</v>
       </c>
-      <c r="L102">
+      <c r="M102">
         <v>11</v>
       </c>
-      <c r="M102" s="2"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
@@ -6116,7 +7869,13 @@
       <c r="I103" t="s">
         <v>39</v>
       </c>
+      <c r="J103" t="s">
+        <v>39</v>
+      </c>
       <c r="K103" t="s">
+        <v>39</v>
+      </c>
+      <c r="L103" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6148,7 +7907,13 @@
       <c r="I104" t="s">
         <v>39</v>
       </c>
+      <c r="J104" t="s">
+        <v>39</v>
+      </c>
       <c r="K104" t="s">
+        <v>39</v>
+      </c>
+      <c r="L104" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6180,7 +7945,13 @@
       <c r="I105" t="s">
         <v>39</v>
       </c>
+      <c r="J105" t="s">
+        <v>39</v>
+      </c>
       <c r="K105" t="s">
+        <v>39</v>
+      </c>
+      <c r="L105" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6212,7 +7983,13 @@
       <c r="I106" t="s">
         <v>39</v>
       </c>
+      <c r="J106" t="s">
+        <v>39</v>
+      </c>
       <c r="K106" t="s">
+        <v>39</v>
+      </c>
+      <c r="L106" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6244,7 +8021,13 @@
       <c r="I107" t="s">
         <v>39</v>
       </c>
+      <c r="J107" t="s">
+        <v>39</v>
+      </c>
       <c r="K107" t="s">
+        <v>39</v>
+      </c>
+      <c r="L107" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6276,7 +8059,13 @@
       <c r="I108" t="s">
         <v>39</v>
       </c>
+      <c r="J108" t="s">
+        <v>39</v>
+      </c>
       <c r="K108" t="s">
+        <v>39</v>
+      </c>
+      <c r="L108" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6308,7 +8097,13 @@
       <c r="I109" t="s">
         <v>39</v>
       </c>
+      <c r="J109" t="s">
+        <v>39</v>
+      </c>
       <c r="K109" t="s">
+        <v>39</v>
+      </c>
+      <c r="L109" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6340,7 +8135,13 @@
       <c r="I110" t="s">
         <v>39</v>
       </c>
+      <c r="J110" t="s">
+        <v>39</v>
+      </c>
       <c r="K110" t="s">
+        <v>39</v>
+      </c>
+      <c r="L110" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6372,7 +8173,13 @@
       <c r="I111" t="s">
         <v>39</v>
       </c>
+      <c r="J111" t="s">
+        <v>39</v>
+      </c>
       <c r="K111" t="s">
+        <v>39</v>
+      </c>
+      <c r="L111" t="s">
         <v>124</v>
       </c>
     </row>
@@ -6404,15 +8211,20 @@
       <c r="I112" t="s">
         <v>53</v>
       </c>
+      <c r="J112" t="s">
+        <v>53</v>
+      </c>
       <c r="K112" t="s">
+        <v>53</v>
+      </c>
+      <c r="L112" t="s">
         <v>135</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>12</v>
       </c>
-      <c r="M112" s="2"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>53</v>
       </c>
@@ -6440,11 +8252,17 @@
       <c r="I113" t="s">
         <v>53</v>
       </c>
+      <c r="J113" t="s">
+        <v>53</v>
+      </c>
       <c r="K113" t="s">
+        <v>53</v>
+      </c>
+      <c r="L113" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -6472,11 +8290,17 @@
       <c r="I114" t="s">
         <v>53</v>
       </c>
+      <c r="J114" t="s">
+        <v>53</v>
+      </c>
       <c r="K114" t="s">
+        <v>53</v>
+      </c>
+      <c r="L114" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>53</v>
       </c>
@@ -6504,11 +8328,17 @@
       <c r="I115" t="s">
         <v>53</v>
       </c>
+      <c r="J115" t="s">
+        <v>53</v>
+      </c>
       <c r="K115" t="s">
+        <v>53</v>
+      </c>
+      <c r="L115" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>53</v>
       </c>
@@ -6536,11 +8366,17 @@
       <c r="I116" t="s">
         <v>53</v>
       </c>
+      <c r="J116" t="s">
+        <v>53</v>
+      </c>
       <c r="K116" t="s">
+        <v>53</v>
+      </c>
+      <c r="L116" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>53</v>
       </c>
@@ -6568,11 +8404,17 @@
       <c r="I117" t="s">
         <v>53</v>
       </c>
+      <c r="J117" t="s">
+        <v>53</v>
+      </c>
       <c r="K117" t="s">
+        <v>53</v>
+      </c>
+      <c r="L117" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>53</v>
       </c>
@@ -6600,11 +8442,17 @@
       <c r="I118" t="s">
         <v>53</v>
       </c>
+      <c r="J118" t="s">
+        <v>53</v>
+      </c>
       <c r="K118" t="s">
+        <v>53</v>
+      </c>
+      <c r="L118" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>53</v>
       </c>
@@ -6632,11 +8480,17 @@
       <c r="I119" t="s">
         <v>53</v>
       </c>
+      <c r="J119" t="s">
+        <v>53</v>
+      </c>
       <c r="K119" t="s">
+        <v>53</v>
+      </c>
+      <c r="L119" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>53</v>
       </c>
@@ -6664,11 +8518,17 @@
       <c r="I120" t="s">
         <v>53</v>
       </c>
+      <c r="J120" t="s">
+        <v>53</v>
+      </c>
       <c r="K120" t="s">
+        <v>53</v>
+      </c>
+      <c r="L120" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>53</v>
       </c>
@@ -6696,11 +8556,17 @@
       <c r="I121" t="s">
         <v>53</v>
       </c>
+      <c r="J121" t="s">
+        <v>53</v>
+      </c>
       <c r="K121" t="s">
+        <v>53</v>
+      </c>
+      <c r="L121" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>10</v>
       </c>
@@ -6728,11 +8594,17 @@
       <c r="I122" t="s">
         <v>10</v>
       </c>
+      <c r="J122" t="s">
+        <v>10</v>
+      </c>
       <c r="K122" t="s">
+        <v>10</v>
+      </c>
+      <c r="L122" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>10</v>
       </c>
@@ -6760,11 +8632,17 @@
       <c r="I123" t="s">
         <v>10</v>
       </c>
+      <c r="J123" t="s">
+        <v>10</v>
+      </c>
       <c r="K123" t="s">
+        <v>10</v>
+      </c>
+      <c r="L123" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>10</v>
       </c>
@@ -6792,11 +8670,17 @@
       <c r="I124" t="s">
         <v>10</v>
       </c>
+      <c r="J124" t="s">
+        <v>10</v>
+      </c>
       <c r="K124" t="s">
+        <v>10</v>
+      </c>
+      <c r="L124" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>10</v>
       </c>
@@ -6824,11 +8708,17 @@
       <c r="I125" t="s">
         <v>10</v>
       </c>
+      <c r="J125" t="s">
+        <v>10</v>
+      </c>
       <c r="K125" t="s">
+        <v>10</v>
+      </c>
+      <c r="L125" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>10</v>
       </c>
@@ -6856,11 +8746,17 @@
       <c r="I126" t="s">
         <v>10</v>
       </c>
+      <c r="J126" t="s">
+        <v>10</v>
+      </c>
       <c r="K126" t="s">
+        <v>10</v>
+      </c>
+      <c r="L126" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>10</v>
       </c>
@@ -6888,11 +8784,17 @@
       <c r="I127" t="s">
         <v>10</v>
       </c>
+      <c r="J127" t="s">
+        <v>10</v>
+      </c>
       <c r="K127" t="s">
+        <v>10</v>
+      </c>
+      <c r="L127" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -6920,11 +8822,17 @@
       <c r="I128" t="s">
         <v>10</v>
       </c>
+      <c r="J128" t="s">
+        <v>10</v>
+      </c>
       <c r="K128" t="s">
+        <v>10</v>
+      </c>
+      <c r="L128" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>10</v>
       </c>
@@ -6952,11 +8860,17 @@
       <c r="I129" t="s">
         <v>10</v>
       </c>
+      <c r="J129" t="s">
+        <v>10</v>
+      </c>
       <c r="K129" t="s">
+        <v>10</v>
+      </c>
+      <c r="L129" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>10</v>
       </c>
@@ -6984,11 +8898,17 @@
       <c r="I130" t="s">
         <v>10</v>
       </c>
+      <c r="J130" t="s">
+        <v>10</v>
+      </c>
       <c r="K130" t="s">
+        <v>10</v>
+      </c>
+      <c r="L130" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>10</v>
       </c>
@@ -7016,11 +8936,17 @@
       <c r="I131" t="s">
         <v>10</v>
       </c>
+      <c r="J131" t="s">
+        <v>10</v>
+      </c>
       <c r="K131" t="s">
+        <v>10</v>
+      </c>
+      <c r="L131" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>26</v>
       </c>
@@ -7048,11 +8974,17 @@
       <c r="I132" t="s">
         <v>26</v>
       </c>
+      <c r="J132" t="s">
+        <v>26</v>
+      </c>
       <c r="K132" t="s">
+        <v>26</v>
+      </c>
+      <c r="L132" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>26</v>
       </c>
@@ -7080,11 +9012,17 @@
       <c r="I133" t="s">
         <v>26</v>
       </c>
+      <c r="J133" t="s">
+        <v>26</v>
+      </c>
       <c r="K133" t="s">
+        <v>26</v>
+      </c>
+      <c r="L133" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>26</v>
       </c>
@@ -7112,11 +9050,17 @@
       <c r="I134" t="s">
         <v>26</v>
       </c>
+      <c r="J134" t="s">
+        <v>26</v>
+      </c>
       <c r="K134" t="s">
+        <v>26</v>
+      </c>
+      <c r="L134" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>26</v>
       </c>
@@ -7144,11 +9088,17 @@
       <c r="I135" t="s">
         <v>26</v>
       </c>
+      <c r="J135" t="s">
+        <v>26</v>
+      </c>
       <c r="K135" t="s">
+        <v>26</v>
+      </c>
+      <c r="L135" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>26</v>
       </c>
@@ -7176,11 +9126,17 @@
       <c r="I136" t="s">
         <v>26</v>
       </c>
+      <c r="J136" t="s">
+        <v>26</v>
+      </c>
       <c r="K136" t="s">
+        <v>26</v>
+      </c>
+      <c r="L136" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>26</v>
       </c>
@@ -7208,11 +9164,17 @@
       <c r="I137" t="s">
         <v>26</v>
       </c>
+      <c r="J137" t="s">
+        <v>26</v>
+      </c>
       <c r="K137" t="s">
+        <v>26</v>
+      </c>
+      <c r="L137" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>26</v>
       </c>
@@ -7240,11 +9202,17 @@
       <c r="I138" t="s">
         <v>26</v>
       </c>
+      <c r="J138" t="s">
+        <v>26</v>
+      </c>
       <c r="K138" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>26</v>
       </c>
@@ -7272,11 +9240,17 @@
       <c r="I139" t="s">
         <v>26</v>
       </c>
+      <c r="J139" t="s">
+        <v>26</v>
+      </c>
       <c r="K139" t="s">
+        <v>26</v>
+      </c>
+      <c r="L139" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>26</v>
       </c>
@@ -7304,11 +9278,17 @@
       <c r="I140" t="s">
         <v>26</v>
       </c>
+      <c r="J140" t="s">
+        <v>26</v>
+      </c>
       <c r="K140" t="s">
+        <v>26</v>
+      </c>
+      <c r="L140" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -7336,11 +9316,17 @@
       <c r="I141" t="s">
         <v>26</v>
       </c>
+      <c r="J141" t="s">
+        <v>26</v>
+      </c>
       <c r="K141" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>39</v>
       </c>
@@ -7368,11 +9354,17 @@
       <c r="I142" t="s">
         <v>39</v>
       </c>
+      <c r="J142" t="s">
+        <v>39</v>
+      </c>
       <c r="K142" t="s">
+        <v>39</v>
+      </c>
+      <c r="L142" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>39</v>
       </c>
@@ -7400,11 +9392,17 @@
       <c r="I143" t="s">
         <v>39</v>
       </c>
+      <c r="J143" t="s">
+        <v>39</v>
+      </c>
       <c r="K143" t="s">
+        <v>39</v>
+      </c>
+      <c r="L143" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>39</v>
       </c>
@@ -7432,11 +9430,17 @@
       <c r="I144" t="s">
         <v>39</v>
       </c>
+      <c r="J144" t="s">
+        <v>39</v>
+      </c>
       <c r="K144" t="s">
+        <v>39</v>
+      </c>
+      <c r="L144" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -7464,11 +9468,17 @@
       <c r="I145" t="s">
         <v>39</v>
       </c>
+      <c r="J145" t="s">
+        <v>39</v>
+      </c>
       <c r="K145" t="s">
+        <v>39</v>
+      </c>
+      <c r="L145" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>39</v>
       </c>
@@ -7496,11 +9506,17 @@
       <c r="I146" t="s">
         <v>39</v>
       </c>
+      <c r="J146" t="s">
+        <v>39</v>
+      </c>
       <c r="K146" t="s">
+        <v>39</v>
+      </c>
+      <c r="L146" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>39</v>
       </c>
@@ -7528,11 +9544,17 @@
       <c r="I147" t="s">
         <v>39</v>
       </c>
+      <c r="J147" t="s">
+        <v>39</v>
+      </c>
       <c r="K147" t="s">
+        <v>39</v>
+      </c>
+      <c r="L147" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>39</v>
       </c>
@@ -7560,11 +9582,17 @@
       <c r="I148" t="s">
         <v>39</v>
       </c>
+      <c r="J148" t="s">
+        <v>39</v>
+      </c>
       <c r="K148" t="s">
+        <v>39</v>
+      </c>
+      <c r="L148" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>39</v>
       </c>
@@ -7592,11 +9620,17 @@
       <c r="I149" t="s">
         <v>39</v>
       </c>
+      <c r="J149" t="s">
+        <v>39</v>
+      </c>
       <c r="K149" t="s">
+        <v>39</v>
+      </c>
+      <c r="L149" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>39</v>
       </c>
@@ -7624,11 +9658,17 @@
       <c r="I150" t="s">
         <v>39</v>
       </c>
+      <c r="J150" t="s">
+        <v>39</v>
+      </c>
       <c r="K150" t="s">
+        <v>39</v>
+      </c>
+      <c r="L150" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>39</v>
       </c>
@@ -7656,11 +9696,17 @@
       <c r="I151" t="s">
         <v>39</v>
       </c>
+      <c r="J151" t="s">
+        <v>39</v>
+      </c>
       <c r="K151" t="s">
+        <v>39</v>
+      </c>
+      <c r="L151" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>53</v>
       </c>
@@ -7688,11 +9734,17 @@
       <c r="I152" t="s">
         <v>53</v>
       </c>
+      <c r="J152" t="s">
+        <v>53</v>
+      </c>
       <c r="K152" t="s">
+        <v>53</v>
+      </c>
+      <c r="L152" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>53</v>
       </c>
@@ -7720,11 +9772,17 @@
       <c r="I153" t="s">
         <v>53</v>
       </c>
+      <c r="J153" t="s">
+        <v>53</v>
+      </c>
       <c r="K153" t="s">
+        <v>53</v>
+      </c>
+      <c r="L153" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>53</v>
       </c>
@@ -7752,11 +9810,17 @@
       <c r="I154" t="s">
         <v>53</v>
       </c>
+      <c r="J154" t="s">
+        <v>53</v>
+      </c>
       <c r="K154" t="s">
+        <v>53</v>
+      </c>
+      <c r="L154" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>53</v>
       </c>
@@ -7784,11 +9848,17 @@
       <c r="I155" t="s">
         <v>53</v>
       </c>
+      <c r="J155" t="s">
+        <v>53</v>
+      </c>
       <c r="K155" t="s">
+        <v>53</v>
+      </c>
+      <c r="L155" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>53</v>
       </c>
@@ -7816,11 +9886,17 @@
       <c r="I156" t="s">
         <v>53</v>
       </c>
+      <c r="J156" t="s">
+        <v>53</v>
+      </c>
       <c r="K156" t="s">
+        <v>53</v>
+      </c>
+      <c r="L156" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>53</v>
       </c>
@@ -7848,11 +9924,17 @@
       <c r="I157" t="s">
         <v>53</v>
       </c>
+      <c r="J157" t="s">
+        <v>53</v>
+      </c>
       <c r="K157" t="s">
+        <v>53</v>
+      </c>
+      <c r="L157" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>53</v>
       </c>
@@ -7880,11 +9962,17 @@
       <c r="I158" t="s">
         <v>53</v>
       </c>
+      <c r="J158" t="s">
+        <v>53</v>
+      </c>
       <c r="K158" t="s">
+        <v>53</v>
+      </c>
+      <c r="L158" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>53</v>
       </c>
@@ -7912,11 +10000,17 @@
       <c r="I159" t="s">
         <v>53</v>
       </c>
+      <c r="J159" t="s">
+        <v>53</v>
+      </c>
       <c r="K159" t="s">
+        <v>53</v>
+      </c>
+      <c r="L159" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>53</v>
       </c>
@@ -7944,11 +10038,17 @@
       <c r="I160" t="s">
         <v>53</v>
       </c>
+      <c r="J160" t="s">
+        <v>53</v>
+      </c>
       <c r="K160" t="s">
+        <v>53</v>
+      </c>
+      <c r="L160" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>53</v>
       </c>
@@ -7976,11 +10076,17 @@
       <c r="I161" t="s">
         <v>53</v>
       </c>
+      <c r="J161" t="s">
+        <v>53</v>
+      </c>
       <c r="K161" t="s">
+        <v>53</v>
+      </c>
+      <c r="L161" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>203</v>
       </c>
@@ -8008,11 +10114,17 @@
       <c r="I162" t="s">
         <v>203</v>
       </c>
+      <c r="J162" t="s">
+        <v>203</v>
+      </c>
       <c r="K162" t="s">
+        <v>203</v>
+      </c>
+      <c r="L162" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>203</v>
       </c>
@@ -8040,11 +10152,17 @@
       <c r="I163" t="s">
         <v>203</v>
       </c>
+      <c r="J163" t="s">
+        <v>203</v>
+      </c>
       <c r="K163" t="s">
+        <v>203</v>
+      </c>
+      <c r="L163" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>203</v>
       </c>
@@ -8072,11 +10190,17 @@
       <c r="I164" t="s">
         <v>203</v>
       </c>
+      <c r="J164" t="s">
+        <v>203</v>
+      </c>
       <c r="K164" t="s">
+        <v>203</v>
+      </c>
+      <c r="L164" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>203</v>
       </c>
@@ -8104,11 +10228,17 @@
       <c r="I165" t="s">
         <v>203</v>
       </c>
+      <c r="J165" t="s">
+        <v>203</v>
+      </c>
       <c r="K165" t="s">
+        <v>203</v>
+      </c>
+      <c r="L165" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>203</v>
       </c>
@@ -8136,11 +10266,17 @@
       <c r="I166" t="s">
         <v>203</v>
       </c>
+      <c r="J166" t="s">
+        <v>203</v>
+      </c>
       <c r="K166" t="s">
+        <v>203</v>
+      </c>
+      <c r="L166" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>212</v>
       </c>
@@ -8168,11 +10304,17 @@
       <c r="I167" t="s">
         <v>212</v>
       </c>
+      <c r="J167" t="s">
+        <v>212</v>
+      </c>
       <c r="K167" t="s">
+        <v>212</v>
+      </c>
+      <c r="L167" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>212</v>
       </c>
@@ -8200,11 +10342,17 @@
       <c r="I168" t="s">
         <v>212</v>
       </c>
+      <c r="J168" t="s">
+        <v>212</v>
+      </c>
       <c r="K168" t="s">
+        <v>212</v>
+      </c>
+      <c r="L168" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>212</v>
       </c>
@@ -8232,11 +10380,17 @@
       <c r="I169" t="s">
         <v>212</v>
       </c>
+      <c r="J169" t="s">
+        <v>212</v>
+      </c>
       <c r="K169" t="s">
+        <v>212</v>
+      </c>
+      <c r="L169" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>212</v>
       </c>
@@ -8264,11 +10418,17 @@
       <c r="I170" t="s">
         <v>212</v>
       </c>
+      <c r="J170" t="s">
+        <v>212</v>
+      </c>
       <c r="K170" t="s">
+        <v>212</v>
+      </c>
+      <c r="L170" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>212</v>
       </c>
@@ -8296,11 +10456,17 @@
       <c r="I171" t="s">
         <v>212</v>
       </c>
+      <c r="J171" t="s">
+        <v>212</v>
+      </c>
       <c r="K171" t="s">
+        <v>212</v>
+      </c>
+      <c r="L171" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>220</v>
       </c>
@@ -8328,11 +10494,17 @@
       <c r="I172" t="s">
         <v>224</v>
       </c>
+      <c r="J172" t="s">
+        <v>993</v>
+      </c>
       <c r="K172" t="s">
+        <v>805</v>
+      </c>
+      <c r="L172" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>228</v>
       </c>
@@ -8360,11 +10532,17 @@
       <c r="I173" t="s">
         <v>230</v>
       </c>
+      <c r="J173" t="s">
+        <v>994</v>
+      </c>
       <c r="K173" t="s">
+        <v>806</v>
+      </c>
+      <c r="L173" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>231</v>
       </c>
@@ -8392,11 +10570,17 @@
       <c r="I174" t="s">
         <v>234</v>
       </c>
+      <c r="J174" t="s">
+        <v>995</v>
+      </c>
       <c r="K174" t="s">
+        <v>807</v>
+      </c>
+      <c r="L174" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>235</v>
       </c>
@@ -8424,11 +10608,17 @@
       <c r="I175" t="s">
         <v>237</v>
       </c>
+      <c r="J175" t="s">
+        <v>996</v>
+      </c>
       <c r="K175" t="s">
+        <v>808</v>
+      </c>
+      <c r="L175" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>238</v>
       </c>
@@ -8456,11 +10646,17 @@
       <c r="I176" t="s">
         <v>241</v>
       </c>
+      <c r="J176" t="s">
+        <v>997</v>
+      </c>
       <c r="K176" t="s">
+        <v>809</v>
+      </c>
+      <c r="L176" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>242</v>
       </c>
@@ -8488,11 +10684,17 @@
       <c r="I177" t="s">
         <v>244</v>
       </c>
+      <c r="J177" t="s">
+        <v>998</v>
+      </c>
       <c r="K177" t="s">
+        <v>810</v>
+      </c>
+      <c r="L177" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>245</v>
       </c>
@@ -8520,11 +10722,17 @@
       <c r="I178" t="s">
         <v>247</v>
       </c>
+      <c r="J178" t="s">
+        <v>999</v>
+      </c>
       <c r="K178" t="s">
+        <v>811</v>
+      </c>
+      <c r="L178" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>248</v>
       </c>
@@ -8552,11 +10760,17 @@
       <c r="I179" t="s">
         <v>250</v>
       </c>
+      <c r="J179" t="s">
+        <v>1000</v>
+      </c>
       <c r="K179" t="s">
+        <v>812</v>
+      </c>
+      <c r="L179" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>251</v>
       </c>
@@ -8584,11 +10798,17 @@
       <c r="I180" t="s">
         <v>253</v>
       </c>
+      <c r="J180" t="s">
+        <v>1001</v>
+      </c>
       <c r="K180" t="s">
+        <v>813</v>
+      </c>
+      <c r="L180" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>254</v>
       </c>
@@ -8616,11 +10836,17 @@
       <c r="I181" t="s">
         <v>256</v>
       </c>
+      <c r="J181" t="s">
+        <v>1002</v>
+      </c>
       <c r="K181" t="s">
+        <v>814</v>
+      </c>
+      <c r="L181" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>257</v>
       </c>
@@ -8648,11 +10874,17 @@
       <c r="I182" t="s">
         <v>259</v>
       </c>
+      <c r="J182" t="s">
+        <v>1003</v>
+      </c>
       <c r="K182" t="s">
+        <v>815</v>
+      </c>
+      <c r="L182" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>260</v>
       </c>
@@ -8680,11 +10912,17 @@
       <c r="I183" t="s">
         <v>262</v>
       </c>
+      <c r="J183" t="s">
+        <v>1004</v>
+      </c>
       <c r="K183" t="s">
+        <v>816</v>
+      </c>
+      <c r="L183" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>263</v>
       </c>
@@ -8712,11 +10950,17 @@
       <c r="I184" t="s">
         <v>265</v>
       </c>
+      <c r="J184" t="s">
+        <v>1005</v>
+      </c>
       <c r="K184" t="s">
+        <v>817</v>
+      </c>
+      <c r="L184" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>266</v>
       </c>
@@ -8744,11 +10988,17 @@
       <c r="I185" t="s">
         <v>268</v>
       </c>
+      <c r="J185" t="s">
+        <v>1006</v>
+      </c>
       <c r="K185" t="s">
+        <v>818</v>
+      </c>
+      <c r="L185" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>269</v>
       </c>
@@ -8776,11 +11026,17 @@
       <c r="I186" t="s">
         <v>271</v>
       </c>
+      <c r="J186" t="s">
+        <v>1007</v>
+      </c>
       <c r="K186" t="s">
+        <v>819</v>
+      </c>
+      <c r="L186" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>272</v>
       </c>
@@ -8808,11 +11064,17 @@
       <c r="I187" t="s">
         <v>275</v>
       </c>
+      <c r="J187" t="s">
+        <v>1008</v>
+      </c>
       <c r="K187" t="s">
+        <v>820</v>
+      </c>
+      <c r="L187" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>278</v>
       </c>
@@ -8840,11 +11102,17 @@
       <c r="I188" t="s">
         <v>280</v>
       </c>
+      <c r="J188" t="s">
+        <v>1009</v>
+      </c>
       <c r="K188" t="s">
+        <v>821</v>
+      </c>
+      <c r="L188" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>282</v>
       </c>
@@ -8872,11 +11140,17 @@
       <c r="I189" t="s">
         <v>284</v>
       </c>
+      <c r="J189" t="s">
+        <v>1010</v>
+      </c>
       <c r="K189" t="s">
+        <v>822</v>
+      </c>
+      <c r="L189" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>285</v>
       </c>
@@ -8904,11 +11178,17 @@
       <c r="I190" t="s">
         <v>288</v>
       </c>
+      <c r="J190" t="s">
+        <v>1011</v>
+      </c>
       <c r="K190" t="s">
+        <v>823</v>
+      </c>
+      <c r="L190" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>289</v>
       </c>
@@ -8936,11 +11216,17 @@
       <c r="I191" t="s">
         <v>291</v>
       </c>
+      <c r="J191" t="s">
+        <v>1012</v>
+      </c>
       <c r="K191" t="s">
+        <v>824</v>
+      </c>
+      <c r="L191" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>292</v>
       </c>
@@ -8968,11 +11254,17 @@
       <c r="I192" t="s">
         <v>294</v>
       </c>
+      <c r="J192" t="s">
+        <v>1013</v>
+      </c>
       <c r="K192" t="s">
+        <v>825</v>
+      </c>
+      <c r="L192" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>295</v>
       </c>
@@ -9000,11 +11292,17 @@
       <c r="I193" t="s">
         <v>297</v>
       </c>
+      <c r="J193" t="s">
+        <v>1014</v>
+      </c>
       <c r="K193" t="s">
+        <v>826</v>
+      </c>
+      <c r="L193" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>298</v>
       </c>
@@ -9032,11 +11330,17 @@
       <c r="I194" t="s">
         <v>299</v>
       </c>
+      <c r="J194" t="s">
+        <v>1015</v>
+      </c>
       <c r="K194" t="s">
+        <v>827</v>
+      </c>
+      <c r="L194" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>300</v>
       </c>
@@ -9064,11 +11368,17 @@
       <c r="I195" t="s">
         <v>302</v>
       </c>
+      <c r="J195" t="s">
+        <v>1016</v>
+      </c>
       <c r="K195" t="s">
+        <v>828</v>
+      </c>
+      <c r="L195" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>303</v>
       </c>
@@ -9096,11 +11406,17 @@
       <c r="I196" t="s">
         <v>305</v>
       </c>
+      <c r="J196" t="s">
+        <v>1017</v>
+      </c>
       <c r="K196" t="s">
+        <v>829</v>
+      </c>
+      <c r="L196" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>306</v>
       </c>
@@ -9128,11 +11444,17 @@
       <c r="I197" t="s">
         <v>308</v>
       </c>
+      <c r="J197" t="s">
+        <v>1018</v>
+      </c>
       <c r="K197" t="s">
+        <v>830</v>
+      </c>
+      <c r="L197" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>309</v>
       </c>
@@ -9160,11 +11482,17 @@
       <c r="I198" t="s">
         <v>311</v>
       </c>
+      <c r="J198" t="s">
+        <v>1019</v>
+      </c>
       <c r="K198" t="s">
+        <v>831</v>
+      </c>
+      <c r="L198" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>312</v>
       </c>
@@ -9192,11 +11520,17 @@
       <c r="I199" t="s">
         <v>315</v>
       </c>
+      <c r="J199" t="s">
+        <v>1020</v>
+      </c>
       <c r="K199" t="s">
+        <v>832</v>
+      </c>
+      <c r="L199" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>316</v>
       </c>
@@ -9224,11 +11558,17 @@
       <c r="I200" t="s">
         <v>318</v>
       </c>
+      <c r="J200" t="s">
+        <v>1021</v>
+      </c>
       <c r="K200" t="s">
+        <v>833</v>
+      </c>
+      <c r="L200" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>319</v>
       </c>
@@ -9256,11 +11596,17 @@
       <c r="I201" t="s">
         <v>321</v>
       </c>
+      <c r="J201" t="s">
+        <v>1022</v>
+      </c>
       <c r="K201" t="s">
+        <v>834</v>
+      </c>
+      <c r="L201" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>325</v>
       </c>
@@ -9288,11 +11634,17 @@
       <c r="I202" t="s">
         <v>327</v>
       </c>
+      <c r="J202" t="s">
+        <v>1023</v>
+      </c>
       <c r="K202" t="s">
+        <v>835</v>
+      </c>
+      <c r="L202" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>328</v>
       </c>
@@ -9320,11 +11672,17 @@
       <c r="I203" t="s">
         <v>330</v>
       </c>
+      <c r="J203" t="s">
+        <v>1024</v>
+      </c>
       <c r="K203" t="s">
+        <v>836</v>
+      </c>
+      <c r="L203" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>331</v>
       </c>
@@ -9352,11 +11710,17 @@
       <c r="I204" t="s">
         <v>333</v>
       </c>
+      <c r="J204" t="s">
+        <v>1025</v>
+      </c>
       <c r="K204" t="s">
+        <v>837</v>
+      </c>
+      <c r="L204" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>334</v>
       </c>
@@ -9384,11 +11748,17 @@
       <c r="I205" t="s">
         <v>336</v>
       </c>
+      <c r="J205" t="s">
+        <v>1026</v>
+      </c>
       <c r="K205" t="s">
+        <v>838</v>
+      </c>
+      <c r="L205" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>337</v>
       </c>
@@ -9416,11 +11786,17 @@
       <c r="I206" t="s">
         <v>339</v>
       </c>
+      <c r="J206" t="s">
+        <v>1027</v>
+      </c>
       <c r="K206" t="s">
+        <v>839</v>
+      </c>
+      <c r="L206" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>340</v>
       </c>
@@ -9448,11 +11824,17 @@
       <c r="I207" t="s">
         <v>342</v>
       </c>
+      <c r="J207" t="s">
+        <v>1028</v>
+      </c>
       <c r="K207" t="s">
+        <v>840</v>
+      </c>
+      <c r="L207" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>343</v>
       </c>
@@ -9480,11 +11862,17 @@
       <c r="I208" t="s">
         <v>344</v>
       </c>
+      <c r="J208" t="s">
+        <v>1029</v>
+      </c>
       <c r="K208" t="s">
+        <v>841</v>
+      </c>
+      <c r="L208" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>345</v>
       </c>
@@ -9512,11 +11900,17 @@
       <c r="I209" t="s">
         <v>346</v>
       </c>
+      <c r="J209" t="s">
+        <v>1030</v>
+      </c>
       <c r="K209" t="s">
+        <v>842</v>
+      </c>
+      <c r="L209" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>347</v>
       </c>
@@ -9544,11 +11938,17 @@
       <c r="I210" t="s">
         <v>349</v>
       </c>
+      <c r="J210" t="s">
+        <v>1031</v>
+      </c>
       <c r="K210" t="s">
+        <v>843</v>
+      </c>
+      <c r="L210" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>350</v>
       </c>
@@ -9576,11 +11976,17 @@
       <c r="I211" t="s">
         <v>352</v>
       </c>
+      <c r="J211" t="s">
+        <v>1032</v>
+      </c>
       <c r="K211" t="s">
+        <v>844</v>
+      </c>
+      <c r="L211" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>353</v>
       </c>
@@ -9608,11 +12014,17 @@
       <c r="I212" t="s">
         <v>355</v>
       </c>
+      <c r="J212" t="s">
+        <v>1033</v>
+      </c>
       <c r="K212" t="s">
+        <v>845</v>
+      </c>
+      <c r="L212" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>356</v>
       </c>
@@ -9640,11 +12052,17 @@
       <c r="I213" t="s">
         <v>358</v>
       </c>
+      <c r="J213" t="s">
+        <v>1034</v>
+      </c>
       <c r="K213" t="s">
+        <v>846</v>
+      </c>
+      <c r="L213" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>359</v>
       </c>
@@ -9672,11 +12090,17 @@
       <c r="I214" t="s">
         <v>360</v>
       </c>
+      <c r="J214" t="s">
+        <v>1035</v>
+      </c>
       <c r="K214" t="s">
+        <v>847</v>
+      </c>
+      <c r="L214" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>361</v>
       </c>
@@ -9704,11 +12128,17 @@
       <c r="I215" t="s">
         <v>363</v>
       </c>
+      <c r="J215" t="s">
+        <v>1036</v>
+      </c>
       <c r="K215" t="s">
+        <v>848</v>
+      </c>
+      <c r="L215" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>364</v>
       </c>
@@ -9736,11 +12166,17 @@
       <c r="I216" t="s">
         <v>366</v>
       </c>
+      <c r="J216" t="s">
+        <v>1037</v>
+      </c>
       <c r="K216" t="s">
+        <v>849</v>
+      </c>
+      <c r="L216" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>367</v>
       </c>
@@ -9768,11 +12204,17 @@
       <c r="I217" t="s">
         <v>369</v>
       </c>
+      <c r="J217" t="s">
+        <v>1038</v>
+      </c>
       <c r="K217" t="s">
+        <v>850</v>
+      </c>
+      <c r="L217" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>370</v>
       </c>
@@ -9800,11 +12242,17 @@
       <c r="I218" t="s">
         <v>372</v>
       </c>
+      <c r="J218" t="s">
+        <v>1039</v>
+      </c>
       <c r="K218" t="s">
+        <v>851</v>
+      </c>
+      <c r="L218" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>373</v>
       </c>
@@ -9832,11 +12280,17 @@
       <c r="I219" t="s">
         <v>375</v>
       </c>
+      <c r="J219" t="s">
+        <v>1040</v>
+      </c>
       <c r="K219" t="s">
+        <v>852</v>
+      </c>
+      <c r="L219" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>377</v>
       </c>
@@ -9864,11 +12318,17 @@
       <c r="I220" t="s">
         <v>380</v>
       </c>
+      <c r="J220" t="s">
+        <v>1041</v>
+      </c>
       <c r="K220" t="s">
+        <v>853</v>
+      </c>
+      <c r="L220" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>381</v>
       </c>
@@ -9896,11 +12356,17 @@
       <c r="I221" t="s">
         <v>383</v>
       </c>
+      <c r="J221" t="s">
+        <v>1042</v>
+      </c>
       <c r="K221" t="s">
+        <v>854</v>
+      </c>
+      <c r="L221" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>384</v>
       </c>
@@ -9928,11 +12394,17 @@
       <c r="I222" t="s">
         <v>386</v>
       </c>
+      <c r="J222" t="s">
+        <v>1043</v>
+      </c>
       <c r="K222" t="s">
+        <v>855</v>
+      </c>
+      <c r="L222" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>387</v>
       </c>
@@ -9960,11 +12432,17 @@
       <c r="I223" t="s">
         <v>389</v>
       </c>
+      <c r="J223" t="s">
+        <v>1044</v>
+      </c>
       <c r="K223" t="s">
+        <v>856</v>
+      </c>
+      <c r="L223" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>390</v>
       </c>
@@ -9992,11 +12470,17 @@
       <c r="I224" t="s">
         <v>392</v>
       </c>
+      <c r="J224" t="s">
+        <v>1045</v>
+      </c>
       <c r="K224" t="s">
+        <v>857</v>
+      </c>
+      <c r="L224" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>393</v>
       </c>
@@ -10024,11 +12508,17 @@
       <c r="I225" t="s">
         <v>395</v>
       </c>
+      <c r="J225" t="s">
+        <v>1046</v>
+      </c>
       <c r="K225" t="s">
+        <v>858</v>
+      </c>
+      <c r="L225" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>396</v>
       </c>
@@ -10056,11 +12546,17 @@
       <c r="I226" t="s">
         <v>398</v>
       </c>
+      <c r="J226" t="s">
+        <v>1047</v>
+      </c>
       <c r="K226" t="s">
+        <v>859</v>
+      </c>
+      <c r="L226" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>399</v>
       </c>
@@ -10088,11 +12584,17 @@
       <c r="I227" t="s">
         <v>401</v>
       </c>
+      <c r="J227" t="s">
+        <v>1048</v>
+      </c>
       <c r="K227" t="s">
+        <v>860</v>
+      </c>
+      <c r="L227" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>402</v>
       </c>
@@ -10120,11 +12622,17 @@
       <c r="I228" t="s">
         <v>404</v>
       </c>
+      <c r="J228" t="s">
+        <v>1049</v>
+      </c>
       <c r="K228" t="s">
+        <v>861</v>
+      </c>
+      <c r="L228" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>405</v>
       </c>
@@ -10152,11 +12660,17 @@
       <c r="I229" t="s">
         <v>407</v>
       </c>
+      <c r="J229" t="s">
+        <v>1050</v>
+      </c>
       <c r="K229" t="s">
+        <v>862</v>
+      </c>
+      <c r="L229" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>408</v>
       </c>
@@ -10184,11 +12698,17 @@
       <c r="I230" t="s">
         <v>410</v>
       </c>
+      <c r="J230" t="s">
+        <v>1051</v>
+      </c>
       <c r="K230" t="s">
+        <v>863</v>
+      </c>
+      <c r="L230" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>411</v>
       </c>
@@ -10216,11 +12736,17 @@
       <c r="I231" t="s">
         <v>413</v>
       </c>
+      <c r="J231" t="s">
+        <v>1052</v>
+      </c>
       <c r="K231" t="s">
+        <v>864</v>
+      </c>
+      <c r="L231" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>414</v>
       </c>
@@ -10248,11 +12774,17 @@
       <c r="I232" t="s">
         <v>415</v>
       </c>
+      <c r="J232" t="s">
+        <v>1053</v>
+      </c>
       <c r="K232" t="s">
+        <v>865</v>
+      </c>
+      <c r="L232" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>417</v>
       </c>
@@ -10280,11 +12812,17 @@
       <c r="I233" t="s">
         <v>419</v>
       </c>
+      <c r="J233" t="s">
+        <v>1054</v>
+      </c>
       <c r="K233" t="s">
+        <v>866</v>
+      </c>
+      <c r="L233" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>420</v>
       </c>
@@ -10312,11 +12850,17 @@
       <c r="I234" t="s">
         <v>422</v>
       </c>
+      <c r="J234" t="s">
+        <v>1018</v>
+      </c>
       <c r="K234" t="s">
+        <v>830</v>
+      </c>
+      <c r="L234" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>423</v>
       </c>
@@ -10344,11 +12888,17 @@
       <c r="I235" t="s">
         <v>425</v>
       </c>
+      <c r="J235" t="s">
+        <v>1055</v>
+      </c>
       <c r="K235" t="s">
+        <v>867</v>
+      </c>
+      <c r="L235" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>426</v>
       </c>
@@ -10376,11 +12926,17 @@
       <c r="I236" t="s">
         <v>428</v>
       </c>
+      <c r="J236" t="s">
+        <v>1056</v>
+      </c>
       <c r="K236" t="s">
+        <v>868</v>
+      </c>
+      <c r="L236" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>429</v>
       </c>
@@ -10408,11 +12964,17 @@
       <c r="I237" t="s">
         <v>431</v>
       </c>
+      <c r="J237" t="s">
+        <v>1057</v>
+      </c>
       <c r="K237" t="s">
+        <v>869</v>
+      </c>
+      <c r="L237" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>432</v>
       </c>
@@ -10440,11 +13002,17 @@
       <c r="I238" t="s">
         <v>434</v>
       </c>
+      <c r="J238" t="s">
+        <v>1052</v>
+      </c>
       <c r="K238" t="s">
+        <v>864</v>
+      </c>
+      <c r="L238" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>435</v>
       </c>
@@ -10472,11 +13040,17 @@
       <c r="I239" t="s">
         <v>437</v>
       </c>
+      <c r="J239" t="s">
+        <v>1058</v>
+      </c>
       <c r="K239" t="s">
+        <v>870</v>
+      </c>
+      <c r="L239" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>438</v>
       </c>
@@ -10504,11 +13078,17 @@
       <c r="I240" t="s">
         <v>440</v>
       </c>
+      <c r="J240" t="s">
+        <v>1059</v>
+      </c>
       <c r="K240" t="s">
+        <v>871</v>
+      </c>
+      <c r="L240" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>441</v>
       </c>
@@ -10536,11 +13116,17 @@
       <c r="I241" t="s">
         <v>443</v>
       </c>
+      <c r="J241" t="s">
+        <v>1060</v>
+      </c>
       <c r="K241" t="s">
+        <v>872</v>
+      </c>
+      <c r="L241" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>444</v>
       </c>
@@ -10568,11 +13154,17 @@
       <c r="I242" t="s">
         <v>446</v>
       </c>
+      <c r="J242" t="s">
+        <v>1061</v>
+      </c>
       <c r="K242" t="s">
+        <v>873</v>
+      </c>
+      <c r="L242" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>447</v>
       </c>
@@ -10600,11 +13192,17 @@
       <c r="I243" t="s">
         <v>449</v>
       </c>
+      <c r="J243" t="s">
+        <v>1062</v>
+      </c>
       <c r="K243" t="s">
+        <v>874</v>
+      </c>
+      <c r="L243" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>450</v>
       </c>
@@ -10632,11 +13230,17 @@
       <c r="I244" t="s">
         <v>452</v>
       </c>
+      <c r="J244" t="s">
+        <v>1063</v>
+      </c>
       <c r="K244" t="s">
+        <v>875</v>
+      </c>
+      <c r="L244" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>453</v>
       </c>
@@ -10664,11 +13268,17 @@
       <c r="I245" t="s">
         <v>455</v>
       </c>
+      <c r="J245" t="s">
+        <v>1064</v>
+      </c>
       <c r="K245" t="s">
+        <v>876</v>
+      </c>
+      <c r="L245" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>456</v>
       </c>
@@ -10696,11 +13306,17 @@
       <c r="I246" t="s">
         <v>458</v>
       </c>
+      <c r="J246" t="s">
+        <v>1065</v>
+      </c>
       <c r="K246" t="s">
+        <v>877</v>
+      </c>
+      <c r="L246" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>334</v>
       </c>
@@ -10728,11 +13344,17 @@
       <c r="I247" t="s">
         <v>336</v>
       </c>
+      <c r="J247" t="s">
+        <v>1066</v>
+      </c>
       <c r="K247" t="s">
+        <v>838</v>
+      </c>
+      <c r="L247" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>461</v>
       </c>
@@ -10760,11 +13382,17 @@
       <c r="I248" t="s">
         <v>463</v>
       </c>
+      <c r="J248" t="s">
+        <v>1067</v>
+      </c>
       <c r="K248" t="s">
+        <v>878</v>
+      </c>
+      <c r="L248" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>464</v>
       </c>
@@ -10792,11 +13420,17 @@
       <c r="I249" t="s">
         <v>466</v>
       </c>
+      <c r="J249" t="s">
+        <v>1068</v>
+      </c>
       <c r="K249" t="s">
+        <v>879</v>
+      </c>
+      <c r="L249" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>467</v>
       </c>
@@ -10824,11 +13458,17 @@
       <c r="I250" t="s">
         <v>469</v>
       </c>
+      <c r="J250" t="s">
+        <v>1069</v>
+      </c>
       <c r="K250" t="s">
+        <v>880</v>
+      </c>
+      <c r="L250" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>470</v>
       </c>
@@ -10856,11 +13496,17 @@
       <c r="I251" t="s">
         <v>471</v>
       </c>
+      <c r="J251" t="s">
+        <v>1070</v>
+      </c>
       <c r="K251" t="s">
+        <v>881</v>
+      </c>
+      <c r="L251" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>347</v>
       </c>
@@ -10888,11 +13534,17 @@
       <c r="I252" t="s">
         <v>349</v>
       </c>
+      <c r="J252" t="s">
+        <v>1031</v>
+      </c>
       <c r="K252" t="s">
+        <v>843</v>
+      </c>
+      <c r="L252" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>473</v>
       </c>
@@ -10920,11 +13572,17 @@
       <c r="I253" t="s">
         <v>475</v>
       </c>
+      <c r="J253" t="s">
+        <v>1071</v>
+      </c>
       <c r="K253" t="s">
+        <v>882</v>
+      </c>
+      <c r="L253" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>476</v>
       </c>
@@ -10952,11 +13610,17 @@
       <c r="I254" t="s">
         <v>478</v>
       </c>
+      <c r="J254" t="s">
+        <v>1072</v>
+      </c>
       <c r="K254" t="s">
+        <v>883</v>
+      </c>
+      <c r="L254" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>479</v>
       </c>
@@ -10984,11 +13648,17 @@
       <c r="I255" t="s">
         <v>481</v>
       </c>
+      <c r="J255" t="s">
+        <v>1073</v>
+      </c>
       <c r="K255" t="s">
+        <v>884</v>
+      </c>
+      <c r="L255" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>482</v>
       </c>
@@ -11016,11 +13686,17 @@
       <c r="I256" t="s">
         <v>484</v>
       </c>
+      <c r="J256" t="s">
+        <v>1074</v>
+      </c>
       <c r="K256" t="s">
+        <v>885</v>
+      </c>
+      <c r="L256" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>485</v>
       </c>
@@ -11048,11 +13724,17 @@
       <c r="I257" t="s">
         <v>487</v>
       </c>
+      <c r="J257" t="s">
+        <v>1075</v>
+      </c>
       <c r="K257" t="s">
+        <v>886</v>
+      </c>
+      <c r="L257" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>488</v>
       </c>
@@ -11080,11 +13762,17 @@
       <c r="I258" t="s">
         <v>490</v>
       </c>
+      <c r="J258" t="s">
+        <v>1076</v>
+      </c>
       <c r="K258" t="s">
+        <v>887</v>
+      </c>
+      <c r="L258" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>491</v>
       </c>
@@ -11112,11 +13800,17 @@
       <c r="I259" t="s">
         <v>493</v>
       </c>
+      <c r="J259" t="s">
+        <v>1077</v>
+      </c>
       <c r="K259" t="s">
+        <v>888</v>
+      </c>
+      <c r="L259" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>494</v>
       </c>
@@ -11144,11 +13838,17 @@
       <c r="I260" t="s">
         <v>496</v>
       </c>
+      <c r="J260" t="s">
+        <v>1078</v>
+      </c>
       <c r="K260" t="s">
+        <v>889</v>
+      </c>
+      <c r="L260" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>497</v>
       </c>
@@ -11176,11 +13876,17 @@
       <c r="I261" t="s">
         <v>499</v>
       </c>
+      <c r="J261" t="s">
+        <v>1079</v>
+      </c>
       <c r="K261" t="s">
+        <v>890</v>
+      </c>
+      <c r="L261" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>500</v>
       </c>
@@ -11208,11 +13914,17 @@
       <c r="I262" t="s">
         <v>502</v>
       </c>
+      <c r="J262" t="s">
+        <v>1080</v>
+      </c>
       <c r="K262" t="s">
+        <v>891</v>
+      </c>
+      <c r="L262" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>503</v>
       </c>
@@ -11240,11 +13952,17 @@
       <c r="I263" t="s">
         <v>505</v>
       </c>
+      <c r="J263" t="s">
+        <v>1081</v>
+      </c>
       <c r="K263" t="s">
+        <v>892</v>
+      </c>
+      <c r="L263" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>506</v>
       </c>
@@ -11272,11 +13990,17 @@
       <c r="I264" t="s">
         <v>509</v>
       </c>
+      <c r="J264" t="s">
+        <v>1082</v>
+      </c>
       <c r="K264" t="s">
+        <v>893</v>
+      </c>
+      <c r="L264" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>510</v>
       </c>
@@ -11304,11 +14028,17 @@
       <c r="I265" t="s">
         <v>512</v>
       </c>
+      <c r="J265" t="s">
+        <v>1083</v>
+      </c>
       <c r="K265" t="s">
+        <v>894</v>
+      </c>
+      <c r="L265" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>513</v>
       </c>
@@ -11336,11 +14066,17 @@
       <c r="I266" t="s">
         <v>515</v>
       </c>
+      <c r="J266" t="s">
+        <v>1084</v>
+      </c>
       <c r="K266" t="s">
+        <v>895</v>
+      </c>
+      <c r="L266" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>516</v>
       </c>
@@ -11368,11 +14104,17 @@
       <c r="I267" t="s">
         <v>518</v>
       </c>
+      <c r="J267" t="s">
+        <v>1085</v>
+      </c>
       <c r="K267" t="s">
+        <v>896</v>
+      </c>
+      <c r="L267" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>519</v>
       </c>
@@ -11400,11 +14142,17 @@
       <c r="I268" t="s">
         <v>521</v>
       </c>
+      <c r="J268" t="s">
+        <v>1086</v>
+      </c>
       <c r="K268" t="s">
+        <v>897</v>
+      </c>
+      <c r="L268" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>522</v>
       </c>
@@ -11432,11 +14180,17 @@
       <c r="I269" t="s">
         <v>524</v>
       </c>
+      <c r="J269" t="s">
+        <v>1087</v>
+      </c>
       <c r="K269" t="s">
+        <v>898</v>
+      </c>
+      <c r="L269" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>525</v>
       </c>
@@ -11464,11 +14218,17 @@
       <c r="I270" t="s">
         <v>527</v>
       </c>
+      <c r="J270" t="s">
+        <v>1088</v>
+      </c>
       <c r="K270" t="s">
+        <v>899</v>
+      </c>
+      <c r="L270" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>528</v>
       </c>
@@ -11496,11 +14256,17 @@
       <c r="I271" t="s">
         <v>530</v>
       </c>
+      <c r="J271" t="s">
+        <v>1089</v>
+      </c>
       <c r="K271" t="s">
+        <v>900</v>
+      </c>
+      <c r="L271" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>531</v>
       </c>
@@ -11528,11 +14294,17 @@
       <c r="I272" t="s">
         <v>533</v>
       </c>
+      <c r="J272" t="s">
+        <v>1090</v>
+      </c>
       <c r="K272" t="s">
+        <v>901</v>
+      </c>
+      <c r="L272" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>534</v>
       </c>
@@ -11560,11 +14332,17 @@
       <c r="I273" t="s">
         <v>536</v>
       </c>
+      <c r="J273" t="s">
+        <v>1091</v>
+      </c>
       <c r="K273" t="s">
+        <v>902</v>
+      </c>
+      <c r="L273" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>537</v>
       </c>
@@ -11592,11 +14370,17 @@
       <c r="I274" t="s">
         <v>539</v>
       </c>
+      <c r="J274" t="s">
+        <v>1092</v>
+      </c>
       <c r="K274" t="s">
+        <v>903</v>
+      </c>
+      <c r="L274" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>540</v>
       </c>
@@ -11624,11 +14408,17 @@
       <c r="I275" t="s">
         <v>542</v>
       </c>
+      <c r="J275" t="s">
+        <v>1093</v>
+      </c>
       <c r="K275" t="s">
+        <v>904</v>
+      </c>
+      <c r="L275" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>543</v>
       </c>
@@ -11656,11 +14446,17 @@
       <c r="I276" t="s">
         <v>545</v>
       </c>
+      <c r="J276" t="s">
+        <v>1094</v>
+      </c>
       <c r="K276" t="s">
+        <v>905</v>
+      </c>
+      <c r="L276" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>546</v>
       </c>
@@ -11688,11 +14484,17 @@
       <c r="I277" t="s">
         <v>548</v>
       </c>
+      <c r="J277" t="s">
+        <v>1095</v>
+      </c>
       <c r="K277" t="s">
+        <v>906</v>
+      </c>
+      <c r="L277" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>549</v>
       </c>
@@ -11720,11 +14522,17 @@
       <c r="I278" t="s">
         <v>551</v>
       </c>
+      <c r="J278" t="s">
+        <v>1096</v>
+      </c>
       <c r="K278" t="s">
+        <v>907</v>
+      </c>
+      <c r="L278" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>552</v>
       </c>
@@ -11752,11 +14560,17 @@
       <c r="I279" t="s">
         <v>554</v>
       </c>
+      <c r="J279" t="s">
+        <v>1097</v>
+      </c>
       <c r="K279" t="s">
+        <v>908</v>
+      </c>
+      <c r="L279" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>555</v>
       </c>
@@ -11784,11 +14598,17 @@
       <c r="I280" t="s">
         <v>557</v>
       </c>
+      <c r="J280" t="s">
+        <v>1098</v>
+      </c>
       <c r="K280" t="s">
+        <v>909</v>
+      </c>
+      <c r="L280" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>558</v>
       </c>
@@ -11816,11 +14636,17 @@
       <c r="I281" t="s">
         <v>560</v>
       </c>
+      <c r="J281" t="s">
+        <v>1099</v>
+      </c>
       <c r="K281" t="s">
+        <v>910</v>
+      </c>
+      <c r="L281" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>561</v>
       </c>
@@ -11848,11 +14674,17 @@
       <c r="I282" t="s">
         <v>563</v>
       </c>
+      <c r="J282" t="s">
+        <v>1100</v>
+      </c>
       <c r="K282" t="s">
+        <v>911</v>
+      </c>
+      <c r="L282" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>564</v>
       </c>
@@ -11880,11 +14712,17 @@
       <c r="I283" t="s">
         <v>566</v>
       </c>
+      <c r="J283" t="s">
+        <v>1101</v>
+      </c>
       <c r="K283" t="s">
+        <v>912</v>
+      </c>
+      <c r="L283" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>567</v>
       </c>
@@ -11912,11 +14750,17 @@
       <c r="I284" t="s">
         <v>568</v>
       </c>
+      <c r="J284" t="s">
+        <v>1102</v>
+      </c>
       <c r="K284" t="s">
+        <v>913</v>
+      </c>
+      <c r="L284" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>569</v>
       </c>
@@ -11944,11 +14788,17 @@
       <c r="I285" t="s">
         <v>571</v>
       </c>
+      <c r="J285" t="s">
+        <v>1103</v>
+      </c>
       <c r="K285" t="s">
+        <v>914</v>
+      </c>
+      <c r="L285" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>572</v>
       </c>
@@ -11976,11 +14826,17 @@
       <c r="I286" t="s">
         <v>574</v>
       </c>
+      <c r="J286" t="s">
+        <v>1104</v>
+      </c>
       <c r="K286" t="s">
+        <v>915</v>
+      </c>
+      <c r="L286" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>575</v>
       </c>
@@ -12008,11 +14864,17 @@
       <c r="I287" t="s">
         <v>577</v>
       </c>
+      <c r="J287" t="s">
+        <v>1105</v>
+      </c>
       <c r="K287" t="s">
+        <v>916</v>
+      </c>
+      <c r="L287" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>578</v>
       </c>
@@ -12040,11 +14902,17 @@
       <c r="I288" t="s">
         <v>580</v>
       </c>
+      <c r="J288" t="s">
+        <v>1097</v>
+      </c>
       <c r="K288" t="s">
+        <v>908</v>
+      </c>
+      <c r="L288" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>581</v>
       </c>
@@ -12072,11 +14940,17 @@
       <c r="I289" t="s">
         <v>583</v>
       </c>
+      <c r="J289" t="s">
+        <v>1106</v>
+      </c>
       <c r="K289" t="s">
+        <v>917</v>
+      </c>
+      <c r="L289" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>584</v>
       </c>
@@ -12104,11 +14978,17 @@
       <c r="I290" t="s">
         <v>586</v>
       </c>
+      <c r="J290" t="s">
+        <v>1107</v>
+      </c>
       <c r="K290" t="s">
+        <v>918</v>
+      </c>
+      <c r="L290" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>587</v>
       </c>
@@ -12136,11 +15016,17 @@
       <c r="I291" t="s">
         <v>589</v>
       </c>
+      <c r="J291" t="s">
+        <v>1108</v>
+      </c>
       <c r="K291" t="s">
+        <v>919</v>
+      </c>
+      <c r="L291" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>590</v>
       </c>
@@ -12168,11 +15054,17 @@
       <c r="I292" t="s">
         <v>592</v>
       </c>
+      <c r="J292" t="s">
+        <v>1109</v>
+      </c>
       <c r="K292" t="s">
+        <v>920</v>
+      </c>
+      <c r="L292" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>464</v>
       </c>
@@ -12200,11 +15092,17 @@
       <c r="I293" t="s">
         <v>594</v>
       </c>
+      <c r="J293" t="s">
+        <v>1068</v>
+      </c>
       <c r="K293" t="s">
+        <v>879</v>
+      </c>
+      <c r="L293" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>595</v>
       </c>
@@ -12232,11 +15130,17 @@
       <c r="I294" t="s">
         <v>597</v>
       </c>
+      <c r="J294" t="s">
+        <v>1034</v>
+      </c>
       <c r="K294" t="s">
+        <v>921</v>
+      </c>
+      <c r="L294" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>598</v>
       </c>
@@ -12264,11 +15168,17 @@
       <c r="I295" t="s">
         <v>600</v>
       </c>
+      <c r="J295" t="s">
+        <v>1110</v>
+      </c>
       <c r="K295" t="s">
+        <v>922</v>
+      </c>
+      <c r="L295" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>601</v>
       </c>
@@ -12296,11 +15206,17 @@
       <c r="I296" t="s">
         <v>603</v>
       </c>
+      <c r="J296" t="s">
+        <v>1111</v>
+      </c>
       <c r="K296" t="s">
+        <v>923</v>
+      </c>
+      <c r="L296" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>604</v>
       </c>
@@ -12328,11 +15244,17 @@
       <c r="I297" t="s">
         <v>606</v>
       </c>
+      <c r="J297" t="s">
+        <v>1112</v>
+      </c>
       <c r="K297" t="s">
+        <v>924</v>
+      </c>
+      <c r="L297" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>607</v>
       </c>
@@ -12360,11 +15282,17 @@
       <c r="I298" t="s">
         <v>609</v>
       </c>
+      <c r="J298" t="s">
+        <v>1113</v>
+      </c>
       <c r="K298" t="s">
+        <v>925</v>
+      </c>
+      <c r="L298" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>610</v>
       </c>
@@ -12392,11 +15320,17 @@
       <c r="I299" t="s">
         <v>612</v>
       </c>
+      <c r="J299" t="s">
+        <v>1114</v>
+      </c>
       <c r="K299" t="s">
+        <v>926</v>
+      </c>
+      <c r="L299" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>613</v>
       </c>
@@ -12424,11 +15358,17 @@
       <c r="I300" t="s">
         <v>614</v>
       </c>
+      <c r="J300" t="s">
+        <v>1115</v>
+      </c>
       <c r="K300" t="s">
+        <v>927</v>
+      </c>
+      <c r="L300" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>615</v>
       </c>
@@ -12456,11 +15396,17 @@
       <c r="I301" t="s">
         <v>617</v>
       </c>
+      <c r="J301" t="s">
+        <v>1116</v>
+      </c>
       <c r="K301" t="s">
+        <v>928</v>
+      </c>
+      <c r="L301" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>618</v>
       </c>
@@ -12488,11 +15434,17 @@
       <c r="I302" t="s">
         <v>620</v>
       </c>
+      <c r="J302" t="s">
+        <v>1117</v>
+      </c>
       <c r="K302" t="s">
+        <v>929</v>
+      </c>
+      <c r="L302" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>621</v>
       </c>
@@ -12520,11 +15472,17 @@
       <c r="I303" t="s">
         <v>623</v>
       </c>
+      <c r="J303" t="s">
+        <v>1118</v>
+      </c>
       <c r="K303" t="s">
+        <v>930</v>
+      </c>
+      <c r="L303" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>624</v>
       </c>
@@ -12552,11 +15510,17 @@
       <c r="I304" t="s">
         <v>626</v>
       </c>
+      <c r="J304" t="s">
+        <v>1119</v>
+      </c>
       <c r="K304" t="s">
+        <v>931</v>
+      </c>
+      <c r="L304" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>627</v>
       </c>
@@ -12584,11 +15548,17 @@
       <c r="I305" t="s">
         <v>629</v>
       </c>
+      <c r="J305" t="s">
+        <v>1120</v>
+      </c>
       <c r="K305" t="s">
+        <v>932</v>
+      </c>
+      <c r="L305" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>630</v>
       </c>
@@ -12616,11 +15586,17 @@
       <c r="I306" t="s">
         <v>632</v>
       </c>
+      <c r="J306" t="s">
+        <v>1121</v>
+      </c>
       <c r="K306" t="s">
+        <v>933</v>
+      </c>
+      <c r="L306" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>633</v>
       </c>
@@ -12648,11 +15624,17 @@
       <c r="I307" t="s">
         <v>637</v>
       </c>
+      <c r="J307" t="s">
+        <v>1122</v>
+      </c>
       <c r="K307" t="s">
+        <v>934</v>
+      </c>
+      <c r="L307" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>638</v>
       </c>
@@ -12680,11 +15662,17 @@
       <c r="I308" t="s">
         <v>640</v>
       </c>
+      <c r="J308" t="s">
+        <v>1123</v>
+      </c>
       <c r="K308" t="s">
+        <v>935</v>
+      </c>
+      <c r="L308" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>641</v>
       </c>
@@ -12712,11 +15700,17 @@
       <c r="I309" t="s">
         <v>644</v>
       </c>
+      <c r="J309" t="s">
+        <v>1124</v>
+      </c>
       <c r="K309" t="s">
+        <v>936</v>
+      </c>
+      <c r="L309" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>645</v>
       </c>
@@ -12744,11 +15738,17 @@
       <c r="I310" t="s">
         <v>648</v>
       </c>
+      <c r="J310" t="s">
+        <v>1125</v>
+      </c>
       <c r="K310" t="s">
+        <v>937</v>
+      </c>
+      <c r="L310" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>649</v>
       </c>
@@ -12776,11 +15776,17 @@
       <c r="I311" t="s">
         <v>652</v>
       </c>
+      <c r="J311" t="s">
+        <v>1126</v>
+      </c>
       <c r="K311" t="s">
+        <v>938</v>
+      </c>
+      <c r="L311" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>653</v>
       </c>
@@ -12808,11 +15814,17 @@
       <c r="I312" t="s">
         <v>656</v>
       </c>
+      <c r="J312" t="s">
+        <v>1127</v>
+      </c>
       <c r="K312" t="s">
+        <v>939</v>
+      </c>
+      <c r="L312" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>657</v>
       </c>
@@ -12840,11 +15852,17 @@
       <c r="I313" t="s">
         <v>660</v>
       </c>
+      <c r="J313" t="s">
+        <v>1128</v>
+      </c>
       <c r="K313" t="s">
+        <v>940</v>
+      </c>
+      <c r="L313" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>661</v>
       </c>
@@ -12872,11 +15890,17 @@
       <c r="I314" t="s">
         <v>663</v>
       </c>
+      <c r="J314" t="s">
+        <v>1129</v>
+      </c>
       <c r="K314" t="s">
+        <v>941</v>
+      </c>
+      <c r="L314" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>664</v>
       </c>
@@ -12904,11 +15928,17 @@
       <c r="I315" t="s">
         <v>666</v>
       </c>
+      <c r="J315" t="s">
+        <v>1130</v>
+      </c>
       <c r="K315" t="s">
+        <v>942</v>
+      </c>
+      <c r="L315" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>667</v>
       </c>
@@ -12936,11 +15966,17 @@
       <c r="I316" t="s">
         <v>669</v>
       </c>
+      <c r="J316" t="s">
+        <v>1131</v>
+      </c>
       <c r="K316" t="s">
+        <v>943</v>
+      </c>
+      <c r="L316" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>670</v>
       </c>
@@ -12968,11 +16004,17 @@
       <c r="I317" t="s">
         <v>672</v>
       </c>
+      <c r="J317" t="s">
+        <v>1132</v>
+      </c>
       <c r="K317" t="s">
+        <v>944</v>
+      </c>
+      <c r="L317" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>673</v>
       </c>
@@ -13000,11 +16042,17 @@
       <c r="I318" t="s">
         <v>675</v>
       </c>
+      <c r="J318" t="s">
+        <v>1133</v>
+      </c>
       <c r="K318" t="s">
+        <v>945</v>
+      </c>
+      <c r="L318" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>676</v>
       </c>
@@ -13032,11 +16080,17 @@
       <c r="I319" t="s">
         <v>678</v>
       </c>
+      <c r="J319" t="s">
+        <v>1134</v>
+      </c>
       <c r="K319" t="s">
+        <v>946</v>
+      </c>
+      <c r="L319" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>679</v>
       </c>
@@ -13064,11 +16118,17 @@
       <c r="I320" t="s">
         <v>681</v>
       </c>
+      <c r="J320" t="s">
+        <v>1135</v>
+      </c>
       <c r="K320" t="s">
+        <v>947</v>
+      </c>
+      <c r="L320" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>682</v>
       </c>
@@ -13096,11 +16156,17 @@
       <c r="I321" t="s">
         <v>685</v>
       </c>
+      <c r="J321" t="s">
+        <v>1136</v>
+      </c>
       <c r="K321" t="s">
+        <v>948</v>
+      </c>
+      <c r="L321" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>686</v>
       </c>
@@ -13128,11 +16194,17 @@
       <c r="I322" t="s">
         <v>688</v>
       </c>
+      <c r="J322" t="s">
+        <v>1137</v>
+      </c>
       <c r="K322" t="s">
+        <v>949</v>
+      </c>
+      <c r="L322" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>689</v>
       </c>
@@ -13160,11 +16232,17 @@
       <c r="I323" t="s">
         <v>691</v>
       </c>
+      <c r="J323" t="s">
+        <v>1138</v>
+      </c>
       <c r="K323" t="s">
+        <v>950</v>
+      </c>
+      <c r="L323" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>692</v>
       </c>
@@ -13192,11 +16270,17 @@
       <c r="I324" t="s">
         <v>694</v>
       </c>
+      <c r="J324" t="s">
+        <v>1139</v>
+      </c>
       <c r="K324" t="s">
+        <v>951</v>
+      </c>
+      <c r="L324" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>695</v>
       </c>
@@ -13224,11 +16308,17 @@
       <c r="I325" t="s">
         <v>697</v>
       </c>
+      <c r="J325" t="s">
+        <v>1140</v>
+      </c>
       <c r="K325" t="s">
+        <v>952</v>
+      </c>
+      <c r="L325" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>698</v>
       </c>
@@ -13256,11 +16346,17 @@
       <c r="I326" t="s">
         <v>700</v>
       </c>
+      <c r="J326" t="s">
+        <v>1141</v>
+      </c>
       <c r="K326" t="s">
+        <v>953</v>
+      </c>
+      <c r="L326" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>701</v>
       </c>
@@ -13288,11 +16384,17 @@
       <c r="I327" t="s">
         <v>703</v>
       </c>
+      <c r="J327" t="s">
+        <v>1142</v>
+      </c>
       <c r="K327" t="s">
+        <v>954</v>
+      </c>
+      <c r="L327" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>704</v>
       </c>
@@ -13320,11 +16422,17 @@
       <c r="I328" t="s">
         <v>706</v>
       </c>
+      <c r="J328" t="s">
+        <v>1143</v>
+      </c>
       <c r="K328" t="s">
+        <v>955</v>
+      </c>
+      <c r="L328" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>707</v>
       </c>
@@ -13352,11 +16460,17 @@
       <c r="I329" t="s">
         <v>709</v>
       </c>
+      <c r="J329" t="s">
+        <v>1144</v>
+      </c>
       <c r="K329" t="s">
+        <v>956</v>
+      </c>
+      <c r="L329" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>710</v>
       </c>
@@ -13384,11 +16498,17 @@
       <c r="I330" t="s">
         <v>712</v>
       </c>
+      <c r="J330" t="s">
+        <v>1145</v>
+      </c>
       <c r="K330" t="s">
+        <v>957</v>
+      </c>
+      <c r="L330" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>713</v>
       </c>
@@ -13416,11 +16536,17 @@
       <c r="I331" t="s">
         <v>714</v>
       </c>
+      <c r="J331" t="s">
+        <v>1146</v>
+      </c>
       <c r="K331" t="s">
+        <v>958</v>
+      </c>
+      <c r="L331" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>715</v>
       </c>
@@ -13448,11 +16574,17 @@
       <c r="I332" t="s">
         <v>717</v>
       </c>
+      <c r="J332" t="s">
+        <v>1147</v>
+      </c>
       <c r="K332" t="s">
+        <v>959</v>
+      </c>
+      <c r="L332" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>718</v>
       </c>
@@ -13480,11 +16612,17 @@
       <c r="I333" t="s">
         <v>720</v>
       </c>
+      <c r="J333" t="s">
+        <v>1148</v>
+      </c>
       <c r="K333" t="s">
+        <v>960</v>
+      </c>
+      <c r="L333" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>721</v>
       </c>
@@ -13512,11 +16650,17 @@
       <c r="I334" t="s">
         <v>723</v>
       </c>
+      <c r="J334" t="s">
+        <v>1149</v>
+      </c>
       <c r="K334" t="s">
+        <v>961</v>
+      </c>
+      <c r="L334" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>724</v>
       </c>
@@ -13544,11 +16688,17 @@
       <c r="I335" t="s">
         <v>726</v>
       </c>
+      <c r="J335" t="s">
+        <v>1150</v>
+      </c>
       <c r="K335" t="s">
+        <v>962</v>
+      </c>
+      <c r="L335" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>727</v>
       </c>
@@ -13576,11 +16726,17 @@
       <c r="I336" t="s">
         <v>730</v>
       </c>
+      <c r="J336" t="s">
+        <v>1151</v>
+      </c>
       <c r="K336" t="s">
+        <v>963</v>
+      </c>
+      <c r="L336" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>731</v>
       </c>
@@ -13608,11 +16764,17 @@
       <c r="I337" t="s">
         <v>733</v>
       </c>
+      <c r="J337" t="s">
+        <v>1152</v>
+      </c>
       <c r="K337" t="s">
+        <v>964</v>
+      </c>
+      <c r="L337" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>734</v>
       </c>
@@ -13640,11 +16802,17 @@
       <c r="I338" t="s">
         <v>736</v>
       </c>
+      <c r="J338" t="s">
+        <v>1153</v>
+      </c>
       <c r="K338" t="s">
+        <v>965</v>
+      </c>
+      <c r="L338" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>737</v>
       </c>
@@ -13672,11 +16840,17 @@
       <c r="I339" t="s">
         <v>739</v>
       </c>
+      <c r="J339" t="s">
+        <v>1154</v>
+      </c>
       <c r="K339" t="s">
+        <v>966</v>
+      </c>
+      <c r="L339" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>740</v>
       </c>
@@ -13704,11 +16878,17 @@
       <c r="I340" t="s">
         <v>742</v>
       </c>
+      <c r="J340" t="s">
+        <v>1155</v>
+      </c>
       <c r="K340" t="s">
+        <v>967</v>
+      </c>
+      <c r="L340" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>743</v>
       </c>
@@ -13736,11 +16916,17 @@
       <c r="I341" t="s">
         <v>745</v>
       </c>
+      <c r="J341" t="s">
+        <v>1156</v>
+      </c>
       <c r="K341" t="s">
+        <v>968</v>
+      </c>
+      <c r="L341" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>746</v>
       </c>
@@ -13768,11 +16954,17 @@
       <c r="I342" t="s">
         <v>748</v>
       </c>
+      <c r="J342" t="s">
+        <v>1157</v>
+      </c>
       <c r="K342" t="s">
+        <v>969</v>
+      </c>
+      <c r="L342" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>749</v>
       </c>
@@ -13800,11 +16992,17 @@
       <c r="I343" t="s">
         <v>751</v>
       </c>
+      <c r="J343" t="s">
+        <v>1158</v>
+      </c>
       <c r="K343" t="s">
+        <v>970</v>
+      </c>
+      <c r="L343" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>752</v>
       </c>
@@ -13832,11 +17030,17 @@
       <c r="I344" t="s">
         <v>754</v>
       </c>
+      <c r="J344" t="s">
+        <v>1159</v>
+      </c>
       <c r="K344" t="s">
+        <v>971</v>
+      </c>
+      <c r="L344" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>755</v>
       </c>
@@ -13864,11 +17068,17 @@
       <c r="I345" t="s">
         <v>757</v>
       </c>
+      <c r="J345" t="s">
+        <v>1160</v>
+      </c>
       <c r="K345" t="s">
+        <v>972</v>
+      </c>
+      <c r="L345" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>758</v>
       </c>
@@ -13896,11 +17106,17 @@
       <c r="I346" t="s">
         <v>760</v>
       </c>
+      <c r="J346" t="s">
+        <v>1161</v>
+      </c>
       <c r="K346" t="s">
+        <v>973</v>
+      </c>
+      <c r="L346" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>761</v>
       </c>
@@ -13928,11 +17144,17 @@
       <c r="I347" t="s">
         <v>763</v>
       </c>
+      <c r="J347" t="s">
+        <v>1162</v>
+      </c>
       <c r="K347" t="s">
+        <v>974</v>
+      </c>
+      <c r="L347" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>764</v>
       </c>
@@ -13960,11 +17182,17 @@
       <c r="I348" t="s">
         <v>766</v>
       </c>
+      <c r="J348" t="s">
+        <v>1163</v>
+      </c>
       <c r="K348" t="s">
+        <v>975</v>
+      </c>
+      <c r="L348" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>767</v>
       </c>
@@ -13992,11 +17220,17 @@
       <c r="I349" t="s">
         <v>769</v>
       </c>
+      <c r="J349" t="s">
+        <v>1164</v>
+      </c>
       <c r="K349" t="s">
+        <v>976</v>
+      </c>
+      <c r="L349" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>770</v>
       </c>
@@ -14024,11 +17258,17 @@
       <c r="I350" t="s">
         <v>772</v>
       </c>
+      <c r="J350" t="s">
+        <v>1165</v>
+      </c>
       <c r="K350" t="s">
+        <v>977</v>
+      </c>
+      <c r="L350" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>773</v>
       </c>
@@ -14054,13 +17294,19 @@
         <v>20</v>
       </c>
       <c r="I351" t="s">
-        <v>773</v>
+        <v>1181</v>
+      </c>
+      <c r="J351" t="s">
+        <v>1166</v>
       </c>
       <c r="K351" t="s">
+        <v>978</v>
+      </c>
+      <c r="L351" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>775</v>
       </c>
@@ -14086,13 +17332,19 @@
         <v>20</v>
       </c>
       <c r="I352" t="s">
-        <v>775</v>
+        <v>1182</v>
+      </c>
+      <c r="J352" t="s">
+        <v>1167</v>
       </c>
       <c r="K352" t="s">
+        <v>979</v>
+      </c>
+      <c r="L352" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>777</v>
       </c>
@@ -14118,13 +17370,19 @@
         <v>20</v>
       </c>
       <c r="I353" t="s">
-        <v>777</v>
+        <v>1183</v>
+      </c>
+      <c r="J353" t="s">
+        <v>1168</v>
       </c>
       <c r="K353" t="s">
+        <v>980</v>
+      </c>
+      <c r="L353" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>779</v>
       </c>
@@ -14150,13 +17408,19 @@
         <v>20</v>
       </c>
       <c r="I354" t="s">
-        <v>779</v>
+        <v>1184</v>
+      </c>
+      <c r="J354" t="s">
+        <v>1169</v>
       </c>
       <c r="K354" t="s">
+        <v>981</v>
+      </c>
+      <c r="L354" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>781</v>
       </c>
@@ -14182,13 +17446,19 @@
         <v>20</v>
       </c>
       <c r="I355" t="s">
-        <v>781</v>
+        <v>1185</v>
+      </c>
+      <c r="J355" t="s">
+        <v>1170</v>
       </c>
       <c r="K355" t="s">
+        <v>982</v>
+      </c>
+      <c r="L355" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>783</v>
       </c>
@@ -14214,13 +17484,19 @@
         <v>20</v>
       </c>
       <c r="I356" t="s">
-        <v>783</v>
+        <v>1186</v>
+      </c>
+      <c r="J356" t="s">
+        <v>1171</v>
       </c>
       <c r="K356" t="s">
+        <v>983</v>
+      </c>
+      <c r="L356" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>784</v>
       </c>
@@ -14246,13 +17522,19 @@
         <v>20</v>
       </c>
       <c r="I357" t="s">
-        <v>784</v>
+        <v>1187</v>
+      </c>
+      <c r="J357" t="s">
+        <v>1172</v>
       </c>
       <c r="K357" t="s">
+        <v>984</v>
+      </c>
+      <c r="L357" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>786</v>
       </c>
@@ -14278,13 +17560,19 @@
         <v>20</v>
       </c>
       <c r="I358" t="s">
-        <v>786</v>
+        <v>1188</v>
+      </c>
+      <c r="J358" t="s">
+        <v>1173</v>
       </c>
       <c r="K358" t="s">
+        <v>985</v>
+      </c>
+      <c r="L358" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>788</v>
       </c>
@@ -14310,13 +17598,19 @@
         <v>20</v>
       </c>
       <c r="I359" t="s">
-        <v>788</v>
+        <v>1189</v>
+      </c>
+      <c r="J359" t="s">
+        <v>1174</v>
       </c>
       <c r="K359" t="s">
+        <v>986</v>
+      </c>
+      <c r="L359" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>790</v>
       </c>
@@ -14342,13 +17636,19 @@
         <v>20</v>
       </c>
       <c r="I360" t="s">
-        <v>790</v>
+        <v>1190</v>
+      </c>
+      <c r="J360" t="s">
+        <v>993</v>
       </c>
       <c r="K360" t="s">
+        <v>805</v>
+      </c>
+      <c r="L360" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>792</v>
       </c>
@@ -14374,13 +17674,19 @@
         <v>20</v>
       </c>
       <c r="I361" t="s">
-        <v>792</v>
+        <v>1191</v>
+      </c>
+      <c r="J361" t="s">
+        <v>1175</v>
       </c>
       <c r="K361" t="s">
+        <v>987</v>
+      </c>
+      <c r="L361" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>794</v>
       </c>
@@ -14406,13 +17712,19 @@
         <v>20</v>
       </c>
       <c r="I362" t="s">
-        <v>794</v>
+        <v>1192</v>
+      </c>
+      <c r="J362" t="s">
+        <v>1176</v>
       </c>
       <c r="K362" t="s">
+        <v>988</v>
+      </c>
+      <c r="L362" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>795</v>
       </c>
@@ -14438,13 +17750,19 @@
         <v>20</v>
       </c>
       <c r="I363" t="s">
-        <v>795</v>
+        <v>1193</v>
+      </c>
+      <c r="J363" t="s">
+        <v>1177</v>
       </c>
       <c r="K363" t="s">
+        <v>989</v>
+      </c>
+      <c r="L363" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>797</v>
       </c>
@@ -14470,13 +17788,19 @@
         <v>20</v>
       </c>
       <c r="I364" t="s">
-        <v>797</v>
+        <v>1194</v>
+      </c>
+      <c r="J364" t="s">
+        <v>1178</v>
       </c>
       <c r="K364" t="s">
+        <v>990</v>
+      </c>
+      <c r="L364" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>799</v>
       </c>
@@ -14502,13 +17826,19 @@
         <v>20</v>
       </c>
       <c r="I365" t="s">
-        <v>799</v>
+        <v>1195</v>
+      </c>
+      <c r="J365" t="s">
+        <v>1179</v>
       </c>
       <c r="K365" t="s">
+        <v>991</v>
+      </c>
+      <c r="L365" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>801</v>
       </c>
@@ -14534,9 +17864,15 @@
         <v>20</v>
       </c>
       <c r="I366" t="s">
-        <v>801</v>
+        <v>1196</v>
+      </c>
+      <c r="J366" t="s">
+        <v>1180</v>
       </c>
       <c r="K366" t="s">
+        <v>992</v>
+      </c>
+      <c r="L366" t="s">
         <v>324</v>
       </c>
     </row>
